--- a/src/attributions/attributions_saliency_traj_113.xlsx
+++ b/src/attributions/attributions_saliency_traj_113.xlsx
@@ -1568,1709 +1568,1709 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.06757855415344238</v>
+        <v>0.001705396920442581</v>
       </c>
       <c r="B3" t="n">
-        <v>0.1120225489139557</v>
+        <v>0.0002764361561276019</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2518828809261322</v>
+        <v>0.0007627913728356361</v>
       </c>
       <c r="D3" t="n">
-        <v>0.06932209432125092</v>
+        <v>0.0005694942665286362</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2321990728378296</v>
+        <v>0.0005690391990356147</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1176656037569046</v>
+        <v>0.0002104008744936436</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02647312358021736</v>
+        <v>0.0001792985276551917</v>
       </c>
       <c r="H3" t="n">
-        <v>0.08791660517454147</v>
+        <v>0.0001563718542456627</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2027970999479294</v>
+        <v>9.118553862208501e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2169452607631683</v>
+        <v>0.001729641575366259</v>
       </c>
       <c r="K3" t="n">
-        <v>0.110319659113884</v>
+        <v>1.292364322580397e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1990737318992615</v>
+        <v>0.0005367328994907439</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01417793892323971</v>
+        <v>0.0003705014241859317</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2819948196411133</v>
+        <v>0.0008441543322987854</v>
       </c>
       <c r="O3" t="n">
-        <v>0.008420656435191631</v>
+        <v>1.418379724782426e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>0.01653865724802017</v>
+        <v>0.0002530109195504338</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.04618009179830551</v>
+        <v>9.152678831014782e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3143632411956787</v>
+        <v>0.00010068500705529</v>
       </c>
       <c r="S3" t="n">
-        <v>0.01038029789924622</v>
+        <v>0.0002668843953870237</v>
       </c>
       <c r="T3" t="n">
-        <v>0.01904797554016113</v>
+        <v>0.0002358478814130649</v>
       </c>
       <c r="U3" t="n">
-        <v>0.04108095169067383</v>
+        <v>0.0001915152533911169</v>
       </c>
       <c r="V3" t="n">
-        <v>0.07227437198162079</v>
+        <v>4.925248504150659e-06</v>
       </c>
       <c r="W3" t="n">
-        <v>0.03614926338195801</v>
+        <v>0.0001849299296736717</v>
       </c>
       <c r="X3" t="n">
-        <v>0.1001280471682549</v>
+        <v>0.0002669873938430101</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.01175131369382143</v>
+        <v>6.574152212124318e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.02118345350027084</v>
+        <v>0.0002025260764639825</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.07992406934499741</v>
+        <v>7.69423641031608e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.05089986696839333</v>
+        <v>2.610608498798683e-05</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.06892812997102737</v>
+        <v>2.665993815753609e-05</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.01819150894880295</v>
+        <v>5.600470831268467e-05</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.03913681209087372</v>
+        <v>0.000640078098513186</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.1913760602474213</v>
+        <v>0.0004307637282181531</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.01072127185761929</v>
+        <v>0.0007957472116686404</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.04437257349491119</v>
+        <v>0.0001181035695481114</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.04819989949464798</v>
+        <v>0.0001207798486575484</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.1135482713580132</v>
+        <v>6.149511318653822e-05</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.0431697741150856</v>
+        <v>8.285198418889195e-05</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.01340408530086279</v>
+        <v>0.0004266207397449762</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.01301949843764305</v>
+        <v>0.0004235552623867989</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.1287435293197632</v>
+        <v>0.0005752717261202633</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.03494056314229965</v>
+        <v>4.255411840858869e-05</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.03374618291854858</v>
+        <v>5.007508207199862e-06</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.05839073657989502</v>
+        <v>3.683681279653683e-05</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.02381760254502296</v>
+        <v>0.0001685409370111302</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.04409603029489517</v>
+        <v>9.171757847070694e-05</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.02505720779299736</v>
+        <v>0.0007890330161899328</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.08419172465801239</v>
+        <v>0.0002475210058037192</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.05480292066931725</v>
+        <v>0.0001571258471813053</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.06955289840698242</v>
+        <v>0.0003886052290908992</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.03686542063951492</v>
+        <v>0.0004911254509352148</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.05298644304275513</v>
+        <v>0.0003149641561321914</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.09474271535873413</v>
+        <v>0.0001239488192368299</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.08040778338909149</v>
+        <v>6.208768172655255e-05</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.1780375391244888</v>
+        <v>0.0001746645430102944</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.03531729057431221</v>
+        <v>0.0004902709624730051</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.1286202669143677</v>
+        <v>8.093654469121248e-05</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.1587396264076233</v>
+        <v>0.0003871488152071834</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.1113855987787247</v>
+        <v>0.0002793549792841077</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.2147101908922195</v>
+        <v>0.0005029310705140233</v>
       </c>
       <c r="BH3" t="n">
-        <v>0.1383130252361298</v>
+        <v>2.665467764018103e-05</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.02651047706604004</v>
+        <v>0.0001708053605398163</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.00183243490755558</v>
+        <v>0.0002140196011168882</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.2797088921070099</v>
+        <v>0.0002480811672285199</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.01081762090325356</v>
+        <v>0.0005452500772662461</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.0863470584154129</v>
+        <v>0.0003077910514548421</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.01444584690034389</v>
+        <v>0.0001007362443488091</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.06293748319149017</v>
+        <v>0.0003259049553889781</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.05378389731049538</v>
+        <v>0.000153205735841766</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.00679454579949379</v>
+        <v>8.738270844332874e-05</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.03572471812367439</v>
+        <v>5.356604378903285e-05</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.05107764154672623</v>
+        <v>8.832901585265063e-06</v>
       </c>
       <c r="BT3" t="n">
-        <v>0.07504954189062119</v>
+        <v>8.169803186319768e-05</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.05767159163951874</v>
+        <v>0.0002897806116379797</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.09977982938289642</v>
+        <v>0.0001691982761258259</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.01600836962461472</v>
+        <v>0.0005198887083679438</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.01830753311514854</v>
+        <v>2.433699592074845e-05</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.06571634113788605</v>
+        <v>0.0003266471612732857</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.08699186891317368</v>
+        <v>0.0001131279859691858</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.02408668771386147</v>
+        <v>6.544117059092969e-05</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.06982365995645523</v>
+        <v>0.0002938066318165511</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.1341754198074341</v>
+        <v>0.0002387384447501972</v>
       </c>
       <c r="CD3" t="n">
-        <v>0.02684894390404224</v>
+        <v>0.0003925597411580384</v>
       </c>
       <c r="CE3" t="n">
-        <v>0.03141969069838524</v>
+        <v>2.664152270881459e-05</v>
       </c>
       <c r="CF3" t="n">
-        <v>0.04572740197181702</v>
+        <v>0.0001162638072855771</v>
       </c>
       <c r="CG3" t="n">
-        <v>0.04401110857725143</v>
+        <v>0.0001612988125998527</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.01477456651628017</v>
+        <v>1.18921379907988e-05</v>
       </c>
       <c r="CI3" t="n">
-        <v>0.01277310214936733</v>
+        <v>2.491217128408607e-05</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0.01038451120257378</v>
+        <v>0.0001736452395562083</v>
       </c>
       <c r="CK3" t="n">
-        <v>0.04098370671272278</v>
+        <v>7.297622505575418e-05</v>
       </c>
       <c r="CL3" t="n">
-        <v>0.04149860516190529</v>
+        <v>3.064755946979858e-05</v>
       </c>
       <c r="CM3" t="n">
-        <v>0.03916383534669876</v>
+        <v>0.0003002702724188566</v>
       </c>
       <c r="CN3" t="n">
-        <v>0.04710466042160988</v>
+        <v>0.000586420064792037</v>
       </c>
       <c r="CO3" t="n">
-        <v>0.0230766236782074</v>
+        <v>0.0002895310171879828</v>
       </c>
       <c r="CP3" t="n">
-        <v>0.1616251468658447</v>
+        <v>6.395780656021088e-05</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.05714913457632065</v>
+        <v>0.0004244730225764215</v>
       </c>
       <c r="CR3" t="n">
-        <v>0.01492709200829268</v>
+        <v>0.0003057147550862283</v>
       </c>
       <c r="CS3" t="n">
-        <v>0.0005282647907733917</v>
+        <v>0.0003562486090231687</v>
       </c>
       <c r="CT3" t="n">
-        <v>0.01572450622916222</v>
+        <v>0.0002320332860108465</v>
       </c>
       <c r="CU3" t="n">
-        <v>0.01468771137297153</v>
+        <v>7.639824616489932e-05</v>
       </c>
       <c r="CV3" t="n">
-        <v>0.0216146819293499</v>
+        <v>0.0003463509783614427</v>
       </c>
       <c r="CW3" t="n">
-        <v>0.03089976124465466</v>
+        <v>0.0001736522681312636</v>
       </c>
       <c r="CX3" t="n">
-        <v>0.03882221877574921</v>
+        <v>0.000202836119569838</v>
       </c>
       <c r="CY3" t="n">
-        <v>0.05148302763700485</v>
+        <v>0.0001914752792799845</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.006269947160035372</v>
+        <v>0.0001706559560261667</v>
       </c>
       <c r="DA3" t="n">
-        <v>0.04454278573393822</v>
+        <v>1.855733717093244e-05</v>
       </c>
       <c r="DB3" t="n">
-        <v>0.006378742400556803</v>
+        <v>0.0001037028705468401</v>
       </c>
       <c r="DC3" t="n">
-        <v>0.01472385041415691</v>
+        <v>7.020940302027157e-06</v>
       </c>
       <c r="DD3" t="n">
-        <v>0.04960788041353226</v>
+        <v>3.00425999739673e-05</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.002398695796728134</v>
+        <v>0.0003260757366660982</v>
       </c>
       <c r="DF3" t="n">
-        <v>0.02135621756315231</v>
+        <v>0.001525512663647532</v>
       </c>
       <c r="DG3" t="n">
-        <v>0.1347611844539642</v>
+        <v>0.0002118350967066363</v>
       </c>
       <c r="DH3" t="n">
-        <v>0.08174959570169449</v>
+        <v>0.0007211579941213131</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.1138224229216576</v>
+        <v>0.0003285579732619226</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0.1395237892866135</v>
+        <v>0.000772345345467329</v>
       </c>
       <c r="DK3" t="n">
-        <v>0.1254426687955856</v>
+        <v>0.0002696793235372752</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.1232863515615463</v>
+        <v>0.0003767982125282288</v>
       </c>
       <c r="DM3" t="n">
-        <v>0.08876787126064301</v>
+        <v>0.000226941381697543</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.02347864396870136</v>
+        <v>0.0004573350306600332</v>
       </c>
       <c r="DO3" t="n">
-        <v>0.02176468260586262</v>
+        <v>0.000240857174503617</v>
       </c>
       <c r="DP3" t="n">
-        <v>0.003561768680810928</v>
+        <v>0.000358546880306676</v>
       </c>
       <c r="DQ3" t="n">
-        <v>0.09093727916479111</v>
+        <v>0.000212411570828408</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.1236880049109459</v>
+        <v>0.0004923673695884645</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.03492115437984467</v>
+        <v>7.481008651666343e-05</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.1703914850950241</v>
+        <v>3.689555524033494e-05</v>
       </c>
       <c r="DU3" t="n">
-        <v>0.1061155274510384</v>
+        <v>0.0002368444693274796</v>
       </c>
       <c r="DV3" t="n">
-        <v>0.06886637210845947</v>
+        <v>6.412157745216973e-06</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.007977541536092758</v>
+        <v>6.922603643033653e-05</v>
       </c>
       <c r="DX3" t="n">
-        <v>0.0211949460208416</v>
+        <v>9.563723870087415e-05</v>
       </c>
       <c r="DY3" t="n">
-        <v>0.01711008325219154</v>
+        <v>0.0007767839124426246</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0.05892810970544815</v>
+        <v>0.0001495886826887727</v>
       </c>
       <c r="EA3" t="n">
-        <v>0.07574076950550079</v>
+        <v>0.0007113952888175845</v>
       </c>
       <c r="EB3" t="n">
-        <v>0.02325521223247051</v>
+        <v>0.0001361293252557516</v>
       </c>
       <c r="EC3" t="n">
-        <v>0.01874088495969772</v>
+        <v>0.0002384640829404816</v>
       </c>
       <c r="ED3" t="n">
-        <v>0.02812312915921211</v>
+        <v>0.0002665478095877916</v>
       </c>
       <c r="EE3" t="n">
-        <v>0.04587653651833534</v>
+        <v>0.0002398753131274134</v>
       </c>
       <c r="EF3" t="n">
-        <v>0.03143990039825439</v>
+        <v>0.0004873234720434994</v>
       </c>
       <c r="EG3" t="n">
-        <v>0.04485096782445908</v>
+        <v>0.0001558234798721969</v>
       </c>
       <c r="EH3" t="n">
-        <v>0.0662258118391037</v>
+        <v>1.387229531246703e-05</v>
       </c>
       <c r="EI3" t="n">
-        <v>0.03772087395191193</v>
+        <v>0.0002482445270288736</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0.01004583761096001</v>
+        <v>0.000261676701484248</v>
       </c>
       <c r="EK3" t="n">
-        <v>0.1376627385616302</v>
+        <v>5.74421210330911e-05</v>
       </c>
       <c r="EL3" t="n">
-        <v>0.00509987398982048</v>
+        <v>0.0001543961989227682</v>
       </c>
       <c r="EM3" t="n">
-        <v>0.00495931226760149</v>
+        <v>3.565691076801158e-05</v>
       </c>
       <c r="EN3" t="n">
-        <v>0.08124612271785736</v>
+        <v>9.212366421706975e-05</v>
       </c>
       <c r="EO3" t="n">
-        <v>0.04477466642856598</v>
+        <v>0.0002997801639139652</v>
       </c>
       <c r="EP3" t="n">
-        <v>0.004104124382138252</v>
+        <v>0.0003561629564501345</v>
       </c>
       <c r="EQ3" t="n">
-        <v>0.05476145073771477</v>
+        <v>4.456545138964429e-05</v>
       </c>
       <c r="ER3" t="n">
-        <v>0.01513713784515858</v>
+        <v>3.263524195062928e-05</v>
       </c>
       <c r="ES3" t="n">
-        <v>0.07861576974391937</v>
+        <v>0.0001890801213448867</v>
       </c>
       <c r="ET3" t="n">
-        <v>0.02393264137208462</v>
+        <v>0.000391630717786029</v>
       </c>
       <c r="EU3" t="n">
-        <v>0.03799628838896751</v>
+        <v>0.0001464709639549255</v>
       </c>
       <c r="EV3" t="n">
-        <v>0.08531416207551956</v>
+        <v>9.359665273223072e-05</v>
       </c>
       <c r="EW3" t="n">
-        <v>0.1389011740684509</v>
+        <v>0.0002482503477949649</v>
       </c>
       <c r="EX3" t="n">
-        <v>0.02725179679691792</v>
+        <v>0.0003197843034286052</v>
       </c>
       <c r="EY3" t="n">
-        <v>0.02531925961375237</v>
+        <v>0.0002867488947231323</v>
       </c>
       <c r="EZ3" t="n">
-        <v>0.04642435535788536</v>
+        <v>0.0002086204767692834</v>
       </c>
       <c r="FA3" t="n">
-        <v>0.07096896320581436</v>
+        <v>0.0001237636170117185</v>
       </c>
       <c r="FB3" t="n">
-        <v>0.0006948537775315344</v>
+        <v>0.0001305389159824699</v>
       </c>
       <c r="FC3" t="n">
-        <v>0.03904116153717041</v>
+        <v>0.0001501029182691127</v>
       </c>
       <c r="FD3" t="n">
-        <v>0.006610328331589699</v>
+        <v>0.0002120875287801027</v>
       </c>
       <c r="FE3" t="n">
-        <v>0.02119187451899052</v>
+        <v>2.421560566290282e-05</v>
       </c>
       <c r="FF3" t="n">
-        <v>0.05350876972079277</v>
+        <v>2.090274756483268e-05</v>
       </c>
       <c r="FG3" t="n">
-        <v>0.01170636434108019</v>
+        <v>0.0006998731405474246</v>
       </c>
       <c r="FH3" t="n">
-        <v>0.03279188275337219</v>
+        <v>0.0002027189912041649</v>
       </c>
       <c r="FI3" t="n">
-        <v>0.02854469977319241</v>
+        <v>0.0001547250576550141</v>
       </c>
       <c r="FJ3" t="n">
-        <v>0.002770163118839264</v>
+        <v>8.998101111501455e-05</v>
       </c>
       <c r="FK3" t="n">
-        <v>0.02620203979313374</v>
+        <v>0.0002395930787315592</v>
       </c>
       <c r="FL3" t="n">
-        <v>0.02059479989111423</v>
+        <v>0.0003850329667329788</v>
       </c>
       <c r="FM3" t="n">
-        <v>0.09858015179634094</v>
+        <v>0.0001008238614303991</v>
       </c>
       <c r="FN3" t="n">
-        <v>0.01080192252993584</v>
+        <v>5.819401849294081e-05</v>
       </c>
       <c r="FO3" t="n">
-        <v>0.06196806579828262</v>
+        <v>7.029812695691362e-05</v>
       </c>
       <c r="FP3" t="n">
-        <v>0.03447233140468597</v>
+        <v>0.0002450035535730422</v>
       </c>
       <c r="FQ3" t="n">
-        <v>0.03295641392469406</v>
+        <v>0.0001739549188641831</v>
       </c>
       <c r="FR3" t="n">
-        <v>0.007452189922332764</v>
+        <v>0.0007391420658677816</v>
       </c>
       <c r="FS3" t="n">
-        <v>0.1875599324703217</v>
+        <v>0.001309615909121931</v>
       </c>
       <c r="FT3" t="n">
-        <v>0.04347053542733192</v>
+        <v>0.0002762170042842627</v>
       </c>
       <c r="FU3" t="n">
-        <v>0.01329996436834335</v>
+        <v>0.0001325159682892263</v>
       </c>
       <c r="FV3" t="n">
-        <v>0.07677609473466873</v>
+        <v>4.772775355377235e-05</v>
       </c>
       <c r="FW3" t="n">
-        <v>0.04344963282346725</v>
+        <v>3.942998591810465e-05</v>
       </c>
       <c r="FX3" t="n">
-        <v>0.02028166502714157</v>
+        <v>2.769189813989215e-05</v>
       </c>
       <c r="FY3" t="n">
-        <v>0.006515697576105595</v>
+        <v>0.0006068292423151433</v>
       </c>
       <c r="FZ3" t="n">
-        <v>0.009434404782950878</v>
+        <v>8.997393888421357e-05</v>
       </c>
       <c r="GA3" t="n">
-        <v>0.001239916542544961</v>
+        <v>2.939629121101461e-05</v>
       </c>
       <c r="GB3" t="n">
-        <v>0.03175053372979164</v>
+        <v>0.0001386156509397551</v>
       </c>
       <c r="GC3" t="n">
-        <v>0.01263951882719994</v>
+        <v>0.0009263589163310826</v>
       </c>
       <c r="GD3" t="n">
-        <v>0.1031662076711655</v>
+        <v>1.922848605317995e-05</v>
       </c>
       <c r="GE3" t="n">
-        <v>0.05045918002724648</v>
+        <v>0.0002104111190419644</v>
       </c>
       <c r="GF3" t="n">
-        <v>0.02345681190490723</v>
+        <v>0.0008567175245843828</v>
       </c>
       <c r="GG3" t="n">
-        <v>0.09299337863922119</v>
+        <v>9.549422247800976e-05</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.000182030227733776</v>
+        <v>4.415586954564787e-05</v>
       </c>
       <c r="B4" t="n">
-        <v>0.001040090573951602</v>
+        <v>0.002871677977964282</v>
       </c>
       <c r="C4" t="n">
-        <v>6.6739710746333e-05</v>
+        <v>0.0003151574055664241</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0005393993924371898</v>
+        <v>0.002601488959044218</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0001935963227879256</v>
+        <v>0.0004498366033658385</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0003297577204648405</v>
+        <v>0.0006268156575970352</v>
       </c>
       <c r="G4" t="n">
-        <v>9.055664122570306e-06</v>
+        <v>0.000802589172963053</v>
       </c>
       <c r="H4" t="n">
-        <v>2.284143920405768e-05</v>
+        <v>0.0004872985300607979</v>
       </c>
       <c r="I4" t="n">
-        <v>3.394662417122163e-05</v>
+        <v>0.0001180720500997268</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0002125503960996866</v>
+        <v>0.0002326074318261817</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0006962849874980748</v>
+        <v>0.002905532019212842</v>
       </c>
       <c r="L4" t="n">
-        <v>8.864171104505658e-05</v>
+        <v>0.0006399170379154384</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0004300487926229835</v>
+        <v>0.003510467708110809</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0003142701170872897</v>
+        <v>0.0008237450965680182</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0003984764334745705</v>
+        <v>0.0003003895690198988</v>
       </c>
       <c r="P4" t="n">
-        <v>9.171338024316356e-05</v>
+        <v>0.0009619544725865126</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0002113931986968964</v>
+        <v>7.048362749628723e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>9.268134454032406e-05</v>
+        <v>4.510843427851796e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>8.888098818715662e-06</v>
+        <v>5.952471838099882e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0001468418049626052</v>
+        <v>9.941063035512343e-05</v>
       </c>
       <c r="U4" t="n">
-        <v>1.27737112052273e-05</v>
+        <v>0.00015192836872302</v>
       </c>
       <c r="V4" t="n">
-        <v>8.42547815409489e-05</v>
+        <v>2.568942727521062e-05</v>
       </c>
       <c r="W4" t="n">
-        <v>2.390183726674877e-05</v>
+        <v>0.0003126289520878345</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0001331079693045467</v>
+        <v>0.0004148756561335176</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0001762980537023395</v>
+        <v>0.0002656322612892836</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.403783532325178e-05</v>
+        <v>0.0004045524983666837</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.336296064546332e-05</v>
+        <v>0.0005237194709479809</v>
       </c>
       <c r="AB4" t="n">
-        <v>5.294369475450367e-05</v>
+        <v>9.049419168150052e-05</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.0001370363606838509</v>
+        <v>8.327927207574248e-05</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.902073174482211e-05</v>
+        <v>0.0001046971592586488</v>
       </c>
       <c r="AE4" t="n">
-        <v>5.855863491888158e-05</v>
+        <v>0.0006318250671029091</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.0001033865046338178</v>
+        <v>3.653641897471971e-06</v>
       </c>
       <c r="AG4" t="n">
-        <v>3.25198816426564e-05</v>
+        <v>0.0004108945722691715</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.205699300044216e-05</v>
+        <v>0.0003558225289452821</v>
       </c>
       <c r="AI4" t="n">
-        <v>7.010777335381135e-05</v>
+        <v>7.820918108336627e-05</v>
       </c>
       <c r="AJ4" t="n">
-        <v>7.059454219415784e-05</v>
+        <v>4.594191705109552e-05</v>
       </c>
       <c r="AK4" t="n">
-        <v>6.213009328348562e-05</v>
+        <v>0.0001083185488823801</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.0001195012300740927</v>
+        <v>0.0007386754732578993</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.757192876539193e-05</v>
+        <v>0.0002585942856967449</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.975588202185463e-05</v>
+        <v>0.0004955502226948738</v>
       </c>
       <c r="AO4" t="n">
-        <v>1.513014194642892e-05</v>
+        <v>0.0003210370487067848</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.0001266018080059439</v>
+        <v>0.0005398626090027392</v>
       </c>
       <c r="AQ4" t="n">
-        <v>4.275826722732745e-05</v>
+        <v>0.000211094637052156</v>
       </c>
       <c r="AR4" t="n">
-        <v>3.31511655531358e-05</v>
+        <v>0.0003136389423161745</v>
       </c>
       <c r="AS4" t="n">
-        <v>7.006495434325188e-05</v>
+        <v>8.965087181422859e-05</v>
       </c>
       <c r="AT4" t="n">
-        <v>8.153438830049708e-05</v>
+        <v>1.694542152108625e-05</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.000724588637240231</v>
+        <v>0.001560652861371636</v>
       </c>
       <c r="AV4" t="n">
-        <v>4.646142315323232e-06</v>
+        <v>8.70520671014674e-05</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.0002353987656533718</v>
+        <v>0.001277015078812838</v>
       </c>
       <c r="AX4" t="n">
-        <v>8.015271305339411e-05</v>
+        <v>0.001597413327544928</v>
       </c>
       <c r="AY4" t="n">
-        <v>5.977344699203968e-07</v>
+        <v>0.0002013856428675354</v>
       </c>
       <c r="AZ4" t="n">
-        <v>8.575058745918795e-05</v>
+        <v>2.600460175017361e-05</v>
       </c>
       <c r="BA4" t="n">
-        <v>6.729806773364544e-05</v>
+        <v>0.0002561809087637812</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.000132982968352735</v>
+        <v>0.0002297428873134777</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.0001244074665009975</v>
+        <v>0.0002291359705850482</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.0001470270362915471</v>
+        <v>0.0001091656158678234</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.0001532541791675612</v>
+        <v>0.0004898773040622473</v>
       </c>
       <c r="BF4" t="n">
-        <v>7.067337719490752e-06</v>
+        <v>9.034250979311764e-06</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.0003096882428508252</v>
+        <v>0.0007584522827528417</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.0002233199775218964</v>
+        <v>0.0004657414683606476</v>
       </c>
       <c r="BI4" t="n">
-        <v>9.87607563729398e-05</v>
+        <v>0.000162962795002386</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.000162668467964977</v>
+        <v>0.0006605086964555085</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.445065299776616e-05</v>
+        <v>0.0004354036645963788</v>
       </c>
       <c r="BL4" t="n">
-        <v>4.9529302486917e-05</v>
+        <v>2.504513395251706e-05</v>
       </c>
       <c r="BM4" t="n">
-        <v>3.789744732785039e-05</v>
+        <v>0.0003079971647821367</v>
       </c>
       <c r="BN4" t="n">
-        <v>2.085540472762659e-05</v>
+        <v>0.0001093323226086795</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.000100604011095129</v>
+        <v>0.000230631121667102</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.68067082692869e-06</v>
+        <v>0.0002636212739162147</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.488831837079488e-05</v>
+        <v>0.000268568517640233</v>
       </c>
       <c r="BR4" t="n">
-        <v>1.062438968801871e-06</v>
+        <v>1.648029137868434e-05</v>
       </c>
       <c r="BS4" t="n">
-        <v>4.217489185975865e-05</v>
+        <v>0.0001189747417811304</v>
       </c>
       <c r="BT4" t="n">
-        <v>4.676195385400206e-05</v>
+        <v>2.129890344804153e-05</v>
       </c>
       <c r="BU4" t="n">
-        <v>6.188324186950922e-05</v>
+        <v>8.30432545626536e-05</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.0003702564572449774</v>
+        <v>0.0009186019888147712</v>
       </c>
       <c r="BW4" t="n">
-        <v>2.888017479563132e-05</v>
+        <v>0.0001460745115764439</v>
       </c>
       <c r="BX4" t="n">
-        <v>9.645833051763475e-05</v>
+        <v>0.0007856472511775792</v>
       </c>
       <c r="BY4" t="n">
-        <v>6.822323484811932e-05</v>
+        <v>0.0003423949528951198</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.0002218804293079302</v>
+        <v>0.0004078303463757038</v>
       </c>
       <c r="CA4" t="n">
-        <v>5.721081106457859e-05</v>
+        <v>0.0004573387268465012</v>
       </c>
       <c r="CB4" t="n">
-        <v>6.359077815432101e-05</v>
+        <v>0.0001158100785687566</v>
       </c>
       <c r="CC4" t="n">
-        <v>8.066014561336488e-05</v>
+        <v>0.000322407839121297</v>
       </c>
       <c r="CD4" t="n">
-        <v>6.008636773913167e-05</v>
+        <v>0.00011712838022504</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.0001714913814794272</v>
+        <v>0.0008774924790486693</v>
       </c>
       <c r="CF4" t="n">
-        <v>6.057229256839491e-05</v>
+        <v>0.0001394774008076638</v>
       </c>
       <c r="CG4" t="n">
-        <v>5.395735570346005e-05</v>
+        <v>0.0008170034852810204</v>
       </c>
       <c r="CH4" t="n">
-        <v>4.958412318956107e-05</v>
+        <v>6.248476711334661e-05</v>
       </c>
       <c r="CI4" t="n">
-        <v>8.75315599841997e-05</v>
+        <v>1.690063800197095e-05</v>
       </c>
       <c r="CJ4" t="n">
-        <v>3.191561700077727e-05</v>
+        <v>2.090413909172639e-05</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.045130920829251e-05</v>
+        <v>1.581085598445497e-05</v>
       </c>
       <c r="CL4" t="n">
-        <v>5.344225428416394e-05</v>
+        <v>9.813423821469769e-05</v>
       </c>
       <c r="CM4" t="n">
-        <v>6.118004239397123e-05</v>
+        <v>0.0001543957478133962</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.756962592480704e-05</v>
+        <v>0.0006342101260088384</v>
       </c>
       <c r="CO4" t="n">
-        <v>6.087557267164811e-05</v>
+        <v>0.0006955732824280858</v>
       </c>
       <c r="CP4" t="n">
-        <v>0.0001225094019901007</v>
+        <v>0.001010117353871465</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.0001455569581594318</v>
+        <v>3.667618875624612e-05</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.0001042710136971436</v>
+        <v>0.0002440501266391948</v>
       </c>
       <c r="CS4" t="n">
-        <v>7.220329280244187e-05</v>
+        <v>0.0002491488994564861</v>
       </c>
       <c r="CT4" t="n">
-        <v>0.0002306880487594754</v>
+        <v>0.0004684661980718374</v>
       </c>
       <c r="CU4" t="n">
-        <v>8.587386219005566e-06</v>
+        <v>0.000259814813034609</v>
       </c>
       <c r="CV4" t="n">
-        <v>4.337645077612251e-05</v>
+        <v>0.0001403097412548959</v>
       </c>
       <c r="CW4" t="n">
-        <v>0.0001335572160314769</v>
+        <v>0.0009196890168823302</v>
       </c>
       <c r="CX4" t="n">
-        <v>6.369236507453024e-05</v>
+        <v>0.0001594036002643406</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.0001175539000541903</v>
+        <v>0.0008784731035120785</v>
       </c>
       <c r="CZ4" t="n">
-        <v>4.190369145362638e-05</v>
+        <v>0.000172111569554545</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.0001085579860955477</v>
+        <v>1.841282755776774e-05</v>
       </c>
       <c r="DB4" t="n">
-        <v>2.194589251303114e-05</v>
+        <v>1.830798282753676e-05</v>
       </c>
       <c r="DC4" t="n">
-        <v>8.487797458656132e-06</v>
+        <v>1.539056211186107e-05</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.679130168166012e-05</v>
+        <v>0.0001575700734974816</v>
       </c>
       <c r="DE4" t="n">
-        <v>2.527131618990097e-05</v>
+        <v>0.0005286801024340093</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.0002112521760864183</v>
+        <v>0.0004912648582831025</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.905973269662354e-05</v>
+        <v>0.0002423650439595804</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.0002777027839329094</v>
+        <v>0.0006889356300234795</v>
       </c>
       <c r="DI4" t="n">
-        <v>6.351688352879137e-05</v>
+        <v>0.0004410288820508868</v>
       </c>
       <c r="DJ4" t="n">
-        <v>1.022930882754736e-05</v>
+        <v>0.0007567340508103371</v>
       </c>
       <c r="DK4" t="n">
-        <v>0.0001023930599330924</v>
+        <v>0.0002912376075983047</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.0001734883553581312</v>
+        <v>0.0007387438672594726</v>
       </c>
       <c r="DM4" t="n">
-        <v>1.373626946588047e-05</v>
+        <v>0.0001174458157038316</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.0001227398461196572</v>
+        <v>1.226134190801531e-05</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.104128361679614e-05</v>
+        <v>0.0004700071294791996</v>
       </c>
       <c r="DP4" t="n">
-        <v>3.337477392051369e-05</v>
+        <v>8.332212746609002e-05</v>
       </c>
       <c r="DQ4" t="n">
-        <v>2.908311398641672e-05</v>
+        <v>0.0006337392842397094</v>
       </c>
       <c r="DR4" t="n">
-        <v>4.484367309487425e-06</v>
+        <v>0.0002822984824888408</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.0001440173218725249</v>
+        <v>0.0001627163146622479</v>
       </c>
       <c r="DT4" t="n">
-        <v>9.942039469024166e-06</v>
+        <v>0.0006791019113734365</v>
       </c>
       <c r="DU4" t="n">
-        <v>3.955505235353485e-06</v>
+        <v>0.0002950261987280101</v>
       </c>
       <c r="DV4" t="n">
-        <v>8.146905747707933e-05</v>
+        <v>0.0008104993612505496</v>
       </c>
       <c r="DW4" t="n">
-        <v>6.482040043920279e-05</v>
+        <v>7.667839236091822e-05</v>
       </c>
       <c r="DX4" t="n">
-        <v>4.03920748794917e-05</v>
+        <v>0.0002473247004672885</v>
       </c>
       <c r="DY4" t="n">
-        <v>0.0001905045937746763</v>
+        <v>8.081521082203835e-05</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.786937304539606e-05</v>
+        <v>0.0005557266995310783</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.0001302410382777452</v>
+        <v>0.0002656294091138989</v>
       </c>
       <c r="EB4" t="n">
-        <v>7.1591159212403e-05</v>
+        <v>0.000560701300855726</v>
       </c>
       <c r="EC4" t="n">
-        <v>6.107635272201151e-06</v>
+        <v>6.033838144503534e-05</v>
       </c>
       <c r="ED4" t="n">
-        <v>6.684775144094601e-05</v>
+        <v>0.001424605026841164</v>
       </c>
       <c r="EE4" t="n">
-        <v>2.004117050091736e-05</v>
+        <v>0.000621957122348249</v>
       </c>
       <c r="EF4" t="n">
-        <v>4.382449697004631e-05</v>
+        <v>0.0003453214303590357</v>
       </c>
       <c r="EG4" t="n">
-        <v>8.031538891373202e-05</v>
+        <v>0.0005142854643054307</v>
       </c>
       <c r="EH4" t="n">
-        <v>5.380120455811266e-06</v>
+        <v>0.0001848560350481421</v>
       </c>
       <c r="EI4" t="n">
-        <v>5.225685526966117e-05</v>
+        <v>0.0007910958956927061</v>
       </c>
       <c r="EJ4" t="n">
-        <v>1.966876880032942e-05</v>
+        <v>0.0002304362860741094</v>
       </c>
       <c r="EK4" t="n">
-        <v>8.921312110032886e-05</v>
+        <v>7.436043961206451e-05</v>
       </c>
       <c r="EL4" t="n">
-        <v>5.215273995418102e-05</v>
+        <v>0.0001249688793905079</v>
       </c>
       <c r="EM4" t="n">
-        <v>6.18091580690816e-05</v>
+        <v>5.486964482770418e-08</v>
       </c>
       <c r="EN4" t="n">
-        <v>6.272772225202061e-06</v>
+        <v>3.807624307228252e-05</v>
       </c>
       <c r="EO4" t="n">
-        <v>4.467946564545855e-05</v>
+        <v>0.0001073251478374004</v>
       </c>
       <c r="EP4" t="n">
-        <v>0.0001377809094265103</v>
+        <v>0.0008515692898072302</v>
       </c>
       <c r="EQ4" t="n">
-        <v>1.042630174197257e-05</v>
+        <v>1.548356522107497e-06</v>
       </c>
       <c r="ER4" t="n">
-        <v>9.936537389876321e-05</v>
+        <v>0.0001614254724700004</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.0001223381841555238</v>
+        <v>0.0002326409448869526</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.0003444126923568547</v>
+        <v>0.0002839892986230552</v>
       </c>
       <c r="EU4" t="n">
-        <v>5.179161234991625e-06</v>
+        <v>0.0003474207478575408</v>
       </c>
       <c r="EV4" t="n">
-        <v>3.200153514626436e-05</v>
+        <v>9.6136711363215e-05</v>
       </c>
       <c r="EW4" t="n">
-        <v>2.710797343752347e-05</v>
+        <v>0.0005017128423787653</v>
       </c>
       <c r="EX4" t="n">
-        <v>3.942354305763729e-05</v>
+        <v>6.934435805305839e-05</v>
       </c>
       <c r="EY4" t="n">
-        <v>0.0001525300467619672</v>
+        <v>0.0009127954836003482</v>
       </c>
       <c r="EZ4" t="n">
-        <v>1.930838152475189e-05</v>
+        <v>9.581918129697442e-05</v>
       </c>
       <c r="FA4" t="n">
-        <v>8.375785546377301e-05</v>
+        <v>0.0009154691360890865</v>
       </c>
       <c r="FB4" t="n">
-        <v>4.351934330770746e-05</v>
+        <v>0.0001033285734592937</v>
       </c>
       <c r="FC4" t="n">
-        <v>0.0001033745284075849</v>
+        <v>3.427094270591624e-05</v>
       </c>
       <c r="FD4" t="n">
-        <v>3.690957237267867e-05</v>
+        <v>6.155585288070142e-05</v>
       </c>
       <c r="FE4" t="n">
-        <v>2.297383616678417e-07</v>
+        <v>0.0001362837792839855</v>
       </c>
       <c r="FF4" t="n">
-        <v>4.998209988116287e-05</v>
+        <v>0.0001758338912623003</v>
       </c>
       <c r="FG4" t="n">
-        <v>1.311244523094501e-05</v>
+        <v>4.756791167892516e-05</v>
       </c>
       <c r="FH4" t="n">
-        <v>7.480013300664723e-05</v>
+        <v>0.0003100290196016431</v>
       </c>
       <c r="FI4" t="n">
-        <v>3.127450327156112e-05</v>
+        <v>0.0003420853463467211</v>
       </c>
       <c r="FJ4" t="n">
-        <v>0.0001339425652986392</v>
+        <v>0.0002589147188700736</v>
       </c>
       <c r="FK4" t="n">
-        <v>4.077061930729542e-06</v>
+        <v>0.0002249837416457012</v>
       </c>
       <c r="FL4" t="n">
-        <v>4.095558324479498e-05</v>
+        <v>0.0002423069381620735</v>
       </c>
       <c r="FM4" t="n">
-        <v>5.636402784148231e-05</v>
+        <v>0.0002044622087851167</v>
       </c>
       <c r="FN4" t="n">
-        <v>3.123615169897676e-05</v>
+        <v>0.000699362950399518</v>
       </c>
       <c r="FO4" t="n">
-        <v>0.0001225097803398967</v>
+        <v>0.0003070373204536736</v>
       </c>
       <c r="FP4" t="n">
-        <v>1.015481302601984e-05</v>
+        <v>0.0003040212031919509</v>
       </c>
       <c r="FQ4" t="n">
-        <v>2.212199615314603e-05</v>
+        <v>0.000413800502428785</v>
       </c>
       <c r="FR4" t="n">
-        <v>2.14302672247868e-05</v>
+        <v>4.922204971080646e-05</v>
       </c>
       <c r="FS4" t="n">
-        <v>0.0001378458982799202</v>
+        <v>0.0009335598442703485</v>
       </c>
       <c r="FT4" t="n">
-        <v>0.0003107289376202971</v>
+        <v>0.0001430264965165406</v>
       </c>
       <c r="FU4" t="n">
-        <v>1.354022970190272e-05</v>
+        <v>0.0006252821767702699</v>
       </c>
       <c r="FV4" t="n">
-        <v>3.358429967192933e-05</v>
+        <v>5.766022513853386e-05</v>
       </c>
       <c r="FW4" t="n">
-        <v>7.10247695678845e-05</v>
+        <v>1.000586053123698e-05</v>
       </c>
       <c r="FX4" t="n">
-        <v>6.667587877018377e-05</v>
+        <v>0.0009932976681739092</v>
       </c>
       <c r="FY4" t="n">
-        <v>6.612561992369592e-05</v>
+        <v>0.0001198345562443137</v>
       </c>
       <c r="FZ4" t="n">
-        <v>7.038499461486936e-05</v>
+        <v>0.0004132736648898572</v>
       </c>
       <c r="GA4" t="n">
-        <v>4.871932833339088e-05</v>
+        <v>7.099044159986079e-05</v>
       </c>
       <c r="GB4" t="n">
-        <v>4.385476495372131e-05</v>
+        <v>0.0008370220311917365</v>
       </c>
       <c r="GC4" t="n">
-        <v>0.0002204842021455988</v>
+        <v>0.0008558652480132878</v>
       </c>
       <c r="GD4" t="n">
-        <v>0.0001057766639860347</v>
+        <v>0.0001632321364013478</v>
       </c>
       <c r="GE4" t="n">
-        <v>0.0001956569030880928</v>
+        <v>0.0009411468054167926</v>
       </c>
       <c r="GF4" t="n">
-        <v>1.741994492476806e-05</v>
+        <v>0.0001027144826366566</v>
       </c>
       <c r="GG4" t="n">
-        <v>5.031256296206266e-05</v>
+        <v>9.92410714388825e-05</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4.211438408674439e-06</v>
+        <v>0.001511178910732269</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0002200423186877742</v>
+        <v>0.002388392575085163</v>
       </c>
       <c r="C5" t="n">
-        <v>4.506291588768363e-05</v>
+        <v>0.0003533818235155195</v>
       </c>
       <c r="D5" t="n">
-        <v>5.946979945292696e-05</v>
+        <v>0.001169921713881195</v>
       </c>
       <c r="E5" t="n">
-        <v>7.863635255489498e-05</v>
+        <v>5.800195503979921e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0001381142064929008</v>
+        <v>0.003291070926934481</v>
       </c>
       <c r="G5" t="n">
-        <v>1.198552126879804e-05</v>
+        <v>0.001034143846482038</v>
       </c>
       <c r="H5" t="n">
-        <v>3.67234788427595e-05</v>
+        <v>0.001053335261531174</v>
       </c>
       <c r="I5" t="n">
-        <v>2.03251838684082e-05</v>
+        <v>0.0007631619810126722</v>
       </c>
       <c r="J5" t="n">
-        <v>1.814539064071141e-05</v>
+        <v>0.001665030489675701</v>
       </c>
       <c r="K5" t="n">
-        <v>0.000190578997717239</v>
+        <v>0.00318320537917316</v>
       </c>
       <c r="L5" t="n">
-        <v>1.25928290799493e-05</v>
+        <v>0.0006684036343358457</v>
       </c>
       <c r="M5" t="n">
-        <v>0.000113120702735614</v>
+        <v>0.0005061435513198376</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0001267189072677866</v>
+        <v>0.001485876739025116</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0001680191053310409</v>
+        <v>0.003250745590776205</v>
       </c>
       <c r="P5" t="n">
-        <v>6.928262882865965e-05</v>
+        <v>0.0005107483011670411</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.469464354566298e-05</v>
+        <v>2.41227971855551e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>3.174710946041159e-05</v>
+        <v>0.001564161852002144</v>
       </c>
       <c r="S5" t="n">
-        <v>1.177314879896585e-05</v>
+        <v>0.0002156082482542843</v>
       </c>
       <c r="T5" t="n">
-        <v>4.228229227010161e-05</v>
+        <v>0.0002494181098882109</v>
       </c>
       <c r="U5" t="n">
-        <v>7.625317721249303e-06</v>
+        <v>0.0009306705323979259</v>
       </c>
       <c r="V5" t="n">
-        <v>1.961001180461608e-05</v>
+        <v>0.0009376818779855967</v>
       </c>
       <c r="W5" t="n">
-        <v>4.819406058231834e-06</v>
+        <v>0.0004949083086103201</v>
       </c>
       <c r="X5" t="n">
-        <v>3.480065788608044e-05</v>
+        <v>0.0005060276016592979</v>
       </c>
       <c r="Y5" t="n">
-        <v>9.698485882836394e-06</v>
+        <v>0.000123441219329834</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.627916728670243e-06</v>
+        <v>0.0008471015025861561</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.364380972925574e-06</v>
+        <v>0.0005373221938498318</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.514211130095646e-05</v>
+        <v>0.0002550733042880893</v>
       </c>
       <c r="AC5" t="n">
-        <v>5.37490050191991e-05</v>
+        <v>0.000858503975905478</v>
       </c>
       <c r="AD5" t="n">
-        <v>5.000932287657633e-05</v>
+        <v>0.0001693936064839363</v>
       </c>
       <c r="AE5" t="n">
-        <v>3.71107817045413e-05</v>
+        <v>0.0008303284412249923</v>
       </c>
       <c r="AF5" t="n">
-        <v>7.179838576121256e-05</v>
+        <v>0.001169173512607813</v>
       </c>
       <c r="AG5" t="n">
-        <v>3.490211383905262e-05</v>
+        <v>0.0003741011023521423</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.886486799980048e-05</v>
+        <v>0.0003878141287714243</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.154932760982774e-05</v>
+        <v>0.001485693617723882</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6.374868007696932e-06</v>
+        <v>6.364814908010885e-05</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.37119704959332e-05</v>
+        <v>0.0002670125395525247</v>
       </c>
       <c r="AL5" t="n">
-        <v>4.149008236709051e-05</v>
+        <v>0.0005658449372276664</v>
       </c>
       <c r="AM5" t="n">
-        <v>3.621804353315383e-06</v>
+        <v>0.0008180846925824881</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.361897011520341e-05</v>
+        <v>0.0008802840020507574</v>
       </c>
       <c r="AO5" t="n">
-        <v>3.856820057990262e-06</v>
+        <v>6.138028402347118e-05</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.231950176996179e-05</v>
+        <v>0.0002740744675975293</v>
       </c>
       <c r="AQ5" t="n">
-        <v>2.23880670091603e-05</v>
+        <v>0.0002600252628326416</v>
       </c>
       <c r="AR5" t="n">
-        <v>7.631816515640821e-06</v>
+        <v>0.0007691844366490841</v>
       </c>
       <c r="AS5" t="n">
-        <v>9.930579835781828e-06</v>
+        <v>0.0007218536920845509</v>
       </c>
       <c r="AT5" t="n">
-        <v>3.480923260212876e-05</v>
+        <v>0.0009275174234062433</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.0001647915341891348</v>
+        <v>0.002790180500596762</v>
       </c>
       <c r="AV5" t="n">
-        <v>3.08665380543971e-06</v>
+        <v>0.0006377751706168056</v>
       </c>
       <c r="AW5" t="n">
-        <v>2.383099308644887e-05</v>
+        <v>0.0002041550178546458</v>
       </c>
       <c r="AX5" t="n">
-        <v>4.116193667869084e-05</v>
+        <v>0.0003904785553459078</v>
       </c>
       <c r="AY5" t="n">
-        <v>4.86213102703914e-05</v>
+        <v>0.001716623781248927</v>
       </c>
       <c r="AZ5" t="n">
-        <v>6.536075670737773e-05</v>
+        <v>8.89398215804249e-05</v>
       </c>
       <c r="BA5" t="n">
-        <v>2.671377660590224e-05</v>
+        <v>0.0003302967525087297</v>
       </c>
       <c r="BB5" t="n">
-        <v>2.976042196678463e-05</v>
+        <v>0.0006891535595059395</v>
       </c>
       <c r="BC5" t="n">
-        <v>9.508257790002972e-07</v>
+        <v>0.00021488378115464</v>
       </c>
       <c r="BD5" t="n">
-        <v>6.459240830736235e-05</v>
+        <v>5.666683136951178e-05</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.273302303976379e-05</v>
+        <v>0.0004262834845576435</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.064649859472411e-05</v>
+        <v>0.0007175279315561056</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.0001324850600212812</v>
+        <v>4.201770934741944e-06</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.83366699074395e-05</v>
+        <v>0.0006488864892162383</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.928159276256338e-05</v>
+        <v>5.352235166355968e-05</v>
       </c>
       <c r="BJ5" t="n">
-        <v>1.595125286257826e-05</v>
+        <v>0.0007449184195138514</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.505681848357199e-05</v>
+        <v>0.0004072767915204167</v>
       </c>
       <c r="BL5" t="n">
-        <v>2.720443808357231e-05</v>
+        <v>5.194821278564632e-05</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.336232071480481e-05</v>
+        <v>0.0008661063620820642</v>
       </c>
       <c r="BN5" t="n">
-        <v>2.71704193437472e-05</v>
+        <v>0.0001136342179961503</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.324467120866757e-06</v>
+        <v>0.000244244234636426</v>
       </c>
       <c r="BP5" t="n">
-        <v>6.437489901145454e-06</v>
+        <v>0.0006053316174075007</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.603245073056314e-05</v>
+        <v>0.0007589465822093189</v>
       </c>
       <c r="BR5" t="n">
-        <v>2.977233816636726e-05</v>
+        <v>0.001329310587607324</v>
       </c>
       <c r="BS5" t="n">
-        <v>3.178947281412547e-06</v>
+        <v>0.0001025534074869938</v>
       </c>
       <c r="BT5" t="n">
-        <v>1.510604670329485e-05</v>
+        <v>0.0009134677238762379</v>
       </c>
       <c r="BU5" t="n">
-        <v>1.369377696391894e-05</v>
+        <v>0.0003349210310261697</v>
       </c>
       <c r="BV5" t="n">
-        <v>7.843055936973542e-05</v>
+        <v>0.001781430677510798</v>
       </c>
       <c r="BW5" t="n">
-        <v>3.088711309828795e-05</v>
+        <v>0.0005475639482028782</v>
       </c>
       <c r="BX5" t="n">
-        <v>1.481168783357134e-05</v>
+        <v>0.001131599536165595</v>
       </c>
       <c r="BY5" t="n">
-        <v>8.649421033624094e-06</v>
+        <v>7.403938798233867e-05</v>
       </c>
       <c r="BZ5" t="n">
-        <v>3.033985194633715e-05</v>
+        <v>0.001227842411026359</v>
       </c>
       <c r="CA5" t="n">
-        <v>2.842843059625011e-05</v>
+        <v>0.000241654270212166</v>
       </c>
       <c r="CB5" t="n">
-        <v>1.058981706592022e-05</v>
+        <v>0.000302982225548476</v>
       </c>
       <c r="CC5" t="n">
-        <v>5.179237632546574e-06</v>
+        <v>0.0007300916477106512</v>
       </c>
       <c r="CD5" t="n">
-        <v>1.033401076711016e-06</v>
+        <v>0.000852032273542136</v>
       </c>
       <c r="CE5" t="n">
-        <v>3.976796142524108e-05</v>
+        <v>0.0008047489100135863</v>
       </c>
       <c r="CF5" t="n">
-        <v>3.070990715059452e-06</v>
+        <v>0.0002415163326077163</v>
       </c>
       <c r="CG5" t="n">
-        <v>1.589689418324269e-05</v>
+        <v>0.0005980576970614493</v>
       </c>
       <c r="CH5" t="n">
-        <v>4.981969141226728e-06</v>
+        <v>0.0003344244905747473</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.930119287862908e-05</v>
+        <v>0.0008644186891615391</v>
       </c>
       <c r="CJ5" t="n">
-        <v>2.397381103946827e-05</v>
+        <v>0.0006102770566940308</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.871880840553786e-06</v>
+        <v>0.0001792097464203835</v>
       </c>
       <c r="CL5" t="n">
-        <v>5.924895503994776e-06</v>
+        <v>0.0001282830780837685</v>
       </c>
       <c r="CM5" t="n">
-        <v>3.121026020380668e-05</v>
+        <v>0.0006728138541802764</v>
       </c>
       <c r="CN5" t="n">
-        <v>4.172776971245185e-05</v>
+        <v>0.001539390999823809</v>
       </c>
       <c r="CO5" t="n">
-        <v>3.290502718300559e-06</v>
+        <v>0.0004038740298710763</v>
       </c>
       <c r="CP5" t="n">
-        <v>8.03708826424554e-06</v>
+        <v>0.0001459322520531714</v>
       </c>
       <c r="CQ5" t="n">
-        <v>1.14547628982109e-05</v>
+        <v>0.0006241792580112815</v>
       </c>
       <c r="CR5" t="n">
-        <v>7.368209480773658e-06</v>
+        <v>0.0002018169761868194</v>
       </c>
       <c r="CS5" t="n">
-        <v>3.411476063774899e-05</v>
+        <v>0.0006214058375917375</v>
       </c>
       <c r="CT5" t="n">
-        <v>7.409176760120317e-05</v>
+        <v>0.0004870116827078164</v>
       </c>
       <c r="CU5" t="n">
-        <v>9.950896128430031e-06</v>
+        <v>0.0004544486873783171</v>
       </c>
       <c r="CV5" t="n">
-        <v>7.764920155750588e-07</v>
+        <v>0.0007204402354545891</v>
       </c>
       <c r="CW5" t="n">
-        <v>2.827753269230016e-05</v>
+        <v>0.0006898663705214858</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.19855012599146e-05</v>
+        <v>0.0001894639572128654</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.821158366510645e-05</v>
+        <v>0.0004873296129517257</v>
       </c>
       <c r="CZ5" t="n">
-        <v>3.359444690431701e-06</v>
+        <v>0.0002069969341391698</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.955331390490755e-05</v>
+        <v>0.0008376938058063388</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.233722650795244e-05</v>
+        <v>0.0004268198099453002</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.662451722950209e-06</v>
+        <v>0.0002502468414604664</v>
       </c>
       <c r="DD5" t="n">
-        <v>4.660621925722808e-06</v>
+        <v>0.0001608342863619328</v>
       </c>
       <c r="DE5" t="n">
-        <v>1.764388071023859e-05</v>
+        <v>0.0001517404743935913</v>
       </c>
       <c r="DF5" t="n">
-        <v>6.524223135784268e-05</v>
+        <v>0.0007257798570208251</v>
       </c>
       <c r="DG5" t="n">
-        <v>6.25133397988975e-05</v>
+        <v>0.000624243461061269</v>
       </c>
       <c r="DH5" t="n">
-        <v>9.107130608754233e-06</v>
+        <v>0.0005367422709241509</v>
       </c>
       <c r="DI5" t="n">
-        <v>2.508611942175776e-05</v>
+        <v>0.0009970981627702713</v>
       </c>
       <c r="DJ5" t="n">
-        <v>9.492327808402479e-05</v>
+        <v>0.0005771020660176873</v>
       </c>
       <c r="DK5" t="n">
-        <v>4.604933201335371e-05</v>
+        <v>0.0001255816896446049</v>
       </c>
       <c r="DL5" t="n">
-        <v>2.504494113964029e-05</v>
+        <v>0.001114735030569136</v>
       </c>
       <c r="DM5" t="n">
-        <v>2.212757863162551e-05</v>
+        <v>0.0001136322098318487</v>
       </c>
       <c r="DN5" t="n">
-        <v>7.027712399576558e-06</v>
+        <v>0.0001932624727487564</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.656281503732316e-05</v>
+        <v>0.0004452191642485559</v>
       </c>
       <c r="DP5" t="n">
-        <v>1.48366007124423e-06</v>
+        <v>0.0003315014764666557</v>
       </c>
       <c r="DQ5" t="n">
-        <v>5.207506183069199e-05</v>
+        <v>0.0006900695152580738</v>
       </c>
       <c r="DR5" t="n">
-        <v>2.943348590633832e-05</v>
+        <v>0.0004574133199639618</v>
       </c>
       <c r="DS5" t="n">
-        <v>3.477451900835149e-05</v>
+        <v>0.0008244938217103481</v>
       </c>
       <c r="DT5" t="n">
-        <v>1.256289760931395e-05</v>
+        <v>0.000390506029361859</v>
       </c>
       <c r="DU5" t="n">
-        <v>1.945804433489684e-05</v>
+        <v>0.0009617262985557318</v>
       </c>
       <c r="DV5" t="n">
-        <v>7.900794116721954e-06</v>
+        <v>0.0003236536285839975</v>
       </c>
       <c r="DW5" t="n">
-        <v>1.470462848374154e-05</v>
+        <v>0.0003363988071214408</v>
       </c>
       <c r="DX5" t="n">
-        <v>1.020920535665937e-05</v>
+        <v>1.062993760569952e-06</v>
       </c>
       <c r="DY5" t="n">
-        <v>8.26531231723493e-06</v>
+        <v>2.525857416912913e-05</v>
       </c>
       <c r="DZ5" t="n">
-        <v>5.51739358343184e-05</v>
+        <v>0.0001889588602352887</v>
       </c>
       <c r="EA5" t="n">
-        <v>3.822245162155014e-06</v>
+        <v>0.000763469492085278</v>
       </c>
       <c r="EB5" t="n">
-        <v>3.642472802312113e-05</v>
+        <v>0.001283948309719563</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.988206324516796e-05</v>
+        <v>0.0002213558909716085</v>
       </c>
       <c r="ED5" t="n">
-        <v>6.733233021805063e-05</v>
+        <v>0.0002242770133307204</v>
       </c>
       <c r="EE5" t="n">
-        <v>1.196254743263125e-05</v>
+        <v>0.0009767313022166491</v>
       </c>
       <c r="EF5" t="n">
-        <v>1.521249214420095e-05</v>
+        <v>0.0008243147167377174</v>
       </c>
       <c r="EG5" t="n">
-        <v>2.309556839463767e-05</v>
+        <v>9.335901995655149e-05</v>
       </c>
       <c r="EH5" t="n">
-        <v>4.329502644395689e-06</v>
+        <v>0.0004998981021344662</v>
       </c>
       <c r="EI5" t="n">
-        <v>1.865297963377088e-05</v>
+        <v>0.0008067318121902645</v>
       </c>
       <c r="EJ5" t="n">
-        <v>1.153880748461233e-05</v>
+        <v>0.0005804516258649528</v>
       </c>
       <c r="EK5" t="n">
-        <v>4.115893716516439e-06</v>
+        <v>0.0005080861155875027</v>
       </c>
       <c r="EL5" t="n">
-        <v>4.287514457246289e-05</v>
+        <v>0.000299712031846866</v>
       </c>
       <c r="EM5" t="n">
-        <v>4.503056061366806e-07</v>
+        <v>3.986684896517545e-05</v>
       </c>
       <c r="EN5" t="n">
-        <v>3.203678261343157e-06</v>
+        <v>0.000231554513447918</v>
       </c>
       <c r="EO5" t="n">
-        <v>7.461355380655732e-06</v>
+        <v>0.0006316677900031209</v>
       </c>
       <c r="EP5" t="n">
-        <v>1.130338205257431e-05</v>
+        <v>0.0003318038070574403</v>
       </c>
       <c r="EQ5" t="n">
-        <v>2.548489101172891e-05</v>
+        <v>0.000251293065957725</v>
       </c>
       <c r="ER5" t="n">
-        <v>3.270171509939246e-05</v>
+        <v>0.0005776519537903368</v>
       </c>
       <c r="ES5" t="n">
-        <v>4.434376751305535e-05</v>
+        <v>0.000788895005825907</v>
       </c>
       <c r="ET5" t="n">
-        <v>5.19533823535312e-05</v>
+        <v>0.0006626603426411748</v>
       </c>
       <c r="EU5" t="n">
-        <v>1.144869474956067e-05</v>
+        <v>3.552043926902115e-05</v>
       </c>
       <c r="EV5" t="n">
-        <v>6.85811892253696e-06</v>
+        <v>0.0002020540414378047</v>
       </c>
       <c r="EW5" t="n">
-        <v>1.331128896708833e-05</v>
+        <v>0.0006327226292341948</v>
       </c>
       <c r="EX5" t="n">
-        <v>2.364697138546035e-06</v>
+        <v>0.0008404396940022707</v>
       </c>
       <c r="EY5" t="n">
-        <v>2.966333522635978e-05</v>
+        <v>0.0008864466799423099</v>
       </c>
       <c r="EZ5" t="n">
-        <v>2.560137090767967e-06</v>
+        <v>0.0001164162677014247</v>
       </c>
       <c r="FA5" t="n">
-        <v>1.451434036425781e-05</v>
+        <v>0.0005150252254679799</v>
       </c>
       <c r="FB5" t="n">
-        <v>9.604634215065744e-06</v>
+        <v>0.0004582470864988863</v>
       </c>
       <c r="FC5" t="n">
-        <v>2.225383650511503e-05</v>
+        <v>0.000754818320274353</v>
       </c>
       <c r="FD5" t="n">
-        <v>1.799163510440849e-05</v>
+        <v>0.0005261753685772419</v>
       </c>
       <c r="FE5" t="n">
-        <v>8.060819709498901e-06</v>
+        <v>0.0002645475324243307</v>
       </c>
       <c r="FF5" t="n">
-        <v>5.106456683279248e-06</v>
+        <v>0.0001368436933262274</v>
       </c>
       <c r="FG5" t="n">
-        <v>3.12392512569204e-06</v>
+        <v>0.0002422587858745828</v>
       </c>
       <c r="FH5" t="n">
-        <v>7.034173449937953e-06</v>
+        <v>0.001157940598204732</v>
       </c>
       <c r="FI5" t="n">
-        <v>5.108665391162504e-06</v>
+        <v>0.0003029088547918946</v>
       </c>
       <c r="FJ5" t="n">
-        <v>5.30574907315895e-05</v>
+        <v>0.0005421870155259967</v>
       </c>
       <c r="FK5" t="n">
-        <v>5.438974403659813e-05</v>
+        <v>0.0003811203641816974</v>
       </c>
       <c r="FL5" t="n">
-        <v>1.32533077703556e-05</v>
+        <v>0.001130868913605809</v>
       </c>
       <c r="FM5" t="n">
-        <v>2.792972009046935e-05</v>
+        <v>0.0006488042999990284</v>
       </c>
       <c r="FN5" t="n">
-        <v>5.36125480721239e-05</v>
+        <v>0.001838985714130104</v>
       </c>
       <c r="FO5" t="n">
-        <v>3.144618312944658e-05</v>
+        <v>0.0003032192762475461</v>
       </c>
       <c r="FP5" t="n">
-        <v>1.881263597169891e-05</v>
+        <v>0.0002772090374492109</v>
       </c>
       <c r="FQ5" t="n">
-        <v>7.002658821875229e-05</v>
+        <v>0.0005974722444079816</v>
       </c>
       <c r="FR5" t="n">
-        <v>3.382688009878621e-05</v>
+        <v>0.001321186078712344</v>
       </c>
       <c r="FS5" t="n">
-        <v>7.968072168296203e-05</v>
+        <v>0.000436693400843069</v>
       </c>
       <c r="FT5" t="n">
-        <v>6.552533886861056e-05</v>
+        <v>0.0005209374357946217</v>
       </c>
       <c r="FU5" t="n">
-        <v>5.587531632045284e-05</v>
+        <v>0.0002211697865277529</v>
       </c>
       <c r="FV5" t="n">
-        <v>5.184983820072375e-05</v>
+        <v>0.0004705160390585661</v>
       </c>
       <c r="FW5" t="n">
-        <v>8.59890496940352e-06</v>
+        <v>0.0009982305346056819</v>
       </c>
       <c r="FX5" t="n">
-        <v>2.796378248604015e-05</v>
+        <v>0.0008760577766224742</v>
       </c>
       <c r="FY5" t="n">
-        <v>1.317349961027503e-05</v>
+        <v>0.0009080921299755573</v>
       </c>
       <c r="FZ5" t="n">
-        <v>3.978287350037135e-05</v>
+        <v>0.0005630721570923924</v>
       </c>
       <c r="GA5" t="n">
-        <v>6.312449113465846e-05</v>
+        <v>0.0004032476281281561</v>
       </c>
       <c r="GB5" t="n">
-        <v>4.695780262409244e-06</v>
+        <v>0.0006834919913671911</v>
       </c>
       <c r="GC5" t="n">
-        <v>1.118491582019487e-05</v>
+        <v>0.001239476492628455</v>
       </c>
       <c r="GD5" t="n">
-        <v>1.266294020751957e-05</v>
+        <v>0.0009386677411384881</v>
       </c>
       <c r="GE5" t="n">
-        <v>1.792735565686598e-05</v>
+        <v>0.0002293881843797863</v>
       </c>
       <c r="GF5" t="n">
-        <v>2.039722494373564e-05</v>
+        <v>0.0004006174567621201</v>
       </c>
       <c r="GG5" t="n">
-        <v>2.731881068029907e-05</v>
+        <v>0.001277004485018551</v>
       </c>
     </row>
     <row r="6">
@@ -3844,571 +3844,571 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.01281987316906452</v>
+        <v>0.0002170789521187544</v>
       </c>
       <c r="B7" t="n">
-        <v>0.07864522188901901</v>
+        <v>0.004655584692955017</v>
       </c>
       <c r="C7" t="n">
-        <v>0.005686255637556314</v>
+        <v>0.001091266749426723</v>
       </c>
       <c r="D7" t="n">
-        <v>0.03690327703952789</v>
+        <v>0.003697587642818689</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01794358901679516</v>
+        <v>0.0004820415342692286</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01806901767849922</v>
+        <v>0.003148259362205863</v>
       </c>
       <c r="G7" t="n">
-        <v>0.003411001758649945</v>
+        <v>0.002042161766439676</v>
       </c>
       <c r="H7" t="n">
-        <v>0.006984507665038109</v>
+        <v>0.002202128991484642</v>
       </c>
       <c r="I7" t="n">
-        <v>0.002057782839983702</v>
+        <v>0.0002041599946096539</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01811023615300655</v>
+        <v>0.000136083850520663</v>
       </c>
       <c r="K7" t="n">
-        <v>0.05042209103703499</v>
+        <v>0.004672398325055838</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002693759510293603</v>
+        <v>0.001994323218241334</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03382767736911774</v>
+        <v>0.005243013612926006</v>
       </c>
       <c r="N7" t="n">
-        <v>0.02979706972837448</v>
+        <v>0.001619290211237967</v>
       </c>
       <c r="O7" t="n">
-        <v>0.02842207252979279</v>
+        <v>0.002884842921048403</v>
       </c>
       <c r="P7" t="n">
-        <v>0.00440176110714674</v>
+        <v>0.00246871798299253</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.003760634921491146</v>
+        <v>0.001117567997425795</v>
       </c>
       <c r="R7" t="n">
-        <v>0.005354352295398712</v>
+        <v>0.0004636576923076063</v>
       </c>
       <c r="S7" t="n">
-        <v>0.001877974020317197</v>
+        <v>4.736545088235289e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>0.009241068735718727</v>
+        <v>2.955891250167042e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>0.002336620818823576</v>
+        <v>0.0002848050207830966</v>
       </c>
       <c r="V7" t="n">
-        <v>0.01258302666246891</v>
+        <v>0.0001959395885933191</v>
       </c>
       <c r="W7" t="n">
-        <v>0.01003232225775719</v>
+        <v>0.0004823370836675167</v>
       </c>
       <c r="X7" t="n">
-        <v>0.005746167618781328</v>
+        <v>0.001287800259888172</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.009789531119167805</v>
+        <v>0.0002796329208649695</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.005655992776155472</v>
+        <v>0.0007034876034595072</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.006723093800246716</v>
+        <v>0.0008719713077880442</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.002414514776319265</v>
+        <v>0.0003473266260698438</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.01099313423037529</v>
+        <v>0.0006876944098621607</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.0002854441991075873</v>
+        <v>0.0007237860700115561</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.002671621274203062</v>
+        <v>0.0004579386149998754</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.008302468806505203</v>
+        <v>0.000228913762839511</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.003489562310278416</v>
+        <v>0.0021862150169909</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.0006085997447371483</v>
+        <v>0.0002338051417609677</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.001685474300757051</v>
+        <v>0.001116704428568482</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.002435653004795313</v>
+        <v>0.0003657344495877624</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.006874013692140579</v>
+        <v>0.0002169585204683244</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.00884469598531723</v>
+        <v>0.001409004908055067</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.0002454389177728444</v>
+        <v>0.00113187066745013</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.0040116086602211</v>
+        <v>0.0008733328431844711</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.007940091192722321</v>
+        <v>0.0005080428090877831</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.01017904561012983</v>
+        <v>0.001017639762721956</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.0005150102078914642</v>
+        <v>0.0005818565841764212</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.0004341034218668938</v>
+        <v>0.0001542761019663885</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.005188846029341221</v>
+        <v>0.0002354996395297348</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.002897689118981361</v>
+        <v>1.186941517516971e-06</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.05543308705091476</v>
+        <v>0.002367143053561449</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.0004276013351045549</v>
+        <v>0.001052526640705764</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.00778571330010891</v>
+        <v>0.002154174260795116</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.004982208367437124</v>
+        <v>0.003534173360094428</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.0016129583818838</v>
+        <v>0.002370595000684261</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.003763514338061213</v>
+        <v>0.0002278628380736336</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.0001082653179764748</v>
+        <v>0.0001135095226345584</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.004888973198831081</v>
+        <v>0.000490709557197988</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.004197865724563599</v>
+        <v>0.0003788245667237788</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.01219419110566378</v>
+        <v>8.133078517857939e-05</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.009726564399898052</v>
+        <v>0.001157778780907393</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.003948166966438293</v>
+        <v>0.000587605987675488</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.02349291183054447</v>
+        <v>0.001622107112780213</v>
       </c>
       <c r="BH7" t="n">
-        <v>0.0111274616792798</v>
+        <v>0.0005688657984137535</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.006940222810953856</v>
+        <v>0.0006180150667205453</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.004489480052143335</v>
+        <v>0.001331883831880987</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.0003464120964054018</v>
+        <v>0.000546624418348074</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.009750879369676113</v>
+        <v>0.0001213738869410008</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.01099557522684336</v>
+        <v>0.0001901495852507651</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.002897709375247359</v>
+        <v>7.541482773376629e-05</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.006806990131735802</v>
+        <v>0.0007268323097378016</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.007773018442094326</v>
+        <v>0.0001787051296560094</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0.005344141274690628</v>
+        <v>4.74573353130836e-05</v>
       </c>
       <c r="BR7" t="n">
-        <v>0.004480002913624048</v>
+        <v>0.0001108319775084965</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.001200944068841636</v>
+        <v>0.0005390837322920561</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.007355370558798313</v>
+        <v>0.0001796961878426373</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.003340058028697968</v>
+        <v>0.0001160798565251753</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.0282029751688242</v>
+        <v>0.001561671728268266</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.00399793079122901</v>
+        <v>0.0007687543984502554</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.008944697678089142</v>
+        <v>0.002038652542978525</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.005372620653361082</v>
+        <v>0.000748295511584729</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.01143688429147005</v>
+        <v>0.001688292133621871</v>
       </c>
       <c r="CA7" t="n">
-        <v>0.002524378942325711</v>
+        <v>0.000607866735663265</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.004038314335048199</v>
+        <v>0.0002014442143263295</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.007160232868045568</v>
+        <v>0.0006437564152292907</v>
       </c>
       <c r="CD7" t="n">
-        <v>0.005207321606576443</v>
+        <v>3.087893128395081e-05</v>
       </c>
       <c r="CE7" t="n">
-        <v>0.01261291559785604</v>
+        <v>0.001528924098238349</v>
       </c>
       <c r="CF7" t="n">
-        <v>0.004761776886880398</v>
+        <v>0.0001870723790489137</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.003183586755767465</v>
+        <v>0.001427852315828204</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.001635313034057617</v>
+        <v>2.819567453116179e-05</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.004983239807188511</v>
+        <v>0.0005762676009908319</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0.002463294425979257</v>
+        <v>0.000119262287626043</v>
       </c>
       <c r="CK7" t="n">
-        <v>0.0009306833962909877</v>
+        <v>0.0003485904016997665</v>
       </c>
       <c r="CL7" t="n">
-        <v>0.003598187584429979</v>
+        <v>6.39873105683364e-05</v>
       </c>
       <c r="CM7" t="n">
-        <v>0.007437338586896658</v>
+        <v>0.0001063208183040842</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.002721774857491255</v>
+        <v>0.0007358535658568144</v>
       </c>
       <c r="CO7" t="n">
-        <v>0.007160578854382038</v>
+        <v>0.002316584344953299</v>
       </c>
       <c r="CP7" t="n">
-        <v>0.01319499313831329</v>
+        <v>0.002191087231040001</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.007835403084754944</v>
+        <v>0.0003420233260840178</v>
       </c>
       <c r="CR7" t="n">
-        <v>0.007401073351502419</v>
+        <v>0.000730128085706383</v>
       </c>
       <c r="CS7" t="n">
-        <v>0.008026519790291786</v>
+        <v>0.0001730834337649867</v>
       </c>
       <c r="CT7" t="n">
-        <v>0.009937265887856483</v>
+        <v>0.0006734970957040787</v>
       </c>
       <c r="CU7" t="n">
-        <v>0.002537966705858707</v>
+        <v>0.00022831407841295</v>
       </c>
       <c r="CV7" t="n">
-        <v>0.00475236913189292</v>
+        <v>1.863495890574995e-05</v>
       </c>
       <c r="CW7" t="n">
-        <v>0.01014481764286757</v>
+        <v>0.00150341959670186</v>
       </c>
       <c r="CX7" t="n">
-        <v>0.004669558722525835</v>
+        <v>0.0003767937305383384</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.00692563084885478</v>
+        <v>0.001565820421092212</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.001507642562501132</v>
+        <v>0.0003857462434098125</v>
       </c>
       <c r="DA7" t="n">
-        <v>0.005716555751860142</v>
+        <v>0.0006433537346310914</v>
       </c>
       <c r="DB7" t="n">
-        <v>0.002859989646822214</v>
+        <v>0.0002434296475257725</v>
       </c>
       <c r="DC7" t="n">
-        <v>0.001642452552914619</v>
+        <v>0.0003083964402321726</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.002540560672059655</v>
+        <v>0.000129602529341355</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.007187447510659695</v>
+        <v>0.0001672543148742989</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.005639513954520226</v>
+        <v>0.001020091236568987</v>
       </c>
       <c r="DG7" t="n">
-        <v>0.0009803437860682607</v>
+        <v>0.0003832387446891516</v>
       </c>
       <c r="DH7" t="n">
-        <v>0.01775688119232655</v>
+        <v>0.001239667646586895</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.01123377680778503</v>
+        <v>0.0005444684647955</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0.004953610710799694</v>
+        <v>0.002847746713086963</v>
       </c>
       <c r="DK7" t="n">
-        <v>0.007007638923823833</v>
+        <v>0.0001555774942971766</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.0008487983141094446</v>
+        <v>0.002456155372783542</v>
       </c>
       <c r="DM7" t="n">
-        <v>0.001693118829280138</v>
+        <v>0.0009225401445291936</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.00957653671503067</v>
+        <v>2.269633114337921e-06</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.004248000681400299</v>
+        <v>0.0009020724100992084</v>
       </c>
       <c r="DP7" t="n">
-        <v>0.006069255527108908</v>
+        <v>0.0002307343820575625</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0.001902757794596255</v>
+        <v>0.0004315031983423978</v>
       </c>
       <c r="DR7" t="n">
-        <v>0.002475368091836572</v>
+        <v>0.0002094785158988088</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.00903662946075201</v>
+        <v>0.0004516617045737803</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.0007972454186528921</v>
+        <v>0.0007820283062756062</v>
       </c>
       <c r="DU7" t="n">
-        <v>0.001462883432395756</v>
+        <v>0.0007515597390010953</v>
       </c>
       <c r="DV7" t="n">
-        <v>0.004900993313640356</v>
+        <v>0.001809005276300013</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.003872030880302191</v>
+        <v>6.983359344303608e-05</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.0009936451679095626</v>
+        <v>4.683545557782054e-05</v>
       </c>
       <c r="DY7" t="n">
-        <v>0.01206910889595747</v>
+        <v>0.0009843653533607721</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0.003666358534246683</v>
+        <v>0.0006136262090876698</v>
       </c>
       <c r="EA7" t="n">
-        <v>0.008957586251199245</v>
+        <v>0.0001745804474921897</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.002406243467703462</v>
+        <v>0.001273388392291963</v>
       </c>
       <c r="EC7" t="n">
-        <v>0.0001950197038240731</v>
+        <v>9.344436693936586e-05</v>
       </c>
       <c r="ED7" t="n">
-        <v>0.001075997948646545</v>
+        <v>0.002579543273895979</v>
       </c>
       <c r="EE7" t="n">
-        <v>0.003000050783157349</v>
+        <v>0.002309964736923575</v>
       </c>
       <c r="EF7" t="n">
-        <v>0.001388280419632792</v>
+        <v>0.0006633227458223701</v>
       </c>
       <c r="EG7" t="n">
-        <v>0.00553568173199892</v>
+        <v>0.0009905272163450718</v>
       </c>
       <c r="EH7" t="n">
-        <v>0.0006026247283443809</v>
+        <v>0.0008543699514120817</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.0007156512001529336</v>
+        <v>0.001428526011295617</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.002430849708616734</v>
+        <v>0.000275162048637867</v>
       </c>
       <c r="EK7" t="n">
-        <v>0.003178413491696119</v>
+        <v>0.0004925642861053348</v>
       </c>
       <c r="EL7" t="n">
-        <v>0.003515989519655704</v>
+        <v>5.175235855858773e-05</v>
       </c>
       <c r="EM7" t="n">
-        <v>0.001788735273294151</v>
+        <v>3.497693978715688e-05</v>
       </c>
       <c r="EN7" t="n">
-        <v>0.0001149495947174728</v>
+        <v>0.0002045099390670657</v>
       </c>
       <c r="EO7" t="n">
-        <v>0.004579111468046904</v>
+        <v>0.0003173516306560487</v>
       </c>
       <c r="EP7" t="n">
-        <v>0.008935190737247467</v>
+        <v>0.001547402353025973</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0.001450263080187142</v>
+        <v>0.0001507643901277333</v>
       </c>
       <c r="ER7" t="n">
-        <v>0.007292804773896933</v>
+        <v>0.001141213346272707</v>
       </c>
       <c r="ES7" t="n">
-        <v>0.007480151951313019</v>
+        <v>0.0004784759366884828</v>
       </c>
       <c r="ET7" t="n">
-        <v>0.02054218575358391</v>
+        <v>0.0002119220007443801</v>
       </c>
       <c r="EU7" t="n">
-        <v>0.006647755391895771</v>
+        <v>0.0006063233013264835</v>
       </c>
       <c r="EV7" t="n">
-        <v>0.01048232335597277</v>
+        <v>0.0004352413234300911</v>
       </c>
       <c r="EW7" t="n">
-        <v>0.0002744126250036061</v>
+        <v>0.00111371383536607</v>
       </c>
       <c r="EX7" t="n">
-        <v>0.003696494502946734</v>
+        <v>2.268508251290768e-05</v>
       </c>
       <c r="EY7" t="n">
-        <v>0.01019417680799961</v>
+        <v>0.001670743222348392</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0.001800275524146855</v>
+        <v>0.0002341119106858969</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.005404018331319094</v>
+        <v>0.001687566167674959</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.0003752660122700036</v>
+        <v>0.0001155156787717715</v>
       </c>
       <c r="FC7" t="n">
-        <v>0.006244713440537453</v>
+        <v>0.00064655183814466</v>
       </c>
       <c r="FD7" t="n">
-        <v>0.00400771526619792</v>
+        <v>0.0002929395996034145</v>
       </c>
       <c r="FE7" t="n">
-        <v>0.001845807302743196</v>
+        <v>0.0004238854162395</v>
       </c>
       <c r="FF7" t="n">
-        <v>0.004241891205310822</v>
+        <v>0.0003346340672578663</v>
       </c>
       <c r="FG7" t="n">
-        <v>0.002617784310132265</v>
+        <v>0.0001369201927445829</v>
       </c>
       <c r="FH7" t="n">
-        <v>0.006189047824591398</v>
+        <v>0.0007767169736325741</v>
       </c>
       <c r="FI7" t="n">
-        <v>0.00332271633669734</v>
+        <v>2.81416141660884e-05</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.00836719386279583</v>
+        <v>0.0008203597972169518</v>
       </c>
       <c r="FK7" t="n">
-        <v>0.0005870027816854417</v>
+        <v>0.0003702398098539561</v>
       </c>
       <c r="FL7" t="n">
-        <v>0.002550069708377123</v>
+        <v>4.775015986524522e-05</v>
       </c>
       <c r="FM7" t="n">
-        <v>0.0007109212456271052</v>
+        <v>0.0004603606066666543</v>
       </c>
       <c r="FN7" t="n">
-        <v>0.005642801057547331</v>
+        <v>7.214224024210125e-05</v>
       </c>
       <c r="FO7" t="n">
-        <v>0.008032780140638351</v>
+        <v>0.0005919414106756449</v>
       </c>
       <c r="FP7" t="n">
-        <v>0.004885144531726837</v>
+        <v>0.001051079481840134</v>
       </c>
       <c r="FQ7" t="n">
-        <v>0.006641808897256851</v>
+        <v>0.002002630615606904</v>
       </c>
       <c r="FR7" t="n">
-        <v>0.0003525725333020091</v>
+        <v>0.001206318149343133</v>
       </c>
       <c r="FS7" t="n">
-        <v>0.006325634196400642</v>
+        <v>0.001353730214759707</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.01723985001444817</v>
+        <v>0.001895503140985966</v>
       </c>
       <c r="FU7" t="n">
-        <v>0.004109182860702276</v>
+        <v>0.0005117234541103244</v>
       </c>
       <c r="FV7" t="n">
-        <v>0.002188890473917127</v>
+        <v>0.0003426377661526203</v>
       </c>
       <c r="FW7" t="n">
-        <v>0.001802891958504915</v>
+        <v>0.001675351290032268</v>
       </c>
       <c r="FX7" t="n">
-        <v>0.003607936669141054</v>
+        <v>0.0009737808140926063</v>
       </c>
       <c r="FY7" t="n">
-        <v>0.008860617876052856</v>
+        <v>0.0004783832118846476</v>
       </c>
       <c r="FZ7" t="n">
-        <v>0.00559689849615097</v>
+        <v>5.618456634692848e-05</v>
       </c>
       <c r="GA7" t="n">
-        <v>0.004275749437510967</v>
+        <v>0.0006915965350344777</v>
       </c>
       <c r="GB7" t="n">
-        <v>0.001058645197190344</v>
+        <v>0.001397606683894992</v>
       </c>
       <c r="GC7" t="n">
-        <v>0.006574089173227549</v>
+        <v>0.0002360641228733584</v>
       </c>
       <c r="GD7" t="n">
-        <v>0.006655857432633638</v>
+        <v>0.001004479243420064</v>
       </c>
       <c r="GE7" t="n">
-        <v>0.02125859446823597</v>
+        <v>0.001084470422938466</v>
       </c>
       <c r="GF7" t="n">
-        <v>0.000764080323278904</v>
+        <v>0.0004722190205939114</v>
       </c>
       <c r="GG7" t="n">
-        <v>0.002594939433038235</v>
+        <v>0.0004874023725278676</v>
       </c>
     </row>
     <row r="8">
@@ -4982,1140 +4982,1140 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.002639313228428364</v>
+        <v>0.02484581619501114</v>
       </c>
       <c r="B9" t="n">
-        <v>0.01151344086974859</v>
+        <v>0.3727176785469055</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001489766989834607</v>
+        <v>0.08247357606887817</v>
       </c>
       <c r="D9" t="n">
-        <v>0.004173922818154097</v>
+        <v>0.01752068288624287</v>
       </c>
       <c r="E9" t="n">
-        <v>0.00787412840873003</v>
+        <v>0.04500429332256317</v>
       </c>
       <c r="F9" t="n">
-        <v>0.003139863489195704</v>
+        <v>0.2391764521598816</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001033185631968081</v>
+        <v>0.1475727260112762</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0002527325414121151</v>
+        <v>0.1548330634832382</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001044884440489113</v>
+        <v>0.05581826344132423</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001036679488606751</v>
+        <v>0.08799341320991516</v>
       </c>
       <c r="K9" t="n">
-        <v>0.007000397890806198</v>
+        <v>0.3140363991260529</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001391205238178372</v>
+        <v>0.08739358931779861</v>
       </c>
       <c r="M9" t="n">
-        <v>0.004338071215897799</v>
+        <v>0.1378947496414185</v>
       </c>
       <c r="N9" t="n">
-        <v>0.008139782585203648</v>
+        <v>0.1877740919589996</v>
       </c>
       <c r="O9" t="n">
-        <v>0.004328078590333462</v>
+        <v>0.2592306137084961</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0009107176447287202</v>
+        <v>0.1336293518543243</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.002039219718426466</v>
+        <v>0.02019715309143066</v>
       </c>
       <c r="R9" t="n">
-        <v>0.0006983602652326226</v>
+        <v>0.1557921320199966</v>
       </c>
       <c r="S9" t="n">
-        <v>6.968369416426867e-05</v>
+        <v>0.01790151931345463</v>
       </c>
       <c r="T9" t="n">
-        <v>0.002708099549636245</v>
+        <v>0.1714048385620117</v>
       </c>
       <c r="U9" t="n">
-        <v>9.020559809869155e-05</v>
+        <v>0.004156230017542839</v>
       </c>
       <c r="V9" t="n">
-        <v>0.001563702942803502</v>
+        <v>0.06243104487657547</v>
       </c>
       <c r="W9" t="n">
-        <v>0.0003226527769584209</v>
+        <v>0.0750131756067276</v>
       </c>
       <c r="X9" t="n">
-        <v>0.001867902232334018</v>
+        <v>0.02784733474254608</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.0009506682399660349</v>
+        <v>0.00848579965531826</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.0007772999233566225</v>
+        <v>0.05269548296928406</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.0008392779272980988</v>
+        <v>0.01948794350028038</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.0003011233638972044</v>
+        <v>0.003443596884608269</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.002138509647920728</v>
+        <v>0.005102329887449741</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.0008136378601193428</v>
+        <v>0.0668502151966095</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.001571089844219387</v>
+        <v>0.06143848225474358</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.0002351025177631527</v>
+        <v>0.1134441047906876</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.0001011927233776078</v>
+        <v>0.1212907209992409</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.002077919896692038</v>
+        <v>0.01579881086945534</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.0005630288505926728</v>
+        <v>0.2293088734149933</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.000913927098736167</v>
+        <v>0.03027161955833435</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.001540953293442726</v>
+        <v>0.01817216724157333</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.00259287771768868</v>
+        <v>0.1273520141839981</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.0004502545925788581</v>
+        <v>0.003838681615889072</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.0004120174562558532</v>
+        <v>0.03177368640899658</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.0008589921635575593</v>
+        <v>0.08704948425292969</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.001611188519746065</v>
+        <v>0.04863014072179794</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.0004442390927579254</v>
+        <v>0.003160032443702221</v>
       </c>
       <c r="AR9" t="n">
-        <v>4.490560968406498e-05</v>
+        <v>0.1794017851352692</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.0008463477715849876</v>
+        <v>0.01705321110785007</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.002063438761979342</v>
+        <v>0.003118935972452164</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.01063962653279305</v>
+        <v>0.3886699080467224</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.0005809229915030301</v>
+        <v>0.0502673014998436</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.0001658430555835366</v>
+        <v>0.02347790636122227</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.0007399781607091427</v>
+        <v>0.05190067738294601</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.001851992448791862</v>
+        <v>0.2289488464593887</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.0005203303880989552</v>
+        <v>0.01679376140236855</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.001512803370133042</v>
+        <v>0.1282512545585632</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.0003795848460868001</v>
+        <v>0.03514767810702324</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.001108683994971216</v>
+        <v>0.03154115006327629</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.0008772386936470866</v>
+        <v>0.08377173542976379</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.0008303601644001901</v>
+        <v>0.1163204237818718</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.0009949725354090333</v>
+        <v>0.04205567762255669</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.005827459972351789</v>
+        <v>0.123661495745182</v>
       </c>
       <c r="BH9" t="n">
-        <v>0.0009862369624897838</v>
+        <v>0.006795608438551426</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.001386495772749186</v>
+        <v>0.05231885612010956</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.002496773609891534</v>
+        <v>0.01550507079809904</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.001017163041979074</v>
+        <v>0.005821956321597099</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.001442740787751973</v>
+        <v>0.003587291575968266</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.003082198090851307</v>
+        <v>0.03427630662918091</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.0002966086030937731</v>
+        <v>0.03103435412049294</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.003025682643055916</v>
+        <v>0.03402426093816757</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.002922867191955447</v>
+        <v>0.03622973337769508</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.0008483724668622017</v>
+        <v>0.05170061439275742</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.001042284420691431</v>
+        <v>0.09707701206207275</v>
       </c>
       <c r="BS9" t="n">
-        <v>8.196660928661004e-05</v>
+        <v>0.02016902528703213</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.000251008925260976</v>
+        <v>0.05698725953698158</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.001161071471869946</v>
+        <v>0.04016564041376114</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.005238553509116173</v>
+        <v>0.4001357555389404</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.001573254470713437</v>
+        <v>0.03530206903815269</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.0003242116945330054</v>
+        <v>0.04945309460163116</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.001996992621570826</v>
+        <v>0.08138135820627213</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.002753128064796329</v>
+        <v>0.0601213127374649</v>
       </c>
       <c r="CA9" t="n">
-        <v>0.0008411132730543613</v>
+        <v>0.06875693798065186</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.0007206775480881333</v>
+        <v>0.02523117512464523</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.0006242876988835633</v>
+        <v>0.01276249624788761</v>
       </c>
       <c r="CD9" t="n">
-        <v>0.0004689170455094427</v>
+        <v>0.03127361461520195</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.002120079239830375</v>
+        <v>0.1410210132598877</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.0002689625252969563</v>
+        <v>0.02129730768501759</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.001390237361192703</v>
+        <v>0.0112591776996851</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.000734243425540626</v>
+        <v>0.01726431399583817</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.001001684460788965</v>
+        <v>0.05063801631331444</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.0005593697424046695</v>
+        <v>0.0241816733032465</v>
       </c>
       <c r="CK9" t="n">
-        <v>2.623850741656497e-05</v>
+        <v>0.01192125584930182</v>
       </c>
       <c r="CL9" t="n">
-        <v>0.0004144265258219093</v>
+        <v>0.00670215766876936</v>
       </c>
       <c r="CM9" t="n">
-        <v>0.002240341855213046</v>
+        <v>0.03921300172805786</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.001315074856393039</v>
+        <v>0.204912856221199</v>
       </c>
       <c r="CO9" t="n">
-        <v>0.001016112393699586</v>
+        <v>0.04824753105640411</v>
       </c>
       <c r="CP9" t="n">
-        <v>0.0003990301338490099</v>
+        <v>0.08537141233682632</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0.00161234347615391</v>
+        <v>0.05882031470537186</v>
       </c>
       <c r="CR9" t="n">
-        <v>0.001072581857442856</v>
+        <v>0.04432152584195137</v>
       </c>
       <c r="CS9" t="n">
-        <v>0.0003904890327248722</v>
+        <v>0.06084779649972916</v>
       </c>
       <c r="CT9" t="n">
-        <v>0.00111719430424273</v>
+        <v>0.05651047080755234</v>
       </c>
       <c r="CU9" t="n">
-        <v>0.0001393548009218648</v>
+        <v>0.05586565285921097</v>
       </c>
       <c r="CV9" t="n">
-        <v>0.0004283422604203224</v>
+        <v>0.003909828141331673</v>
       </c>
       <c r="CW9" t="n">
-        <v>0.001284540863707662</v>
+        <v>0.1279240548610687</v>
       </c>
       <c r="CX9" t="n">
-        <v>0.0003737048828043044</v>
+        <v>0.02911795675754547</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.001981030683964491</v>
+        <v>0.002886164933443069</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.0006522369221784174</v>
+        <v>0.001946938456967473</v>
       </c>
       <c r="DA9" t="n">
-        <v>0.001407679985277355</v>
+        <v>0.05807098373770714</v>
       </c>
       <c r="DB9" t="n">
-        <v>0.0005645886994898319</v>
+        <v>0.002074026502668858</v>
       </c>
       <c r="DC9" t="n">
-        <v>0.0002424772246740758</v>
+        <v>0.01132646948099136</v>
       </c>
       <c r="DD9" t="n">
-        <v>1.165423600468785e-05</v>
+        <v>0.009128879755735397</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.00130805023945868</v>
+        <v>0.0680077075958252</v>
       </c>
       <c r="DF9" t="n">
-        <v>0.003799682017415762</v>
+        <v>0.3084760904312134</v>
       </c>
       <c r="DG9" t="n">
-        <v>0.0002724035002756864</v>
+        <v>0.1157760173082352</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.002736263908445835</v>
+        <v>0.06825584173202515</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.00346832862123847</v>
+        <v>0.07414853572845459</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0.0001625774311833084</v>
+        <v>0.200263723731041</v>
       </c>
       <c r="DK9" t="n">
-        <v>0.003735895035788417</v>
+        <v>0.03881476074457169</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.0007867474923841655</v>
+        <v>0.1672784090042114</v>
       </c>
       <c r="DM9" t="n">
-        <v>0.001620641094632447</v>
+        <v>0.1061211600899696</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.002510871971026063</v>
+        <v>0.01506297755986452</v>
       </c>
       <c r="DO9" t="n">
-        <v>0.00143972469959408</v>
+        <v>0.0579066276550293</v>
       </c>
       <c r="DP9" t="n">
-        <v>2.864653652068228e-06</v>
+        <v>0.01117652654647827</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.001748647075146437</v>
+        <v>0.0647801011800766</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.0004038444894831628</v>
+        <v>0.0581510104238987</v>
       </c>
       <c r="DS9" t="n">
-        <v>9.105881326831877e-05</v>
+        <v>0.04524699971079826</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.0001742910244502127</v>
+        <v>0.02736831083893776</v>
       </c>
       <c r="DU9" t="n">
-        <v>0.001363283954560757</v>
+        <v>0.07471367716789246</v>
       </c>
       <c r="DV9" t="n">
-        <v>0.000598323589656502</v>
+        <v>0.0004304646863602102</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.0001794332929421216</v>
+        <v>0.003336701542139053</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.001288841478526592</v>
+        <v>0.08351020514965057</v>
       </c>
       <c r="DY9" t="n">
-        <v>0.002388164401054382</v>
+        <v>0.0882994681596756</v>
       </c>
       <c r="DZ9" t="n">
-        <v>0.001108834519982338</v>
+        <v>0.05725973844528198</v>
       </c>
       <c r="EA9" t="n">
-        <v>0.002731885993853211</v>
+        <v>0.02899937517940998</v>
       </c>
       <c r="EB9" t="n">
-        <v>4.724906466435641e-05</v>
+        <v>0.03647859022021294</v>
       </c>
       <c r="EC9" t="n">
-        <v>0.0005394831532612443</v>
+        <v>0.04105919972062111</v>
       </c>
       <c r="ED9" t="n">
-        <v>0.0001281740551348776</v>
+        <v>0.04557386413216591</v>
       </c>
       <c r="EE9" t="n">
-        <v>0.0001247551408596337</v>
+        <v>0.1598495244979858</v>
       </c>
       <c r="EF9" t="n">
-        <v>0.001225195243023336</v>
+        <v>0.03136749193072319</v>
       </c>
       <c r="EG9" t="n">
-        <v>4.380149039207026e-05</v>
+        <v>0.0357067734003067</v>
       </c>
       <c r="EH9" t="n">
-        <v>0.0001054589083651081</v>
+        <v>0.03775234147906303</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.001420519547536969</v>
+        <v>0.03606785461306572</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.001090909587219357</v>
+        <v>0.01458271034061909</v>
       </c>
       <c r="EK9" t="n">
-        <v>0.0006000093417242169</v>
+        <v>0.006344256456941366</v>
       </c>
       <c r="EL9" t="n">
-        <v>0.0008548686746507883</v>
+        <v>0.0006434619426727295</v>
       </c>
       <c r="EM9" t="n">
-        <v>8.797979717201088e-06</v>
+        <v>0.04320719838142395</v>
       </c>
       <c r="EN9" t="n">
-        <v>2.207332727266476e-05</v>
+        <v>0.003903819248080254</v>
       </c>
       <c r="EO9" t="n">
-        <v>0.001710005686618388</v>
+        <v>0.01420656777918339</v>
       </c>
       <c r="EP9" t="n">
-        <v>4.375965363578871e-05</v>
+        <v>0.111302949488163</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0.0002621646272018552</v>
+        <v>0.001356017775833607</v>
       </c>
       <c r="ER9" t="n">
-        <v>0.00110101921018213</v>
+        <v>0.06132348626852036</v>
       </c>
       <c r="ES9" t="n">
-        <v>0.00070826371666044</v>
+        <v>0.1712650060653687</v>
       </c>
       <c r="ET9" t="n">
-        <v>0.003299083327874541</v>
+        <v>0.007736545987427235</v>
       </c>
       <c r="EU9" t="n">
-        <v>0.0002650083624757826</v>
+        <v>0.05550886318087578</v>
       </c>
       <c r="EV9" t="n">
-        <v>0.001894977875053883</v>
+        <v>0.06078696995973587</v>
       </c>
       <c r="EW9" t="n">
-        <v>0.0002861915272660553</v>
+        <v>0.009382469579577446</v>
       </c>
       <c r="EX9" t="n">
-        <v>0.0004662072751671076</v>
+        <v>0.02643777243793011</v>
       </c>
       <c r="EY9" t="n">
-        <v>0.001077901921235025</v>
+        <v>0.1589503735303879</v>
       </c>
       <c r="EZ9" t="n">
-        <v>8.224653720390052e-05</v>
+        <v>0.0123039735481143</v>
       </c>
       <c r="FA9" t="n">
-        <v>0.001620619092136621</v>
+        <v>0.01277958229184151</v>
       </c>
       <c r="FB9" t="n">
-        <v>0.0006752299377694726</v>
+        <v>0.01371950656175613</v>
       </c>
       <c r="FC9" t="n">
-        <v>0.001320613897405565</v>
+        <v>0.05284238234162331</v>
       </c>
       <c r="FD9" t="n">
-        <v>0.0006488896324299276</v>
+        <v>0.02174359001219273</v>
       </c>
       <c r="FE9" t="n">
-        <v>4.127334250370041e-05</v>
+        <v>0.00104330200701952</v>
       </c>
       <c r="FF9" t="n">
-        <v>0.0004599202366080135</v>
+        <v>0.01515918970108032</v>
       </c>
       <c r="FG9" t="n">
-        <v>0.00133670074865222</v>
+        <v>0.07907002419233322</v>
       </c>
       <c r="FH9" t="n">
-        <v>0.002359297126531601</v>
+        <v>0.08471851795911789</v>
       </c>
       <c r="FI9" t="n">
-        <v>0.001144909998401999</v>
+        <v>0.01905409246683121</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.0003127563395537436</v>
+        <v>0.04855398088693619</v>
       </c>
       <c r="FK9" t="n">
-        <v>0.0003748269518837333</v>
+        <v>0.02153174020349979</v>
       </c>
       <c r="FL9" t="n">
-        <v>2.283795038238168e-05</v>
+        <v>0.1674397885799408</v>
       </c>
       <c r="FM9" t="n">
-        <v>3.586948150768876e-05</v>
+        <v>0.03047825954854488</v>
       </c>
       <c r="FN9" t="n">
-        <v>0.0005050675827078521</v>
+        <v>0.1945691257715225</v>
       </c>
       <c r="FO9" t="n">
-        <v>0.0009716622298583388</v>
+        <v>0.136879175901413</v>
       </c>
       <c r="FP9" t="n">
-        <v>0.00161036173813045</v>
+        <v>0.06138462945818901</v>
       </c>
       <c r="FQ9" t="n">
-        <v>0.001320699229836464</v>
+        <v>0.0596938244998455</v>
       </c>
       <c r="FR9" t="n">
-        <v>0.001575657515786588</v>
+        <v>0.09293794631958008</v>
       </c>
       <c r="FS9" t="n">
-        <v>0.001913293497636914</v>
+        <v>0.08035679906606674</v>
       </c>
       <c r="FT9" t="n">
-        <v>0.005209374241530895</v>
+        <v>0.1534886211156845</v>
       </c>
       <c r="FU9" t="n">
-        <v>0.0006650754367001355</v>
+        <v>0.06086006388068199</v>
       </c>
       <c r="FV9" t="n">
-        <v>0.0003039574949070811</v>
+        <v>0.008922789245843887</v>
       </c>
       <c r="FW9" t="n">
-        <v>0.001838687108829618</v>
+        <v>0.1967706829309464</v>
       </c>
       <c r="FX9" t="n">
-        <v>0.0002206550416303799</v>
+        <v>0.01189305260777473</v>
       </c>
       <c r="FY9" t="n">
-        <v>0.0005741876666434109</v>
+        <v>0.04733229428529739</v>
       </c>
       <c r="FZ9" t="n">
-        <v>0.002204882213845849</v>
+        <v>0.06609083712100983</v>
       </c>
       <c r="GA9" t="n">
-        <v>0.0006174585432745516</v>
+        <v>0.05721795931458473</v>
       </c>
       <c r="GB9" t="n">
-        <v>0.001650236314162612</v>
+        <v>0.01244758162647486</v>
       </c>
       <c r="GC9" t="n">
-        <v>0.0001514619798399508</v>
+        <v>0.07833752036094666</v>
       </c>
       <c r="GD9" t="n">
-        <v>0.001425002468749881</v>
+        <v>0.1161306202411652</v>
       </c>
       <c r="GE9" t="n">
-        <v>0.002387015148997307</v>
+        <v>0.02808540314435959</v>
       </c>
       <c r="GF9" t="n">
-        <v>0.001949380966834724</v>
+        <v>0.08655516803264618</v>
       </c>
       <c r="GG9" t="n">
-        <v>4.746866034111008e-05</v>
+        <v>0.06756529957056046</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.0003398451372049749</v>
+        <v>0.0008343125227838755</v>
       </c>
       <c r="B10" t="n">
-        <v>0.007682823110371828</v>
+        <v>0.005329490639269352</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0003645622928161174</v>
+        <v>0.0006776537047699094</v>
       </c>
       <c r="D10" t="n">
-        <v>0.004258545581251383</v>
+        <v>0.004059040918946266</v>
       </c>
       <c r="E10" t="n">
-        <v>0.001432075747288764</v>
+        <v>0.0006332873599603772</v>
       </c>
       <c r="F10" t="n">
-        <v>0.001157523016445339</v>
+        <v>0.002924266969785094</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0003656451299320906</v>
+        <v>0.002040313323959708</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0006668134592473507</v>
+        <v>0.001617699163034558</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0009229629067704082</v>
+        <v>0.0003986777737736702</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0008361571235582232</v>
+        <v>0.0009025064064189792</v>
       </c>
       <c r="K10" t="n">
-        <v>0.005081954877823591</v>
+        <v>0.005145784467458725</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0006036170525476336</v>
+        <v>0.001480408711358905</v>
       </c>
       <c r="M10" t="n">
-        <v>0.004334086552262306</v>
+        <v>0.00548894377425313</v>
       </c>
       <c r="N10" t="n">
-        <v>0.00288806390017271</v>
+        <v>0.001934952568262815</v>
       </c>
       <c r="O10" t="n">
-        <v>0.002242628484964371</v>
+        <v>0.002553972182795405</v>
       </c>
       <c r="P10" t="n">
-        <v>0.0003317757800687104</v>
+        <v>0.002438497263938189</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.0004270879144314677</v>
+        <v>0.0003285376005806029</v>
       </c>
       <c r="R10" t="n">
-        <v>0.0001994873309740797</v>
+        <v>0.0008195738773792982</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0002887157897930592</v>
+        <v>0.0005408417200669646</v>
       </c>
       <c r="T10" t="n">
-        <v>0.001198558718897402</v>
+        <v>0.000279369589406997</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0003586836392059922</v>
+        <v>0.0002977381809614599</v>
       </c>
       <c r="V10" t="n">
-        <v>0.0009354843059554696</v>
+        <v>0.0002426987193757668</v>
       </c>
       <c r="W10" t="n">
-        <v>0.0004050759016536176</v>
+        <v>0.0006467407802119851</v>
       </c>
       <c r="X10" t="n">
-        <v>0.000903816195204854</v>
+        <v>0.001430309261195362</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.0007835617288947105</v>
+        <v>0.0002781168150249869</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.0002646597858984023</v>
+        <v>0.0008960642735473812</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.0002187519130529836</v>
+        <v>0.0007778757717460394</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.0009302382823079824</v>
+        <v>0.000486998149426654</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.001104541006498039</v>
+        <v>0.0004338865401223302</v>
       </c>
       <c r="AD10" t="n">
-        <v>8.738502947380766e-05</v>
+        <v>0.001043088035658002</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.0003559732576832175</v>
+        <v>0.0002364579995628446</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.0007634946377947927</v>
+        <v>0.0005471371114253998</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.0004040880012325943</v>
+        <v>0.001974506536498666</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.0001256185641977936</v>
+        <v>8.696012082509696e-05</v>
       </c>
       <c r="AI10" t="n">
-        <v>6.86635758029297e-05</v>
+        <v>0.001067931647412479</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.0002690330147743225</v>
+        <v>0.0006420027348212898</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.000404006423195824</v>
+        <v>0.0005800347425974905</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.0006483487668447196</v>
+        <v>0.001722758985124528</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.0004203225835226476</v>
+        <v>0.0009931337554007769</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.0003852804657071829</v>
+        <v>0.00100090354681015</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.0009293300099670887</v>
+        <v>0.000362645136192441</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.0009431001381017268</v>
+        <v>0.0009506539208814502</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.000337213248712942</v>
+        <v>0.0009088772931136191</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.0006217930349521339</v>
+        <v>0.0002421462850179523</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.0002320444182259962</v>
+        <v>0.0004073940508533269</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.0008303722133859992</v>
+        <v>0.0003419909917283803</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.00620197644457221</v>
+        <v>0.002940624719485641</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.000391313573345542</v>
+        <v>0.0009371396154165268</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.0007013007416389883</v>
+        <v>0.001895061694085598</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.001038481597788632</v>
+        <v>0.003408687422052026</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.0008914402569644153</v>
+        <v>0.002051799558103085</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.0002250958204967901</v>
+        <v>0.0002132332010660321</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.0002406058047199622</v>
+        <v>0.0001100522640626878</v>
       </c>
       <c r="BB10" t="n">
-        <v>0.000253468519076705</v>
+        <v>0.0003246779670007527</v>
       </c>
       <c r="BC10" t="n">
-        <v>0.0001552458415972069</v>
+        <v>0.0006518904119729996</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.001368708093650639</v>
+        <v>0.0001241945428773761</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.001284704427234828</v>
+        <v>0.0007676348323002458</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.0006820668932050467</v>
+        <v>0.0003891921951435506</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.00235876627266407</v>
+        <v>0.001177894184365869</v>
       </c>
       <c r="BH10" t="n">
-        <v>0.001784836407750845</v>
+        <v>0.0007049805717542768</v>
       </c>
       <c r="BI10" t="n">
-        <v>0.0009361437987536192</v>
+        <v>0.0009082681499421597</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.0004186398000456393</v>
+        <v>0.0008836995111778378</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.0002682491613086313</v>
+        <v>0.0008485292783007026</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.001361937262117863</v>
+        <v>0.0003427833144087344</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.001747072557918727</v>
+        <v>0.0002406782296020538</v>
       </c>
       <c r="BN10" t="n">
-        <v>0.0005739213665947318</v>
+        <v>0.0001271194778382778</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.0002878897939808667</v>
+        <v>0.0008876704378053546</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.001231777248904109</v>
+        <v>6.518860755022615e-05</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0.0009481868473812938</v>
+        <v>4.082933810423128e-05</v>
       </c>
       <c r="BR10" t="n">
-        <v>7.591358735226095e-05</v>
+        <v>0.0003004364261869341</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.0002878014347516</v>
+        <v>0.0004458330222405493</v>
       </c>
       <c r="BT10" t="n">
-        <v>0.0006530745886266232</v>
+        <v>0.0002088713372359052</v>
       </c>
       <c r="BU10" t="n">
-        <v>0.0007144077681005001</v>
+        <v>0.0002976083487737924</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.003086691722273827</v>
+        <v>0.002292363438755274</v>
       </c>
       <c r="BW10" t="n">
-        <v>0.0002033903874689713</v>
+        <v>0.0005644972552545369</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.0005953079089522362</v>
+        <v>0.002842583460733294</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.0003304595011286438</v>
+        <v>0.0006673529278486967</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0.002023548586294055</v>
+        <v>0.00145224982406944</v>
       </c>
       <c r="CA10" t="n">
-        <v>0.0001538613287266344</v>
+        <v>0.0002579216379672289</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.0002411735040368512</v>
+        <v>0.000176207089680247</v>
       </c>
       <c r="CC10" t="n">
-        <v>0.0002986190083902329</v>
+        <v>0.0006792821804992855</v>
       </c>
       <c r="CD10" t="n">
-        <v>0.0004928509588353336</v>
+        <v>4.484632154344581e-05</v>
       </c>
       <c r="CE10" t="n">
-        <v>0.001242543570697308</v>
+        <v>0.001689126715064049</v>
       </c>
       <c r="CF10" t="n">
-        <v>0.000369179411791265</v>
+        <v>7.448787800967693e-05</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.0003953726263716817</v>
+        <v>0.001612346852198243</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.0002424397971481085</v>
+        <v>9.088090155273676e-05</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.0004558716609608382</v>
+        <v>0.0005574330571107566</v>
       </c>
       <c r="CJ10" t="n">
-        <v>0.0003013404202647507</v>
+        <v>0.0001236506359418854</v>
       </c>
       <c r="CK10" t="n">
-        <v>2.590475196484476e-05</v>
+        <v>0.0002982258738484234</v>
       </c>
       <c r="CL10" t="n">
-        <v>0.0001624914002604783</v>
+        <v>9.221843356499448e-06</v>
       </c>
       <c r="CM10" t="n">
-        <v>0.001030611456371844</v>
+        <v>0.0002034998615272343</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.001113432692363858</v>
+        <v>0.0009617027826607227</v>
       </c>
       <c r="CO10" t="n">
-        <v>0.0005718095926567912</v>
+        <v>0.001918485737405717</v>
       </c>
       <c r="CP10" t="n">
-        <v>0.001700677210465074</v>
+        <v>0.002533922903239727</v>
       </c>
       <c r="CQ10" t="n">
-        <v>0.001238953089341521</v>
+        <v>0.0004687591572292149</v>
       </c>
       <c r="CR10" t="n">
-        <v>0.0009504096815362573</v>
+        <v>0.0006741444813087583</v>
       </c>
       <c r="CS10" t="n">
-        <v>0.0004466317186597735</v>
+        <v>0.0003661763039417565</v>
       </c>
       <c r="CT10" t="n">
-        <v>0.00137670524418354</v>
+        <v>0.0004582783731166273</v>
       </c>
       <c r="CU10" t="n">
-        <v>1.368153971270658e-05</v>
+        <v>0.0004204240685794502</v>
       </c>
       <c r="CV10" t="n">
-        <v>0.0004733697278425097</v>
+        <v>1.724449975881726e-05</v>
       </c>
       <c r="CW10" t="n">
-        <v>0.0009247626876458526</v>
+        <v>0.001613049069419503</v>
       </c>
       <c r="CX10" t="n">
-        <v>0.0004767855862155557</v>
+        <v>0.0002754088200163096</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.0007645433652214706</v>
+        <v>0.00166908698156476</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.0001913070300361142</v>
+        <v>0.000336750119458884</v>
       </c>
       <c r="DA10" t="n">
-        <v>0.0004408362146932632</v>
+        <v>0.0006159598706290126</v>
       </c>
       <c r="DB10" t="n">
-        <v>0.0002652405528351665</v>
+        <v>0.000239000961300917</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.955309562617913e-05</v>
+        <v>0.0002373677998548374</v>
       </c>
       <c r="DD10" t="n">
-        <v>8.058019011514261e-05</v>
+        <v>0.0001193565840367228</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.0003884175966959447</v>
+        <v>0.000236247040447779</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.0009753520716913044</v>
+        <v>0.00170466210693121</v>
       </c>
       <c r="DG10" t="n">
-        <v>0.0003988920943811536</v>
+        <v>0.0004097055934835225</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.001233040005899966</v>
+        <v>0.001492451992817223</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.0004634656943380833</v>
+        <v>0.0002275671140523627</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0.0004674597876146436</v>
+        <v>0.00309859705157578</v>
       </c>
       <c r="DK10" t="n">
-        <v>0.0005301583441905677</v>
+        <v>0.0002631616371218115</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.0002727916580624878</v>
+        <v>0.002700154669582844</v>
       </c>
       <c r="DM10" t="n">
-        <v>0.0002517619868740439</v>
+        <v>0.001287919352762401</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.001130905118770897</v>
+        <v>0.0002291289856657386</v>
       </c>
       <c r="DO10" t="n">
-        <v>0.0004252180806361139</v>
+        <v>0.0008709560497663915</v>
       </c>
       <c r="DP10" t="n">
-        <v>0.0006906245835125446</v>
+        <v>0.0001468268455937505</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0.0002703723730519414</v>
+        <v>0.0004351814277470112</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.0004227625904604793</v>
+        <v>5.052534106653184e-05</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.0007887901738286018</v>
+        <v>0.0004799923917744309</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.0002016067883232608</v>
+        <v>0.0004387410590425134</v>
       </c>
       <c r="DU10" t="n">
-        <v>1.479670027038082e-05</v>
+        <v>0.001159344566985965</v>
       </c>
       <c r="DV10" t="n">
-        <v>5.328846600605175e-05</v>
+        <v>0.002235930878669024</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.0003515156568028033</v>
+        <v>0.0001220138656208292</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.0001462053915020078</v>
+        <v>0.0001456086174584925</v>
       </c>
       <c r="DY10" t="n">
-        <v>0.0006648288108408451</v>
+        <v>0.0009338997770100832</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0.0005076329689472914</v>
+        <v>0.0006569449324160814</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.001072462764568627</v>
+        <v>7.704236486461014e-05</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.0007534337346442044</v>
+        <v>0.001528740860521793</v>
       </c>
       <c r="EC10" t="n">
-        <v>8.759109186939895e-05</v>
+        <v>8.676667494000867e-05</v>
       </c>
       <c r="ED10" t="n">
-        <v>8.024074486456811e-05</v>
+        <v>0.002319466089829803</v>
       </c>
       <c r="EE10" t="n">
-        <v>0.0001465102250222117</v>
+        <v>0.002234621671959758</v>
       </c>
       <c r="EF10" t="n">
-        <v>0.0003315541543997824</v>
+        <v>0.0007771508535370231</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.0005707239033654332</v>
+        <v>0.001176396734081209</v>
       </c>
       <c r="EH10" t="n">
-        <v>2.932961615442764e-05</v>
+        <v>0.000936415686737746</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.0005125158932060003</v>
+        <v>0.00150701857637614</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.0004258229164406657</v>
+        <v>0.0002642384497448802</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.0002511290367692709</v>
+        <v>0.0004729237989522517</v>
       </c>
       <c r="EL10" t="n">
-        <v>0.0002498066751286387</v>
+        <v>9.33155242819339e-05</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.0003177192993462086</v>
+        <v>0.0001901883661048487</v>
       </c>
       <c r="EN10" t="n">
-        <v>7.745633774902672e-05</v>
+        <v>0.0002686772495508194</v>
       </c>
       <c r="EO10" t="n">
-        <v>0.0006081609753891826</v>
+        <v>0.0005439898814074695</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.0008095783996395767</v>
+        <v>0.001755659352056682</v>
       </c>
       <c r="EQ10" t="n">
-        <v>4.307854396756738e-05</v>
+        <v>3.733222547452897e-05</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.0007837355369701982</v>
+        <v>0.001393549609929323</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.0004263879091013223</v>
+        <v>0.0002370304428040981</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.00204404816031456</v>
+        <v>0.0002950011112261564</v>
       </c>
       <c r="EU10" t="n">
-        <v>0.0004662984283640981</v>
+        <v>0.0003927953075617552</v>
       </c>
       <c r="EV10" t="n">
-        <v>0.0002437482762616128</v>
+        <v>0.0008644339977763593</v>
       </c>
       <c r="EW10" t="n">
-        <v>0.000213059174711816</v>
+        <v>0.001151424599811435</v>
       </c>
       <c r="EX10" t="n">
-        <v>0.0003112283884547651</v>
+        <v>8.794335008133203e-05</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.0009458811255171895</v>
+        <v>0.001814056653529406</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0.0001992152974708006</v>
+        <v>0.0001246637111762539</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.0005727691459469497</v>
+        <v>0.001847006380558014</v>
       </c>
       <c r="FB10" t="n">
-        <v>3.333209315314889e-05</v>
+        <v>4.551544407149777e-06</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.000630558468401432</v>
+        <v>0.0006276432541199028</v>
       </c>
       <c r="FD10" t="n">
-        <v>0.0003279831144027412</v>
+        <v>0.0003004082827828825</v>
       </c>
       <c r="FE10" t="n">
-        <v>3.69184635928832e-05</v>
+        <v>0.0003993493737652898</v>
       </c>
       <c r="FF10" t="n">
-        <v>0.0001520237274235114</v>
+        <v>0.0003393095976207405</v>
       </c>
       <c r="FG10" t="n">
-        <v>0.000304623827105388</v>
+        <v>2.395556657575071e-05</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.0002726053935475647</v>
+        <v>0.0009409707854501903</v>
       </c>
       <c r="FI10" t="n">
-        <v>5.950561535428278e-05</v>
+        <v>0.0001064181778929196</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.0007074729073792696</v>
+        <v>0.0009122511255554855</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.0003782735439017415</v>
+        <v>0.0003162346838507801</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.0004841452464461327</v>
+        <v>0.0002175913541577756</v>
       </c>
       <c r="FM10" t="n">
-        <v>0.000251195568125695</v>
+        <v>0.0003437174600549042</v>
       </c>
       <c r="FN10" t="n">
-        <v>0.0002428444277029485</v>
+        <v>6.982691411394626e-05</v>
       </c>
       <c r="FO10" t="n">
-        <v>0.0004797662841156125</v>
+        <v>0.0001674522936809808</v>
       </c>
       <c r="FP10" t="n">
-        <v>0.0003534687566570938</v>
+        <v>0.0005628904909826815</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0.0002557676925789565</v>
+        <v>0.001962607726454735</v>
       </c>
       <c r="FR10" t="n">
-        <v>3.827324690064415e-05</v>
+        <v>0.001265374012291431</v>
       </c>
       <c r="FS10" t="n">
-        <v>0.001202581450343132</v>
+        <v>0.001680399291217327</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.0009054509573616087</v>
+        <v>0.001903607975691557</v>
       </c>
       <c r="FU10" t="n">
-        <v>0.0001554528280394152</v>
+        <v>0.0004909447743557394</v>
       </c>
       <c r="FV10" t="n">
-        <v>0.0001943999959621578</v>
+        <v>0.0002969639608636498</v>
       </c>
       <c r="FW10" t="n">
-        <v>0.0001740846782922745</v>
+        <v>0.001927346223965287</v>
       </c>
       <c r="FX10" t="n">
-        <v>0.0005041386466473341</v>
+        <v>0.0006096020224504173</v>
       </c>
       <c r="FY10" t="n">
-        <v>0.0007976675988174975</v>
+        <v>0.0008492953493259847</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.0007186910952441394</v>
+        <v>0.000386427971534431</v>
       </c>
       <c r="GA10" t="n">
-        <v>4.474377783481032e-05</v>
+        <v>0.0005151961231604218</v>
       </c>
       <c r="GB10" t="n">
-        <v>0.0002350834110984579</v>
+        <v>0.001572426408529282</v>
       </c>
       <c r="GC10" t="n">
-        <v>0.0001772811228875071</v>
+        <v>0.0002319648046977818</v>
       </c>
       <c r="GD10" t="n">
-        <v>0.0009153109276667237</v>
+        <v>0.001039141556248069</v>
       </c>
       <c r="GE10" t="n">
-        <v>0.001439720625057817</v>
+        <v>0.0007766184280626476</v>
       </c>
       <c r="GF10" t="n">
-        <v>4.226402961649001e-05</v>
+        <v>0.000836540013551712</v>
       </c>
       <c r="GG10" t="n">
-        <v>0.0001380805770168081</v>
+        <v>0.0006013690726831555</v>
       </c>
     </row>
     <row r="11">
@@ -6689,2278 +6689,2278 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1.949356231989441e-09</v>
+        <v>8.513681315491795e-09</v>
       </c>
       <c r="B12" t="n">
-        <v>6.791522011440065e-09</v>
+        <v>4.546641463321066e-08</v>
       </c>
       <c r="C12" t="n">
-        <v>4.767301553521008e-10</v>
+        <v>3.968887440919389e-09</v>
       </c>
       <c r="D12" t="n">
-        <v>1.312607622594442e-08</v>
+        <v>1.702301766215442e-08</v>
       </c>
       <c r="E12" t="n">
-        <v>1.20728738117748e-09</v>
+        <v>3.99189659106014e-09</v>
       </c>
       <c r="F12" t="n">
-        <v>2.931345999268586e-10</v>
+        <v>2.54480525541112e-08</v>
       </c>
       <c r="G12" t="n">
-        <v>9.02450669748589e-10</v>
+        <v>7.424977077619133e-09</v>
       </c>
       <c r="H12" t="n">
-        <v>4.84286166724246e-10</v>
+        <v>1.163160057160439e-08</v>
       </c>
       <c r="I12" t="n">
-        <v>3.787005709021685e-10</v>
+        <v>3.506169354849931e-09</v>
       </c>
       <c r="J12" t="n">
-        <v>3.31163918509958e-09</v>
+        <v>4.581883761289873e-09</v>
       </c>
       <c r="K12" t="n">
-        <v>3.956273086913598e-09</v>
+        <v>4.879309045691116e-08</v>
       </c>
       <c r="L12" t="n">
-        <v>2.892575068358383e-10</v>
+        <v>1.427625573313662e-08</v>
       </c>
       <c r="M12" t="n">
-        <v>7.022121550903648e-09</v>
+        <v>3.198379872060286e-08</v>
       </c>
       <c r="N12" t="n">
-        <v>2.674234833577316e-09</v>
+        <v>2.199740478658896e-08</v>
       </c>
       <c r="O12" t="n">
-        <v>3.329950759578537e-09</v>
+        <v>3.274964655020085e-08</v>
       </c>
       <c r="P12" t="n">
-        <v>2.185362557582948e-09</v>
+        <v>2.220364114791096e-09</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.516277935489143e-09</v>
+        <v>2.543544486144356e-09</v>
       </c>
       <c r="R12" t="n">
-        <v>1.827567819301379e-10</v>
+        <v>6.512850703188633e-09</v>
       </c>
       <c r="S12" t="n">
-        <v>4.709210799092034e-10</v>
+        <v>4.12310269259919e-10</v>
       </c>
       <c r="T12" t="n">
-        <v>1.084835665743356e-09</v>
+        <v>6.443094502373015e-09</v>
       </c>
       <c r="U12" t="n">
-        <v>8.577450971714029e-10</v>
+        <v>1.457970633111927e-08</v>
       </c>
       <c r="V12" t="n">
-        <v>9.115038723805924e-10</v>
+        <v>1.85990411960546e-09</v>
       </c>
       <c r="W12" t="n">
-        <v>1.810514183020473e-09</v>
+        <v>6.397868013152674e-09</v>
       </c>
       <c r="X12" t="n">
-        <v>8.181496036208102e-10</v>
+        <v>7.194370876817402e-09</v>
       </c>
       <c r="Y12" t="n">
-        <v>4.305538148230426e-09</v>
+        <v>1.531408777566412e-08</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.36177363724488e-10</v>
+        <v>7.454904249470928e-09</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.787293646415833e-09</v>
+        <v>9.493189567777449e-10</v>
       </c>
       <c r="AB12" t="n">
-        <v>4.922144913876991e-10</v>
+        <v>2.738943516433778e-10</v>
       </c>
       <c r="AC12" t="n">
-        <v>5.567720728905101e-10</v>
+        <v>9.316686089277937e-09</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.306547647850209e-10</v>
+        <v>3.632736333969433e-10</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.608657873575225e-09</v>
+        <v>1.723362075267687e-08</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.287150246971237e-09</v>
+        <v>7.636032250957214e-09</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.460023768551366e-09</v>
+        <v>2.278488508977716e-08</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.049491049620599e-09</v>
+        <v>4.256754060349976e-09</v>
       </c>
       <c r="AI12" t="n">
-        <v>7.57585993937937e-10</v>
+        <v>1.552695039208629e-08</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.510099684187693e-10</v>
+        <v>1.988762265980881e-09</v>
       </c>
       <c r="AK12" t="n">
-        <v>9.020343916255058e-10</v>
+        <v>1.63601332481278e-09</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.100315949464914e-09</v>
+        <v>8.826473774092847e-09</v>
       </c>
       <c r="AM12" t="n">
-        <v>4.96897412105568e-10</v>
+        <v>1.465923205046238e-08</v>
       </c>
       <c r="AN12" t="n">
-        <v>7.537919732847342e-10</v>
+        <v>8.593809219803461e-09</v>
       </c>
       <c r="AO12" t="n">
-        <v>6.466611690569835e-10</v>
+        <v>1.579849584487647e-09</v>
       </c>
       <c r="AP12" t="n">
-        <v>7.539153190627701e-10</v>
+        <v>4.506957029803971e-09</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.609893218734726e-09</v>
+        <v>7.398055501539602e-09</v>
       </c>
       <c r="AR12" t="n">
-        <v>6.882308611899646e-10</v>
+        <v>2.045955183049841e-09</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.168964813835771e-09</v>
+        <v>5.488649534868273e-10</v>
       </c>
       <c r="AT12" t="n">
-        <v>8.542097584829378e-11</v>
+        <v>1.004576422047876e-09</v>
       </c>
       <c r="AU12" t="n">
-        <v>3.707211870818128e-09</v>
+        <v>3.364276679462819e-08</v>
       </c>
       <c r="AV12" t="n">
-        <v>4.695776545382557e-10</v>
+        <v>2.176967761613469e-08</v>
       </c>
       <c r="AW12" t="n">
-        <v>5.595603980168562e-09</v>
+        <v>3.432324646723828e-09</v>
       </c>
       <c r="AX12" t="n">
-        <v>2.566833690043069e-10</v>
+        <v>4.119845442573933e-08</v>
       </c>
       <c r="AY12" t="n">
-        <v>8.989588518026892e-10</v>
+        <v>3.099385992300085e-08</v>
       </c>
       <c r="AZ12" t="n">
-        <v>6.392039120228787e-10</v>
+        <v>9.198409811617125e-10</v>
       </c>
       <c r="BA12" t="n">
-        <v>5.992654150688281e-10</v>
+        <v>5.407069014751187e-09</v>
       </c>
       <c r="BB12" t="n">
-        <v>2.516526764750893e-09</v>
+        <v>2.452416048015493e-11</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.142385297470128e-09</v>
+        <v>6.144958319964644e-09</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.568237761873092e-10</v>
+        <v>1.930737170141583e-08</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.246015624012387e-09</v>
+        <v>3.251344082855212e-09</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.139214611534101e-09</v>
+        <v>1.502835189626239e-09</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.218508932116947e-09</v>
+        <v>3.883514310132341e-08</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.765522834825902e-10</v>
+        <v>2.610502480848709e-09</v>
       </c>
       <c r="BI12" t="n">
-        <v>1.802121785132726e-09</v>
+        <v>2.294046286266394e-09</v>
       </c>
       <c r="BJ12" t="n">
-        <v>5.114559886720826e-09</v>
+        <v>1.971359786523408e-08</v>
       </c>
       <c r="BK12" t="n">
-        <v>1.570657215399507e-10</v>
+        <v>3.397861103593414e-09</v>
       </c>
       <c r="BL12" t="n">
-        <v>5.355334509182796e-10</v>
+        <v>5.398757552121936e-10</v>
       </c>
       <c r="BM12" t="n">
-        <v>3.351353916603017e-10</v>
+        <v>3.999208963989531e-09</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.433538288075908e-09</v>
+        <v>7.901919119035483e-09</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.132037352746806e-09</v>
+        <v>3.098956646852002e-09</v>
       </c>
       <c r="BP12" t="n">
-        <v>1.011807526651864e-09</v>
+        <v>1.294673879215225e-08</v>
       </c>
       <c r="BQ12" t="n">
-        <v>7.886216124575185e-10</v>
+        <v>1.748683420288444e-10</v>
       </c>
       <c r="BR12" t="n">
-        <v>7.221327424922208e-10</v>
+        <v>3.423590522189102e-09</v>
       </c>
       <c r="BS12" t="n">
-        <v>1.486686329599252e-10</v>
+        <v>7.573840221652972e-09</v>
       </c>
       <c r="BT12" t="n">
-        <v>6.938855046101366e-11</v>
+        <v>2.376411956106494e-09</v>
       </c>
       <c r="BU12" t="n">
-        <v>2.851838210027324e-10</v>
+        <v>2.342740668126453e-09</v>
       </c>
       <c r="BV12" t="n">
-        <v>2.044154401303899e-09</v>
+        <v>1.555345363613014e-08</v>
       </c>
       <c r="BW12" t="n">
-        <v>8.721945388145969e-10</v>
+        <v>1.577059904889211e-08</v>
       </c>
       <c r="BX12" t="n">
-        <v>2.301582924246759e-09</v>
+        <v>4.282414423073533e-09</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.57919599619305e-09</v>
+        <v>2.93884738766792e-09</v>
       </c>
       <c r="BZ12" t="n">
-        <v>4.254712970830354e-10</v>
+        <v>1.436338248339553e-08</v>
       </c>
       <c r="CA12" t="n">
-        <v>2.074823424180749e-09</v>
+        <v>1.341523070408357e-08</v>
       </c>
       <c r="CB12" t="n">
-        <v>9.526490707401081e-10</v>
+        <v>1.088389711689786e-09</v>
       </c>
       <c r="CC12" t="n">
-        <v>1.960963613711897e-09</v>
+        <v>2.768569373756691e-09</v>
       </c>
       <c r="CD12" t="n">
-        <v>2.438420576567069e-10</v>
+        <v>3.335604292775685e-10</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.222284384816419e-09</v>
+        <v>1.488760581480619e-08</v>
       </c>
       <c r="CF12" t="n">
-        <v>1.329848564601832e-09</v>
+        <v>2.160262857486828e-09</v>
       </c>
       <c r="CG12" t="n">
-        <v>1.295059948169808e-09</v>
+        <v>5.741669806269556e-09</v>
       </c>
       <c r="CH12" t="n">
-        <v>7.144858038543589e-10</v>
+        <v>6.077040204388595e-09</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.153553710886435e-10</v>
+        <v>6.447108624740849e-09</v>
       </c>
       <c r="CJ12" t="n">
-        <v>8.522372252350863e-10</v>
+        <v>2.939524179623731e-09</v>
       </c>
       <c r="CK12" t="n">
-        <v>5.392030155704219e-10</v>
+        <v>1.352621237238338e-09</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.361474155636699e-09</v>
+        <v>1.012065320438182e-09</v>
       </c>
       <c r="CM12" t="n">
-        <v>1.210858635580792e-09</v>
+        <v>1.807935845477004e-08</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.475630284630824e-09</v>
+        <v>2.469960058704146e-08</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.049480363723987e-10</v>
+        <v>2.762793016586329e-08</v>
       </c>
       <c r="CP12" t="n">
-        <v>3.149337457486467e-09</v>
+        <v>4.094388383890646e-09</v>
       </c>
       <c r="CQ12" t="n">
-        <v>1.527853621396957e-09</v>
+        <v>1.135953908715237e-08</v>
       </c>
       <c r="CR12" t="n">
-        <v>9.152862356920366e-10</v>
+        <v>9.250396892923618e-09</v>
       </c>
       <c r="CS12" t="n">
-        <v>1.610078181890628e-09</v>
+        <v>1.061476240238335e-08</v>
       </c>
       <c r="CT12" t="n">
-        <v>4.230755745737724e-09</v>
+        <v>3.959883976278888e-09</v>
       </c>
       <c r="CU12" t="n">
-        <v>6.769036442477727e-10</v>
+        <v>2.958501887917464e-09</v>
       </c>
       <c r="CV12" t="n">
-        <v>3.20201254400132e-10</v>
+        <v>6.482294145904177e-10</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.127033799619426e-09</v>
+        <v>1.31071580256048e-08</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.107115954468441e-09</v>
+        <v>5.873338482231816e-10</v>
       </c>
       <c r="CY12" t="n">
-        <v>2.26420215909684e-09</v>
+        <v>7.096062404343684e-09</v>
       </c>
       <c r="CZ12" t="n">
-        <v>9.482244989200694e-10</v>
+        <v>7.79275666218382e-09</v>
       </c>
       <c r="DA12" t="n">
-        <v>3.069797471777491e-10</v>
+        <v>6.380921124815586e-09</v>
       </c>
       <c r="DB12" t="n">
-        <v>7.937080992448386e-10</v>
+        <v>4.115158880324543e-09</v>
       </c>
       <c r="DC12" t="n">
-        <v>6.925712781047366e-10</v>
+        <v>1.432536755885394e-09</v>
       </c>
       <c r="DD12" t="n">
-        <v>1.022580908838222e-09</v>
+        <v>4.848679791003008e-11</v>
       </c>
       <c r="DE12" t="n">
-        <v>1.207331679076162e-09</v>
+        <v>4.604607806157901e-09</v>
       </c>
       <c r="DF12" t="n">
-        <v>8.402268880658426e-10</v>
+        <v>2.218475625426208e-09</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.688444578069493e-09</v>
+        <v>1.755450895757349e-09</v>
       </c>
       <c r="DH12" t="n">
-        <v>9.643161824612889e-09</v>
+        <v>5.857601514946964e-09</v>
       </c>
       <c r="DI12" t="n">
-        <v>3.63928975843919e-09</v>
+        <v>2.113285768601258e-09</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.174073143734745e-10</v>
+        <v>1.370921509646905e-08</v>
       </c>
       <c r="DK12" t="n">
-        <v>2.026192769122304e-09</v>
+        <v>2.937526222268616e-09</v>
       </c>
       <c r="DL12" t="n">
-        <v>5.073284459200522e-09</v>
+        <v>1.598595389395996e-08</v>
       </c>
       <c r="DM12" t="n">
-        <v>5.851209516904987e-10</v>
+        <v>2.031649071199126e-09</v>
       </c>
       <c r="DN12" t="n">
-        <v>8.300785059311977e-11</v>
+        <v>4.832327427095606e-09</v>
       </c>
       <c r="DO12" t="n">
-        <v>4.051187163511827e-10</v>
+        <v>9.152767432851761e-09</v>
       </c>
       <c r="DP12" t="n">
-        <v>2.106786300970498e-09</v>
+        <v>9.22900644795277e-10</v>
       </c>
       <c r="DQ12" t="n">
-        <v>8.092748138288641e-10</v>
+        <v>4.730796199226006e-09</v>
       </c>
       <c r="DR12" t="n">
-        <v>1.530101600977218e-09</v>
+        <v>3.045091068187844e-09</v>
       </c>
       <c r="DS12" t="n">
-        <v>1.504510627192701e-09</v>
+        <v>2.512009267263693e-09</v>
       </c>
       <c r="DT12" t="n">
-        <v>3.938074311093942e-10</v>
+        <v>1.224566048563247e-08</v>
       </c>
       <c r="DU12" t="n">
-        <v>2.074340421653886e-10</v>
+        <v>2.095460915896297e-09</v>
       </c>
       <c r="DV12" t="n">
-        <v>2.237646512526226e-09</v>
+        <v>2.138673460549967e-09</v>
       </c>
       <c r="DW12" t="n">
-        <v>4.87518803105047e-10</v>
+        <v>2.135810556191942e-10</v>
       </c>
       <c r="DX12" t="n">
-        <v>1.284723993855152e-09</v>
+        <v>6.606881264303865e-09</v>
       </c>
       <c r="DY12" t="n">
-        <v>2.019641343053991e-09</v>
+        <v>1.063124521749614e-08</v>
       </c>
       <c r="DZ12" t="n">
-        <v>7.29185156700396e-10</v>
+        <v>1.582508235564717e-09</v>
       </c>
       <c r="EA12" t="n">
-        <v>2.327652293132587e-09</v>
+        <v>1.783777214825477e-08</v>
       </c>
       <c r="EB12" t="n">
-        <v>2.225960971102836e-09</v>
+        <v>5.977838668513868e-09</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.357125050700404e-10</v>
+        <v>1.762152646023196e-10</v>
       </c>
       <c r="ED12" t="n">
-        <v>1.144100814087778e-09</v>
+        <v>1.580979436255348e-08</v>
       </c>
       <c r="EE12" t="n">
-        <v>1.806514382529656e-10</v>
+        <v>1.509403801946974e-08</v>
       </c>
       <c r="EF12" t="n">
-        <v>5.316080908812637e-11</v>
+        <v>4.323530700123257e-10</v>
       </c>
       <c r="EG12" t="n">
-        <v>5.41262812348009e-10</v>
+        <v>3.806899240288431e-11</v>
       </c>
       <c r="EH12" t="n">
-        <v>7.380185906846748e-10</v>
+        <v>9.207122175780569e-09</v>
       </c>
       <c r="EI12" t="n">
-        <v>1.645336866751279e-09</v>
+        <v>6.836475385796348e-09</v>
       </c>
       <c r="EJ12" t="n">
-        <v>1.203225297174981e-09</v>
+        <v>5.263632196772505e-09</v>
       </c>
       <c r="EK12" t="n">
-        <v>4.928459862441059e-10</v>
+        <v>8.595423928170476e-09</v>
       </c>
       <c r="EL12" t="n">
-        <v>1.357757462017162e-09</v>
+        <v>5.409887204876895e-09</v>
       </c>
       <c r="EM12" t="n">
-        <v>4.374995365985512e-10</v>
+        <v>1.212765443625585e-09</v>
       </c>
       <c r="EN12" t="n">
-        <v>7.980026639486937e-10</v>
+        <v>4.429854705279013e-09</v>
       </c>
       <c r="EO12" t="n">
-        <v>3.069260678945085e-10</v>
+        <v>3.824243588468335e-09</v>
       </c>
       <c r="EP12" t="n">
-        <v>2.27845284306305e-10</v>
+        <v>1.213145051082165e-08</v>
       </c>
       <c r="EQ12" t="n">
-        <v>1.059688115034874e-09</v>
+        <v>5.516889167722638e-09</v>
       </c>
       <c r="ER12" t="n">
-        <v>5.355588750255436e-10</v>
+        <v>3.014218874497487e-10</v>
       </c>
       <c r="ES12" t="n">
-        <v>4.068978043392235e-09</v>
+        <v>6.834140364730956e-09</v>
       </c>
       <c r="ET12" t="n">
-        <v>5.266844183005048e-10</v>
+        <v>1.330674681554456e-09</v>
       </c>
       <c r="EU12" t="n">
-        <v>6.302109945011125e-10</v>
+        <v>1.308736230498653e-09</v>
       </c>
       <c r="EV12" t="n">
-        <v>2.153959677286821e-09</v>
+        <v>3.061427111816784e-09</v>
       </c>
       <c r="EW12" t="n">
-        <v>1.603310817444026e-10</v>
+        <v>6.629861548645977e-09</v>
       </c>
       <c r="EX12" t="n">
-        <v>5.473126812871598e-11</v>
+        <v>2.81789674927424e-10</v>
       </c>
       <c r="EY12" t="n">
-        <v>1.114104697386153e-09</v>
+        <v>1.441915387090376e-08</v>
       </c>
       <c r="EZ12" t="n">
-        <v>1.13815734614775e-09</v>
+        <v>1.26609389639043e-10</v>
       </c>
       <c r="FA12" t="n">
-        <v>1.960816398138832e-09</v>
+        <v>6.848089206812347e-09</v>
       </c>
       <c r="FB12" t="n">
-        <v>5.264430003038001e-10</v>
+        <v>3.596587250243033e-09</v>
       </c>
       <c r="FC12" t="n">
-        <v>2.633515627792349e-10</v>
+        <v>4.335387160381288e-09</v>
       </c>
       <c r="FD12" t="n">
-        <v>9.327317807006352e-10</v>
+        <v>4.042519097247066e-11</v>
       </c>
       <c r="FE12" t="n">
-        <v>7.023244208426149e-10</v>
+        <v>1.089958123756674e-09</v>
       </c>
       <c r="FF12" t="n">
-        <v>1.485219391916814e-09</v>
+        <v>3.414916793786915e-09</v>
       </c>
       <c r="FG12" t="n">
-        <v>4.717884416471918e-10</v>
+        <v>4.617445981125456e-09</v>
       </c>
       <c r="FH12" t="n">
-        <v>8.228215886418866e-10</v>
+        <v>3.79075792977801e-09</v>
       </c>
       <c r="FI12" t="n">
-        <v>2.514562558175726e-09</v>
+        <v>7.74693553751149e-09</v>
       </c>
       <c r="FJ12" t="n">
-        <v>3.712770535457821e-09</v>
+        <v>6.647484784849667e-09</v>
       </c>
       <c r="FK12" t="n">
-        <v>9.531145872543334e-10</v>
+        <v>9.093684694150284e-10</v>
       </c>
       <c r="FL12" t="n">
-        <v>1.339044014558866e-10</v>
+        <v>2.97831470597032e-09</v>
       </c>
       <c r="FM12" t="n">
-        <v>1.693899354116013e-09</v>
+        <v>6.247052208863124e-09</v>
       </c>
       <c r="FN12" t="n">
-        <v>1.016000172882059e-09</v>
+        <v>6.93024038156409e-09</v>
       </c>
       <c r="FO12" t="n">
-        <v>5.895551824508516e-10</v>
+        <v>1.88385005372993e-08</v>
       </c>
       <c r="FP12" t="n">
-        <v>8.696511288874831e-10</v>
+        <v>1.273038208182697e-08</v>
       </c>
       <c r="FQ12" t="n">
-        <v>8.583855848343092e-10</v>
+        <v>2.117827513359316e-08</v>
       </c>
       <c r="FR12" t="n">
-        <v>4.800653763403773e-10</v>
+        <v>1.384439585194741e-08</v>
       </c>
       <c r="FS12" t="n">
-        <v>7.669880286442776e-10</v>
+        <v>6.95938462413892e-09</v>
       </c>
       <c r="FT12" t="n">
-        <v>2.618666838927197e-09</v>
+        <v>2.076259164596195e-08</v>
       </c>
       <c r="FU12" t="n">
-        <v>3.941693360598464e-10</v>
+        <v>1.190960574604105e-08</v>
       </c>
       <c r="FV12" t="n">
-        <v>4.915479689948654e-10</v>
+        <v>1.121357406930201e-08</v>
       </c>
       <c r="FW12" t="n">
-        <v>1.440581876011038e-09</v>
+        <v>1.00075610021122e-08</v>
       </c>
       <c r="FX12" t="n">
-        <v>7.489845410546536e-10</v>
+        <v>5.339812592097815e-09</v>
       </c>
       <c r="FY12" t="n">
-        <v>2.506862051276926e-09</v>
+        <v>7.28174354147626e-10</v>
       </c>
       <c r="FZ12" t="n">
-        <v>7.680621139094512e-10</v>
+        <v>2.426237877273252e-09</v>
       </c>
       <c r="GA12" t="n">
-        <v>2.390577458211141e-10</v>
+        <v>9.826308655647154e-09</v>
       </c>
       <c r="GB12" t="n">
-        <v>2.510904262287283e-10</v>
+        <v>9.571722081602729e-09</v>
       </c>
       <c r="GC12" t="n">
-        <v>2.030415391374163e-09</v>
+        <v>7.338808227785876e-09</v>
       </c>
       <c r="GD12" t="n">
-        <v>5.957772053477584e-10</v>
+        <v>1.586110798257323e-08</v>
       </c>
       <c r="GE12" t="n">
-        <v>5.172718253732e-09</v>
+        <v>1.839936558667432e-08</v>
       </c>
       <c r="GF12" t="n">
-        <v>2.772386764604562e-10</v>
+        <v>3.46695805397701e-09</v>
       </c>
       <c r="GG12" t="n">
-        <v>1.779412062141716e-09</v>
+        <v>8.416425778534631e-09</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.001688069896772504</v>
+        <v>0.03005289845168591</v>
       </c>
       <c r="B13" t="n">
-        <v>0.009606230072677135</v>
+        <v>0.04125579074025154</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0001830510300351307</v>
+        <v>0.07385976612567902</v>
       </c>
       <c r="D13" t="n">
-        <v>0.005101590882986784</v>
+        <v>0.03617329150438309</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0004316780832596123</v>
+        <v>0.04664383083581924</v>
       </c>
       <c r="F13" t="n">
-        <v>0.007537626661360264</v>
+        <v>0.07298743724822998</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0002143544261343777</v>
+        <v>0.02261603064835072</v>
       </c>
       <c r="H13" t="n">
-        <v>0.001854686066508293</v>
+        <v>0.05534276366233826</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0002494094951543957</v>
+        <v>0.005815936252474785</v>
       </c>
       <c r="J13" t="n">
-        <v>0.002303196350112557</v>
+        <v>0.03274229541420937</v>
       </c>
       <c r="K13" t="n">
-        <v>0.007553294766694307</v>
+        <v>0.1707537621259689</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0005710829864256084</v>
+        <v>0.06449620425701141</v>
       </c>
       <c r="M13" t="n">
-        <v>0.005342305637896061</v>
+        <v>0.0421941764652729</v>
       </c>
       <c r="N13" t="n">
-        <v>0.00127386162057519</v>
+        <v>0.06360931694507599</v>
       </c>
       <c r="O13" t="n">
-        <v>0.008210737258195877</v>
+        <v>0.1000913232564926</v>
       </c>
       <c r="P13" t="n">
-        <v>0.001020100666210055</v>
+        <v>0.08270787447690964</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.0001043134834617376</v>
+        <v>0.008229832164943218</v>
       </c>
       <c r="R13" t="n">
-        <v>0.0002405767445452511</v>
+        <v>0.01605003699660301</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0004952927120029926</v>
+        <v>0.03932581841945648</v>
       </c>
       <c r="T13" t="n">
-        <v>0.001479205675423145</v>
+        <v>0.004865270107984543</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0001408293028362095</v>
+        <v>0.0002529490739107132</v>
       </c>
       <c r="V13" t="n">
-        <v>0.001453222706913948</v>
+        <v>0.03201122209429741</v>
       </c>
       <c r="W13" t="n">
-        <v>9.16227072593756e-05</v>
+        <v>0.04891121387481689</v>
       </c>
       <c r="X13" t="n">
-        <v>5.518395482795313e-06</v>
+        <v>0.02049193531274796</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.0008815572364255786</v>
+        <v>0.02780178189277649</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.000186449964530766</v>
+        <v>0.06862284243106842</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.001197042758576572</v>
+        <v>0.02464593574404716</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.0001708117197267711</v>
+        <v>0.08107287436723709</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.001118393498472869</v>
+        <v>0.007292079273611307</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.0004728797648567706</v>
+        <v>0.02177231386303902</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.001010766602121294</v>
+        <v>0.01322438754141331</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.0005552666261792183</v>
+        <v>0.09831001609563828</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.0004674345254898071</v>
+        <v>0.03083758614957333</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.001833727350458503</v>
+        <v>0.04756073653697968</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.0002445146674290299</v>
+        <v>0.05750216171145439</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.0003616594476625323</v>
+        <v>0.004276365973055363</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.001151200034655631</v>
+        <v>0.03169672563672066</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.001426575123332441</v>
+        <v>0.002594864927232265</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.0003746936854440719</v>
+        <v>0.002745741978287697</v>
       </c>
       <c r="AN13" t="n">
-        <v>0.0005505658918991685</v>
+        <v>0.01891923323273659</v>
       </c>
       <c r="AO13" t="n">
-        <v>1.741203595884144e-05</v>
+        <v>0.04253076016902924</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.001357603468932211</v>
+        <v>5.221855826675892e-05</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.0006051145610399544</v>
+        <v>0.02863224223256111</v>
       </c>
       <c r="AR13" t="n">
-        <v>4.650210030376911e-07</v>
+        <v>0.05679171159863472</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.0008851679158397019</v>
+        <v>0.01021220069378614</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.001415574923157692</v>
+        <v>0.009465026669204235</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.007434331811964512</v>
+        <v>0.1758937388658524</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.0008223699405789375</v>
+        <v>0.05157546699047089</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.000323924352414906</v>
+        <v>0.02105109766125679</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.001585445133969188</v>
+        <v>0.02462159655988216</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.00434539932757616</v>
+        <v>0.06987369805574417</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.0004334454133640975</v>
+        <v>0.00979127548635006</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.001558201387524605</v>
+        <v>0.02235131338238716</v>
       </c>
       <c r="BB13" t="n">
-        <v>0.001630960148759186</v>
+        <v>0.01024551875889301</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.00102261092979461</v>
+        <v>0.032044917345047</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.001798177952878177</v>
+        <v>0.02964578196406364</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.002260802313685417</v>
+        <v>0.01350295357406139</v>
       </c>
       <c r="BF13" t="n">
-        <v>0.002214011270552874</v>
+        <v>0.01602201908826828</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.002763165859505534</v>
+        <v>0.04768793284893036</v>
       </c>
       <c r="BH13" t="n">
-        <v>0.002519707661122084</v>
+        <v>0.02008075453341007</v>
       </c>
       <c r="BI13" t="n">
-        <v>0.0001581143005751073</v>
+        <v>0.02711526490747929</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.002034406177699566</v>
+        <v>0.06348814815282822</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.0003187850525137037</v>
+        <v>0.01615200750529766</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.0005375159671530128</v>
+        <v>0.03222150355577469</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.002337180776521564</v>
+        <v>0.07458897680044174</v>
       </c>
       <c r="BN13" t="n">
-        <v>0.0006723077385686338</v>
+        <v>0.003731167409569025</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.00244675250723958</v>
+        <v>0.04059676453471184</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.002088629873469472</v>
+        <v>0.04945823922753334</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.0002813769388012588</v>
+        <v>0.01215737406164408</v>
       </c>
       <c r="BR13" t="n">
-        <v>0.001343442243523896</v>
+        <v>0.01174174062907696</v>
       </c>
       <c r="BS13" t="n">
-        <v>0.000266905699390918</v>
+        <v>0.04139969497919083</v>
       </c>
       <c r="BT13" t="n">
-        <v>0.0002527542237658054</v>
+        <v>0.0006580636836588383</v>
       </c>
       <c r="BU13" t="n">
-        <v>0.0006717218784615397</v>
+        <v>0.02954672649502754</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.003694337559863925</v>
+        <v>0.08123541623353958</v>
       </c>
       <c r="BW13" t="n">
-        <v>5.702691851183772e-05</v>
+        <v>0.02486352622509003</v>
       </c>
       <c r="BX13" t="n">
-        <v>0.0006384474691003561</v>
+        <v>0.05308976769447327</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.0006746798753738403</v>
+        <v>0.02733000367879868</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0.0007001450285315514</v>
+        <v>0.01950021274387836</v>
       </c>
       <c r="CA13" t="n">
-        <v>0.001361644128337502</v>
+        <v>0.01235601492226124</v>
       </c>
       <c r="CB13" t="n">
-        <v>0.0008307185489684343</v>
+        <v>0.03628331795334816</v>
       </c>
       <c r="CC13" t="n">
-        <v>0.001062167342752218</v>
+        <v>0.0005667904042638838</v>
       </c>
       <c r="CD13" t="n">
-        <v>0.0002886055444832891</v>
+        <v>0.02844207733869553</v>
       </c>
       <c r="CE13" t="n">
-        <v>0.00182808272074908</v>
+        <v>0.0153195159509778</v>
       </c>
       <c r="CF13" t="n">
-        <v>0.0008277924498543143</v>
+        <v>0.02068987116217613</v>
       </c>
       <c r="CG13" t="n">
-        <v>0.0009433833765797317</v>
+        <v>0.002893369412049651</v>
       </c>
       <c r="CH13" t="n">
-        <v>0.0005086103337816894</v>
+        <v>0.02227465622127056</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.001314350520260632</v>
+        <v>0.0289527028799057</v>
       </c>
       <c r="CJ13" t="n">
-        <v>0.0004207499732729048</v>
+        <v>0.01266542449593544</v>
       </c>
       <c r="CK13" t="n">
-        <v>0.0003058345173485577</v>
+        <v>0.01002504769712687</v>
       </c>
       <c r="CL13" t="n">
-        <v>0.0005660505266860127</v>
+        <v>0.01170596200972795</v>
       </c>
       <c r="CM13" t="n">
-        <v>0.001640588277950883</v>
+        <v>0.01757708191871643</v>
       </c>
       <c r="CN13" t="n">
-        <v>0.001323449425399303</v>
+        <v>0.1075394824147224</v>
       </c>
       <c r="CO13" t="n">
-        <v>0.000348148139892146</v>
+        <v>0.01779451034963131</v>
       </c>
       <c r="CP13" t="n">
-        <v>0.001250732690095901</v>
+        <v>0.05215410143136978</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.0001331143284915015</v>
+        <v>0.03247290104627609</v>
       </c>
       <c r="CR13" t="n">
-        <v>0.0002645524800755084</v>
+        <v>0.01935414224863052</v>
       </c>
       <c r="CS13" t="n">
-        <v>0.0001057709159795195</v>
+        <v>0.03469046205282211</v>
       </c>
       <c r="CT13" t="n">
-        <v>0.001185592263936996</v>
+        <v>0.0104111023247242</v>
       </c>
       <c r="CU13" t="n">
-        <v>0.0005236275028437376</v>
+        <v>0.01421611197292805</v>
       </c>
       <c r="CV13" t="n">
-        <v>0.0001805236679501832</v>
+        <v>0.023398632183671</v>
       </c>
       <c r="CW13" t="n">
-        <v>0.001338620786555111</v>
+        <v>0.01194907631725073</v>
       </c>
       <c r="CX13" t="n">
-        <v>0.000745452765841037</v>
+        <v>0.01757747679948807</v>
       </c>
       <c r="CY13" t="n">
-        <v>0.001464969245716929</v>
+        <v>0.004519082605838776</v>
       </c>
       <c r="CZ13" t="n">
-        <v>0.000337716774083674</v>
+        <v>0.006704673171043396</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.001251384965144098</v>
+        <v>0.0301049966365099</v>
       </c>
       <c r="DB13" t="n">
-        <v>0.0006227785488590598</v>
+        <v>0.001854826579801738</v>
       </c>
       <c r="DC13" t="n">
-        <v>0.0009930217638611794</v>
+        <v>0.01556648686528206</v>
       </c>
       <c r="DD13" t="n">
-        <v>0.0002893451601266861</v>
+        <v>0.0136724840849638</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.0009961361065506935</v>
+        <v>0.04648704081773758</v>
       </c>
       <c r="DF13" t="n">
-        <v>0.003182966960594058</v>
+        <v>0.0224839486181736</v>
       </c>
       <c r="DG13" t="n">
-        <v>0.0002914509386755526</v>
+        <v>0.05578268319368362</v>
       </c>
       <c r="DH13" t="n">
-        <v>0.002806209027767181</v>
+        <v>0.0650208368897438</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.0001409869873896241</v>
+        <v>0.05225732922554016</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0.0007509172428399324</v>
+        <v>0.02796467766165733</v>
       </c>
       <c r="DK13" t="n">
-        <v>0.00187057233415544</v>
+        <v>0.05020807683467865</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.001996759325265884</v>
+        <v>0.01675730012357235</v>
       </c>
       <c r="DM13" t="n">
-        <v>0.0009052821551449597</v>
+        <v>0.005913277622312307</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.00101900810841471</v>
+        <v>0.03620807453989983</v>
       </c>
       <c r="DO13" t="n">
-        <v>0.000996534014120698</v>
+        <v>0.03637436032295227</v>
       </c>
       <c r="DP13" t="n">
-        <v>0.001177514437586069</v>
+        <v>0.005186391994357109</v>
       </c>
       <c r="DQ13" t="n">
-        <v>0.001444775611162186</v>
+        <v>0.04788686707615852</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.0004376312717795372</v>
+        <v>0.05057962611317635</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.0001019110131892376</v>
+        <v>0.02301653660833836</v>
       </c>
       <c r="DT13" t="n">
-        <v>8.764752419665456e-05</v>
+        <v>0.009768020361661911</v>
       </c>
       <c r="DU13" t="n">
-        <v>0.0005050060572102666</v>
+        <v>0.06692716479301453</v>
       </c>
       <c r="DV13" t="n">
-        <v>0.000621616723947227</v>
+        <v>0.007826785556972027</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.0001261923753190786</v>
+        <v>0.0408942773938179</v>
       </c>
       <c r="DX13" t="n">
-        <v>0.0001621021365281194</v>
+        <v>0.02789898589253426</v>
       </c>
       <c r="DY13" t="n">
-        <v>0.001053887652233243</v>
+        <v>0.04291503131389618</v>
       </c>
       <c r="DZ13" t="n">
-        <v>0.0004453372675925493</v>
+        <v>0.005099557340145111</v>
       </c>
       <c r="EA13" t="n">
-        <v>0.0005572211230173707</v>
+        <v>0.009985924698412418</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.00056157645303756</v>
+        <v>0.03709830716252327</v>
       </c>
       <c r="EC13" t="n">
-        <v>9.793492790777236e-05</v>
+        <v>0.003942076116800308</v>
       </c>
       <c r="ED13" t="n">
-        <v>0.0001437774335499853</v>
+        <v>0.008961550891399384</v>
       </c>
       <c r="EE13" t="n">
-        <v>0.0007305721519514918</v>
+        <v>0.01710409112274647</v>
       </c>
       <c r="EF13" t="n">
-        <v>0.0005033451598137617</v>
+        <v>0.02343219518661499</v>
       </c>
       <c r="EG13" t="n">
-        <v>0.000401898636482656</v>
+        <v>0.01987097784876823</v>
       </c>
       <c r="EH13" t="n">
-        <v>0.0002157499839086086</v>
+        <v>0.004002845846116543</v>
       </c>
       <c r="EI13" t="n">
-        <v>0.0003179367631673813</v>
+        <v>0.02950126677751541</v>
       </c>
       <c r="EJ13" t="n">
-        <v>4.177789378445596e-05</v>
+        <v>0.01524069905281067</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.0008757262257859111</v>
+        <v>0.03483118489384651</v>
       </c>
       <c r="EL13" t="n">
-        <v>0.0007414437714032829</v>
+        <v>0.009280703030526638</v>
       </c>
       <c r="EM13" t="n">
-        <v>6.777761882403865e-05</v>
+        <v>0.02468958869576454</v>
       </c>
       <c r="EN13" t="n">
-        <v>0.0004618842212948948</v>
+        <v>0.01290185190737247</v>
       </c>
       <c r="EO13" t="n">
-        <v>0.0008408550638705492</v>
+        <v>0.007251022383570671</v>
       </c>
       <c r="EP13" t="n">
-        <v>0.000583380286116153</v>
+        <v>0.02100301161408424</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0.000415256799897179</v>
+        <v>0.01206475403159857</v>
       </c>
       <c r="ER13" t="n">
-        <v>0.0006455593975260854</v>
+        <v>0.03473988920450211</v>
       </c>
       <c r="ES13" t="n">
-        <v>0.0004993574693799019</v>
+        <v>0.009723031893372536</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.001864977995865047</v>
+        <v>0.005960474722087383</v>
       </c>
       <c r="EU13" t="n">
-        <v>0.0007599741802550852</v>
+        <v>0.017964793369174</v>
       </c>
       <c r="EV13" t="n">
-        <v>0.001755730481818318</v>
+        <v>0.008627673611044884</v>
       </c>
       <c r="EW13" t="n">
-        <v>0.0001293646346312016</v>
+        <v>0.01821365021169186</v>
       </c>
       <c r="EX13" t="n">
-        <v>0.0002561768051236868</v>
+        <v>0.02609804645180702</v>
       </c>
       <c r="EY13" t="n">
-        <v>0.00124308920931071</v>
+        <v>0.01931157335639</v>
       </c>
       <c r="EZ13" t="n">
-        <v>0.0004616683872882277</v>
+        <v>0.01972031965851784</v>
       </c>
       <c r="FA13" t="n">
-        <v>0.0009553981362842023</v>
+        <v>0.005458551459014416</v>
       </c>
       <c r="FB13" t="n">
-        <v>0.0003255903429817408</v>
+        <v>0.008964387699961662</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.001209423295222223</v>
+        <v>0.03281625732779503</v>
       </c>
       <c r="FD13" t="n">
-        <v>0.0007002915372140706</v>
+        <v>0.01615961082279682</v>
       </c>
       <c r="FE13" t="n">
-        <v>0.0003730427997652441</v>
+        <v>0.003961057402193546</v>
       </c>
       <c r="FF13" t="n">
-        <v>0.0006322682020254433</v>
+        <v>0.01260354463011026</v>
       </c>
       <c r="FG13" t="n">
-        <v>0.0005726199597120285</v>
+        <v>0.03486034274101257</v>
       </c>
       <c r="FH13" t="n">
-        <v>0.001004009856842458</v>
+        <v>0.01088093779981136</v>
       </c>
       <c r="FI13" t="n">
-        <v>0.0006467569619417191</v>
+        <v>0.01275984290987253</v>
       </c>
       <c r="FJ13" t="n">
-        <v>0.0002771919826045632</v>
+        <v>0.03022407740354538</v>
       </c>
       <c r="FK13" t="n">
-        <v>5.611831875285134e-05</v>
+        <v>0.005571008659899235</v>
       </c>
       <c r="FL13" t="n">
-        <v>0.0003204953973181546</v>
+        <v>0.0008769968990236521</v>
       </c>
       <c r="FM13" t="n">
-        <v>9.958430018741637e-05</v>
+        <v>0.03073394671082497</v>
       </c>
       <c r="FN13" t="n">
-        <v>8.934264769777656e-05</v>
+        <v>0.03216399997472763</v>
       </c>
       <c r="FO13" t="n">
-        <v>0.0001223815343109891</v>
+        <v>0.03148021548986435</v>
       </c>
       <c r="FP13" t="n">
-        <v>0.001108870725147426</v>
+        <v>0.0003587640821933746</v>
       </c>
       <c r="FQ13" t="n">
-        <v>0.0005970904603600502</v>
+        <v>0.08690522611141205</v>
       </c>
       <c r="FR13" t="n">
-        <v>0.0001875810121418908</v>
+        <v>0.02252977527678013</v>
       </c>
       <c r="FS13" t="n">
-        <v>0.0008815460605546832</v>
+        <v>0.02394479140639305</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.004232014529407024</v>
+        <v>0.04582568258047104</v>
       </c>
       <c r="FU13" t="n">
-        <v>0.0006955328281037509</v>
+        <v>0.03088135085999966</v>
       </c>
       <c r="FV13" t="n">
-        <v>0.0003467060741968453</v>
+        <v>0.03973864763975143</v>
       </c>
       <c r="FW13" t="n">
-        <v>0.001649849000386894</v>
+        <v>0.008473049849271774</v>
       </c>
       <c r="FX13" t="n">
-        <v>0.0002245379873784259</v>
+        <v>0.03655053675174713</v>
       </c>
       <c r="FY13" t="n">
-        <v>0.001110535929910839</v>
+        <v>0.02353448420763016</v>
       </c>
       <c r="FZ13" t="n">
-        <v>0.001192463794723153</v>
+        <v>0.02480420470237732</v>
       </c>
       <c r="GA13" t="n">
-        <v>0.0002512831124477088</v>
+        <v>0.004995780065655708</v>
       </c>
       <c r="GB13" t="n">
-        <v>0.001367545337416232</v>
+        <v>0.03470969945192337</v>
       </c>
       <c r="GC13" t="n">
-        <v>0.0005480673862621188</v>
+        <v>0.01874165050685406</v>
       </c>
       <c r="GD13" t="n">
-        <v>0.0006856831023469567</v>
+        <v>0.001704022055491805</v>
       </c>
       <c r="GE13" t="n">
-        <v>0.003158885985612869</v>
+        <v>0.003398221917450428</v>
       </c>
       <c r="GF13" t="n">
-        <v>0.001270066015422344</v>
+        <v>0.01909440197050571</v>
       </c>
       <c r="GG13" t="n">
-        <v>0.0008732810965739191</v>
+        <v>0.03150102496147156</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.0002942474966403097</v>
+        <v>1.302576401940314e-05</v>
       </c>
       <c r="B14" t="n">
-        <v>0.0004199130926281214</v>
+        <v>6.590299017261714e-05</v>
       </c>
       <c r="C14" t="n">
-        <v>0.001670595956966281</v>
+        <v>0.0001037811889545992</v>
       </c>
       <c r="D14" t="n">
-        <v>0.001535473391413689</v>
+        <v>0.0001205968073918484</v>
       </c>
       <c r="E14" t="n">
-        <v>0.001684274291619658</v>
+        <v>5.136233085067943e-06</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0007200372638180852</v>
+        <v>3.644244861789048e-05</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0004457737086340785</v>
+        <v>2.551068610046059e-05</v>
       </c>
       <c r="H14" t="n">
-        <v>5.914501525694504e-05</v>
+        <v>2.830893572536297e-05</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0008779120398685336</v>
+        <v>7.926880789455026e-05</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0002202334289904684</v>
+        <v>2.851666613423731e-05</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0003920674207620323</v>
+        <v>7.505308894906193e-05</v>
       </c>
       <c r="L14" t="n">
-        <v>0.001313574844971299</v>
+        <v>0.0001460399944335222</v>
       </c>
       <c r="M14" t="n">
-        <v>0.001879599643871188</v>
+        <v>0.0001683426380623132</v>
       </c>
       <c r="N14" t="n">
-        <v>0.0004366682842373848</v>
+        <v>5.861302634002641e-05</v>
       </c>
       <c r="O14" t="n">
-        <v>0.0006360848783515394</v>
+        <v>5.44948925380595e-05</v>
       </c>
       <c r="P14" t="n">
-        <v>0.0003140670014545321</v>
+        <v>4.124536644667387e-06</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.0002466386358719319</v>
+        <v>8.043673733482137e-05</v>
       </c>
       <c r="R14" t="n">
-        <v>0.001254096394404769</v>
+        <v>2.733102519414388e-05</v>
       </c>
       <c r="S14" t="n">
-        <v>8.614236139692366e-05</v>
+        <v>1.785058157111052e-05</v>
       </c>
       <c r="T14" t="n">
-        <v>0.000504443421959877</v>
+        <v>2.983586000482319e-06</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0004529901198111475</v>
+        <v>2.477354064467363e-05</v>
       </c>
       <c r="V14" t="n">
-        <v>0.0003382510039955378</v>
+        <v>2.655059142853133e-05</v>
       </c>
       <c r="W14" t="n">
-        <v>4.682510552811436e-05</v>
+        <v>4.47383317805361e-05</v>
       </c>
       <c r="X14" t="n">
-        <v>0.0002580445725470781</v>
+        <v>4.155272472416982e-05</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.0001664894225541502</v>
+        <v>7.740299224678893e-06</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.320839798310772e-05</v>
+        <v>1.522041293355869e-05</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.0002263557107653469</v>
+        <v>2.792322447930928e-05</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.0005895810318179429</v>
+        <v>2.431561915727798e-05</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.0002784435055218637</v>
+        <v>4.650108166970313e-06</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.0003120916371699423</v>
+        <v>1.51178201122093e-05</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.0006806404562667012</v>
+        <v>5.19085988344159e-05</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.0003943428455386311</v>
+        <v>2.451470390951727e-05</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.0001676568354014307</v>
+        <v>4.35067977377912e-06</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.0001071766309905797</v>
+        <v>1.155870450020302e-05</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.0001434811129001901</v>
+        <v>2.823136310325935e-05</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.0003901653690263629</v>
+        <v>4.576717401505448e-06</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.0001081787995644845</v>
+        <v>5.804744432680309e-06</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.0001480485079810023</v>
+        <v>1.426450580765959e-06</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.0001434937003068626</v>
+        <v>2.65232320089126e-05</v>
       </c>
       <c r="AN14" t="n">
-        <v>8.409077418036759e-05</v>
+        <v>2.868976480385754e-05</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.0004864575457759202</v>
+        <v>2.975264760607388e-05</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.0001177804369945079</v>
+        <v>2.632355972309597e-06</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.0001712437806418166</v>
+        <v>1.317780515819322e-05</v>
       </c>
       <c r="AR14" t="n">
-        <v>5.950254126219079e-05</v>
+        <v>2.476113877492025e-05</v>
       </c>
       <c r="AS14" t="n">
-        <v>9.651486834627576e-06</v>
+        <v>4.675371019402519e-05</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.000657921948004514</v>
+        <v>2.61437708104495e-05</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.0009534002165310085</v>
+        <v>5.295952178130392e-06</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.0005927325692027807</v>
+        <v>0.0001769531518220901</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.001002954901196063</v>
+        <v>9.834455704549327e-05</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.0007276808028109372</v>
+        <v>3.376405220478773e-05</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.0004050051211379468</v>
+        <v>7.560849189758301e-05</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.0001009993138723075</v>
+        <v>6.711423338856548e-05</v>
       </c>
       <c r="BA14" t="n">
-        <v>0.0001723976311041042</v>
+        <v>3.408557313377969e-05</v>
       </c>
       <c r="BB14" t="n">
-        <v>0.0003644093230832368</v>
+        <v>5.909540050197393e-05</v>
       </c>
       <c r="BC14" t="n">
-        <v>0.0002745870151557028</v>
+        <v>2.799552021315321e-05</v>
       </c>
       <c r="BD14" t="n">
-        <v>0.00149239506572485</v>
+        <v>1.261297984456178e-05</v>
       </c>
       <c r="BE14" t="n">
-        <v>0.0004053131269756705</v>
+        <v>3.968959572375752e-05</v>
       </c>
       <c r="BF14" t="n">
-        <v>0.0004696226678788662</v>
+        <v>2.460297764628194e-05</v>
       </c>
       <c r="BG14" t="n">
-        <v>5.450832031783648e-05</v>
+        <v>2.910446164605673e-05</v>
       </c>
       <c r="BH14" t="n">
-        <v>0.001202852232381701</v>
+        <v>3.578653195290826e-05</v>
       </c>
       <c r="BI14" t="n">
-        <v>0.0003574391885194927</v>
+        <v>5.331879219738767e-05</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.0007263527950271964</v>
+        <v>3.980257679359056e-05</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.001123597961850464</v>
+        <v>4.276625622878782e-05</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.0002690731780603528</v>
+        <v>4.816743967239745e-05</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.0003013023524545133</v>
+        <v>4.130985325900838e-05</v>
       </c>
       <c r="BN14" t="n">
-        <v>0.0001226624444825575</v>
+        <v>2.181125273637008e-05</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.0003480173763819039</v>
+        <v>3.815069794654846e-05</v>
       </c>
       <c r="BP14" t="n">
-        <v>0.0003282726975157857</v>
+        <v>4.176781658316031e-05</v>
       </c>
       <c r="BQ14" t="n">
-        <v>6.264306284720078e-05</v>
+        <v>1.593302476976532e-05</v>
       </c>
       <c r="BR14" t="n">
-        <v>0.0001497398188803345</v>
+        <v>1.946230986504816e-05</v>
       </c>
       <c r="BS14" t="n">
-        <v>0.0002195558481616899</v>
+        <v>8.075781806837767e-05</v>
       </c>
       <c r="BT14" t="n">
-        <v>9.253001189790666e-05</v>
+        <v>1.192149647977203e-05</v>
       </c>
       <c r="BU14" t="n">
-        <v>0.0002872224140446633</v>
+        <v>4.608526978699956e-06</v>
       </c>
       <c r="BV14" t="n">
-        <v>0.0003744478162843734</v>
+        <v>2.063804458884988e-05</v>
       </c>
       <c r="BW14" t="n">
-        <v>0.0004011776763945818</v>
+        <v>9.393344225827605e-05</v>
       </c>
       <c r="BX14" t="n">
-        <v>0.0008390638395212591</v>
+        <v>9.775020589586347e-05</v>
       </c>
       <c r="BY14" t="n">
-        <v>0.0008641169406473637</v>
+        <v>3.564294456737116e-05</v>
       </c>
       <c r="BZ14" t="n">
-        <v>0.0002262976631755009</v>
+        <v>2.455637331877369e-05</v>
       </c>
       <c r="CA14" t="n">
-        <v>5.677293665939942e-05</v>
+        <v>4.829920726479031e-06</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.487680078251287e-05</v>
+        <v>2.304295958310831e-05</v>
       </c>
       <c r="CC14" t="n">
-        <v>0.0004989798180758953</v>
+        <v>3.308330269646831e-05</v>
       </c>
       <c r="CD14" t="n">
-        <v>6.989643588894978e-05</v>
+        <v>2.946844460893772e-06</v>
       </c>
       <c r="CE14" t="n">
-        <v>0.000147269616718404</v>
+        <v>1.756636083882768e-05</v>
       </c>
       <c r="CF14" t="n">
-        <v>0.000500353635288775</v>
+        <v>3.791653216467239e-05</v>
       </c>
       <c r="CG14" t="n">
-        <v>0.0003083516494370997</v>
+        <v>4.981172969564795e-05</v>
       </c>
       <c r="CH14" t="n">
-        <v>0.000451909756520763</v>
+        <v>9.589110050001182e-06</v>
       </c>
       <c r="CI14" t="n">
-        <v>0.0001386952644679695</v>
+        <v>1.441880522179417e-05</v>
       </c>
       <c r="CJ14" t="n">
-        <v>0.0001668052427703515</v>
+        <v>4.552052814688068e-07</v>
       </c>
       <c r="CK14" t="n">
-        <v>0.0001745566260069609</v>
+        <v>1.088879616872873e-05</v>
       </c>
       <c r="CL14" t="n">
-        <v>7.236416422529146e-05</v>
+        <v>7.327390903810738e-06</v>
       </c>
       <c r="CM14" t="n">
-        <v>0.0006699255318380892</v>
+        <v>6.756909897376318e-06</v>
       </c>
       <c r="CN14" t="n">
-        <v>0.000684895203448832</v>
+        <v>1.843947757151909e-05</v>
       </c>
       <c r="CO14" t="n">
-        <v>3.857596311718225e-06</v>
+        <v>7.095848559401929e-05</v>
       </c>
       <c r="CP14" t="n">
-        <v>0.0002990609791595489</v>
+        <v>0.0001002576973405667</v>
       </c>
       <c r="CQ14" t="n">
-        <v>0.0001024662924464792</v>
+        <v>1.874461304396391e-06</v>
       </c>
       <c r="CR14" t="n">
-        <v>0.0002067367604468018</v>
+        <v>5.148208583705127e-05</v>
       </c>
       <c r="CS14" t="n">
-        <v>0.0002539907000027597</v>
+        <v>1.078461627912475e-05</v>
       </c>
       <c r="CT14" t="n">
-        <v>0.0006456360570155084</v>
+        <v>1.438295657862909e-05</v>
       </c>
       <c r="CU14" t="n">
-        <v>1.696436811471358e-05</v>
+        <v>3.463188113528304e-05</v>
       </c>
       <c r="CV14" t="n">
-        <v>1.132398301706417e-05</v>
+        <v>6.418874363589566e-06</v>
       </c>
       <c r="CW14" t="n">
-        <v>0.0002277699531987309</v>
+        <v>3.086296783294529e-05</v>
       </c>
       <c r="CX14" t="n">
-        <v>0.0003414354287087917</v>
+        <v>3.225024556741118e-05</v>
       </c>
       <c r="CY14" t="n">
-        <v>0.0003239192883484066</v>
+        <v>4.476425965549424e-05</v>
       </c>
       <c r="CZ14" t="n">
-        <v>0.0003298452065791935</v>
+        <v>6.001096153340768e-06</v>
       </c>
       <c r="DA14" t="n">
-        <v>9.629849228076637e-05</v>
+        <v>2.664009844011161e-05</v>
       </c>
       <c r="DB14" t="n">
-        <v>0.0001858913747128099</v>
+        <v>2.951304850284941e-06</v>
       </c>
       <c r="DC14" t="n">
-        <v>9.480470907874405e-05</v>
+        <v>7.633123459527269e-06</v>
       </c>
       <c r="DD14" t="n">
-        <v>9.49359018704854e-05</v>
+        <v>8.389632057514973e-06</v>
       </c>
       <c r="DE14" t="n">
-        <v>6.453915557358414e-05</v>
+        <v>3.885812111548148e-05</v>
       </c>
       <c r="DF14" t="n">
-        <v>0.0004954907344654202</v>
+        <v>3.717554864124395e-05</v>
       </c>
       <c r="DG14" t="n">
-        <v>0.001213577808812261</v>
+        <v>6.153323965918389e-07</v>
       </c>
       <c r="DH14" t="n">
-        <v>4.241500937496312e-05</v>
+        <v>3.213225863873959e-05</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.0003973935381509364</v>
+        <v>1.729959694785066e-05</v>
       </c>
       <c r="DJ14" t="n">
-        <v>0.0003113516431767493</v>
+        <v>4.885159796685912e-07</v>
       </c>
       <c r="DK14" t="n">
-        <v>0.0005983144510537386</v>
+        <v>4.365574568510056e-05</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.0003165967063978314</v>
+        <v>5.111316568218172e-05</v>
       </c>
       <c r="DM14" t="n">
-        <v>0.0002986906329169869</v>
+        <v>5.480853724293411e-05</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.586872531333938e-05</v>
+        <v>1.246732426807284e-05</v>
       </c>
       <c r="DO14" t="n">
-        <v>0.0005756384925916791</v>
+        <v>2.821997622959316e-05</v>
       </c>
       <c r="DP14" t="n">
-        <v>0.0001419799373252317</v>
+        <v>1.415976657881401e-05</v>
       </c>
       <c r="DQ14" t="n">
-        <v>0.0001549652370158583</v>
+        <v>1.46750571730081e-05</v>
       </c>
       <c r="DR14" t="n">
-        <v>0.001038853428326547</v>
+        <v>4.160834578215145e-05</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.0002704058715607971</v>
+        <v>1.024798893922707e-05</v>
       </c>
       <c r="DT14" t="n">
-        <v>5.058950046077371e-05</v>
+        <v>6.625066816923209e-06</v>
       </c>
       <c r="DU14" t="n">
-        <v>0.0001428826944902539</v>
+        <v>1.939988942467608e-05</v>
       </c>
       <c r="DV14" t="n">
-        <v>0.0005982838338240981</v>
+        <v>3.108296732534654e-05</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.0001364649797324091</v>
+        <v>5.325035454006866e-05</v>
       </c>
       <c r="DX14" t="n">
-        <v>0.0006434574024751782</v>
+        <v>1.929594327521045e-05</v>
       </c>
       <c r="DY14" t="n">
-        <v>0.000540047069080174</v>
+        <v>2.454166133247782e-05</v>
       </c>
       <c r="DZ14" t="n">
-        <v>0.0001451805437682196</v>
+        <v>4.664966581913177e-06</v>
       </c>
       <c r="EA14" t="n">
-        <v>0.0003736248181667179</v>
+        <v>1.06396701085032e-05</v>
       </c>
       <c r="EB14" t="n">
-        <v>8.85988338268362e-05</v>
+        <v>1.637875539017841e-05</v>
       </c>
       <c r="EC14" t="n">
-        <v>3.23164276778698e-05</v>
+        <v>9.136863809544593e-06</v>
       </c>
       <c r="ED14" t="n">
-        <v>0.0002712399582378566</v>
+        <v>5.338736082194373e-05</v>
       </c>
       <c r="EE14" t="n">
-        <v>0.0002267922245664522</v>
+        <v>2.321084866707679e-05</v>
       </c>
       <c r="EF14" t="n">
-        <v>0.0002010305470321327</v>
+        <v>2.3436365154339e-05</v>
       </c>
       <c r="EG14" t="n">
-        <v>0.0004890197888016701</v>
+        <v>2.175392000935972e-05</v>
       </c>
       <c r="EH14" t="n">
-        <v>0.000549279386177659</v>
+        <v>1.013100063573802e-05</v>
       </c>
       <c r="EI14" t="n">
-        <v>0.0006855645915493369</v>
+        <v>5.602583769359626e-05</v>
       </c>
       <c r="EJ14" t="n">
-        <v>1.740649167913944e-05</v>
+        <v>1.318847716902383e-05</v>
       </c>
       <c r="EK14" t="n">
-        <v>0.0001035897657857276</v>
+        <v>6.277369720919523e-06</v>
       </c>
       <c r="EL14" t="n">
-        <v>0.0001853327557910234</v>
+        <v>5.176976628717966e-06</v>
       </c>
       <c r="EM14" t="n">
-        <v>5.911008338443935e-05</v>
+        <v>1.761426347002271e-06</v>
       </c>
       <c r="EN14" t="n">
-        <v>0.0002149595529772341</v>
+        <v>6.879326974740252e-07</v>
       </c>
       <c r="EO14" t="n">
-        <v>3.456613194430247e-05</v>
+        <v>3.560988261597231e-06</v>
       </c>
       <c r="EP14" t="n">
-        <v>0.0006014388636685908</v>
+        <v>2.034927274507936e-05</v>
       </c>
       <c r="EQ14" t="n">
-        <v>9.862937440630049e-05</v>
+        <v>1.242615235241828e-05</v>
       </c>
       <c r="ER14" t="n">
-        <v>0.0003393929218873382</v>
+        <v>3.667850978672504e-05</v>
       </c>
       <c r="ES14" t="n">
-        <v>0.0002000547974603251</v>
+        <v>1.411563425790519e-05</v>
       </c>
       <c r="ET14" t="n">
-        <v>7.746285700704902e-05</v>
+        <v>5.355850589694455e-05</v>
       </c>
       <c r="EU14" t="n">
-        <v>0.000266959163127467</v>
+        <v>2.082658284052741e-06</v>
       </c>
       <c r="EV14" t="n">
-        <v>0.0001440921769244596</v>
+        <v>3.300955722806975e-05</v>
       </c>
       <c r="EW14" t="n">
-        <v>0.0005929036415182054</v>
+        <v>5.361918738344684e-06</v>
       </c>
       <c r="EX14" t="n">
-        <v>1.833984060795046e-05</v>
+        <v>1.603591499588219e-06</v>
       </c>
       <c r="EY14" t="n">
-        <v>0.000345874490449205</v>
+        <v>2.343729465792421e-05</v>
       </c>
       <c r="EZ14" t="n">
-        <v>0.0004792411637026817</v>
+        <v>3.902333992300555e-05</v>
       </c>
       <c r="FA14" t="n">
-        <v>0.0003531479742377996</v>
+        <v>6.366387970047072e-05</v>
       </c>
       <c r="FB14" t="n">
-        <v>0.0003188015834894031</v>
+        <v>3.887979346473003e-06</v>
       </c>
       <c r="FC14" t="n">
-        <v>5.122863876749761e-05</v>
+        <v>2.179803595936392e-05</v>
       </c>
       <c r="FD14" t="n">
-        <v>0.0001460885396227241</v>
+        <v>4.45859723186004e-06</v>
       </c>
       <c r="FE14" t="n">
-        <v>0.0001387745141983032</v>
+        <v>2.271336416015401e-05</v>
       </c>
       <c r="FF14" t="n">
-        <v>0.00014382520748768</v>
+        <v>1.155885092885001e-05</v>
       </c>
       <c r="FG14" t="n">
-        <v>0.0001264040038222447</v>
+        <v>1.424312631570501e-05</v>
       </c>
       <c r="FH14" t="n">
-        <v>0.0002421791141387075</v>
+        <v>1.48029466799926e-05</v>
       </c>
       <c r="FI14" t="n">
-        <v>1.107741627492942e-05</v>
+        <v>1.173760028905235e-05</v>
       </c>
       <c r="FJ14" t="n">
-        <v>0.0003023716853931546</v>
+        <v>3.351924533490092e-05</v>
       </c>
       <c r="FK14" t="n">
-        <v>5.735323793487623e-05</v>
+        <v>1.103382237488404e-05</v>
       </c>
       <c r="FL14" t="n">
-        <v>0.000116962444735691</v>
+        <v>2.761949872365221e-05</v>
       </c>
       <c r="FM14" t="n">
-        <v>2.090696943923831e-05</v>
+        <v>3.513268893584609e-07</v>
       </c>
       <c r="FN14" t="n">
-        <v>0.0004249743651598692</v>
+        <v>1.229249119205633e-05</v>
       </c>
       <c r="FO14" t="n">
-        <v>7.07386716385372e-05</v>
+        <v>2.130156644852832e-06</v>
       </c>
       <c r="FP14" t="n">
-        <v>0.0002117293333867565</v>
+        <v>6.465789920184761e-05</v>
       </c>
       <c r="FQ14" t="n">
-        <v>5.632874672301114e-05</v>
+        <v>1.929054269567132e-05</v>
       </c>
       <c r="FR14" t="n">
-        <v>8.028504089452326e-05</v>
+        <v>2.826921445375774e-05</v>
       </c>
       <c r="FS14" t="n">
-        <v>8.640289888717234e-05</v>
+        <v>1.540337689220905e-05</v>
       </c>
       <c r="FT14" t="n">
-        <v>0.000459707691334188</v>
+        <v>4.562168760458007e-05</v>
       </c>
       <c r="FU14" t="n">
-        <v>0.0003501501341816038</v>
+        <v>3.146518429275602e-05</v>
       </c>
       <c r="FV14" t="n">
-        <v>0.0001107192729250528</v>
+        <v>1.907944897538982e-05</v>
       </c>
       <c r="FW14" t="n">
-        <v>0.0005088725592941046</v>
+        <v>2.380510522925761e-05</v>
       </c>
       <c r="FX14" t="n">
-        <v>8.250935934484005e-06</v>
+        <v>1.400148266839096e-05</v>
       </c>
       <c r="FY14" t="n">
-        <v>6.939195009181276e-05</v>
+        <v>2.5752106012078e-05</v>
       </c>
       <c r="FZ14" t="n">
-        <v>0.0004064759705215693</v>
+        <v>2.820187000907026e-05</v>
       </c>
       <c r="GA14" t="n">
-        <v>0.0001285918551729992</v>
+        <v>7.79118636273779e-06</v>
       </c>
       <c r="GB14" t="n">
-        <v>0.0003919727460015565</v>
+        <v>6.630884308833629e-05</v>
       </c>
       <c r="GC14" t="n">
-        <v>0.0006656856276094913</v>
+        <v>2.004189809667878e-05</v>
       </c>
       <c r="GD14" t="n">
-        <v>0.0004753886605612934</v>
+        <v>4.146634091739543e-05</v>
       </c>
       <c r="GE14" t="n">
-        <v>0.0001176192163256928</v>
+        <v>2.816908818203956e-06</v>
       </c>
       <c r="GF14" t="n">
-        <v>0.0003828332992270589</v>
+        <v>1.705670729279518e-05</v>
       </c>
       <c r="GG14" t="n">
-        <v>0.0001083721872419119</v>
+        <v>4.135750714340247e-05</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1.792124294297537e-06</v>
+        <v>0.0016616340726614</v>
       </c>
       <c r="B15" t="n">
-        <v>2.76775645033922e-05</v>
+        <v>0.001517624827101827</v>
       </c>
       <c r="C15" t="n">
-        <v>7.687414836254902e-06</v>
+        <v>0.002256435807794333</v>
       </c>
       <c r="D15" t="n">
-        <v>1.528321035948466e-06</v>
+        <v>0.002166775753721595</v>
       </c>
       <c r="E15" t="n">
-        <v>2.793402745737694e-05</v>
+        <v>0.001790148671716452</v>
       </c>
       <c r="F15" t="n">
-        <v>9.844117448665202e-05</v>
+        <v>0.005419777240604162</v>
       </c>
       <c r="G15" t="n">
-        <v>2.904539360315539e-05</v>
+        <v>0.0004929043934680521</v>
       </c>
       <c r="H15" t="n">
-        <v>4.820129106519744e-05</v>
+        <v>0.002397679490968585</v>
       </c>
       <c r="I15" t="n">
-        <v>1.84868295036722e-05</v>
+        <v>0.001458934624679387</v>
       </c>
       <c r="J15" t="n">
-        <v>2.462308657413814e-06</v>
+        <v>0.001236003125086427</v>
       </c>
       <c r="K15" t="n">
-        <v>1.687399708316661e-05</v>
+        <v>0.001391677418723702</v>
       </c>
       <c r="L15" t="n">
-        <v>8.673978300066665e-06</v>
+        <v>0.002624338492751122</v>
       </c>
       <c r="M15" t="n">
-        <v>5.250427420833148e-06</v>
+        <v>0.001107897725887597</v>
       </c>
       <c r="N15" t="n">
-        <v>1.906759280245751e-05</v>
+        <v>0.003106119344010949</v>
       </c>
       <c r="O15" t="n">
-        <v>7.749975338811055e-05</v>
+        <v>0.005615949630737305</v>
       </c>
       <c r="P15" t="n">
-        <v>1.863354009401519e-05</v>
+        <v>0.0009990991093218327</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.754568751901388e-05</v>
+        <v>0.003559280419722199</v>
       </c>
       <c r="R15" t="n">
-        <v>8.999666079034796e-07</v>
+        <v>0.002428393345326185</v>
       </c>
       <c r="S15" t="n">
-        <v>3.839917553705163e-06</v>
+        <v>6.931315874680877e-05</v>
       </c>
       <c r="T15" t="n">
-        <v>4.586372597259469e-06</v>
+        <v>0.001404742710292339</v>
       </c>
       <c r="U15" t="n">
-        <v>7.912913133623078e-06</v>
+        <v>0.0002114852977683768</v>
       </c>
       <c r="V15" t="n">
-        <v>1.646950840950012e-05</v>
+        <v>0.0002921921259257942</v>
       </c>
       <c r="W15" t="n">
-        <v>2.240675894427113e-05</v>
+        <v>0.0001872797874966636</v>
       </c>
       <c r="X15" t="n">
-        <v>7.144196388253476e-06</v>
+        <v>0.0006323570851236582</v>
       </c>
       <c r="Y15" t="n">
-        <v>3.683292106870795e-06</v>
+        <v>0.0004292218945920467</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.812744812923484e-06</v>
+        <v>9.216366015607491e-05</v>
       </c>
       <c r="AA15" t="n">
-        <v>5.85177076573018e-07</v>
+        <v>0.0001379501482006162</v>
       </c>
       <c r="AB15" t="n">
-        <v>3.438188514337526e-06</v>
+        <v>0.0009251023875549436</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.69286740856478e-05</v>
+        <v>0.0002687987289391458</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.964715556823649e-05</v>
+        <v>3.880325675709173e-05</v>
       </c>
       <c r="AE15" t="n">
-        <v>4.397373231768142e-06</v>
+        <v>0.0009979454334825277</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.020353920466732e-05</v>
+        <v>0.001111682271584868</v>
       </c>
       <c r="AG15" t="n">
-        <v>5.533452167583164e-06</v>
+        <v>0.0006408462068066001</v>
       </c>
       <c r="AH15" t="n">
-        <v>7.468179319403134e-06</v>
+        <v>0.0004513573658186942</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.344816723758413e-06</v>
+        <v>0.0006091062678024173</v>
       </c>
       <c r="AJ15" t="n">
-        <v>3.142951300105779e-06</v>
+        <v>0.0007287250482477248</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.936347416631179e-06</v>
+        <v>0.0004078053752891719</v>
       </c>
       <c r="AL15" t="n">
-        <v>3.339159093229682e-06</v>
+        <v>0.002085481770336628</v>
       </c>
       <c r="AM15" t="n">
-        <v>2.193561613239581e-06</v>
+        <v>0.0004063455562572926</v>
       </c>
       <c r="AN15" t="n">
-        <v>6.342163032968529e-06</v>
+        <v>0.0007101717055775225</v>
       </c>
       <c r="AO15" t="n">
-        <v>3.08170092466753e-06</v>
+        <v>0.001539758057333529</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.700803113635629e-05</v>
+        <v>0.001709455391392112</v>
       </c>
       <c r="AQ15" t="n">
-        <v>6.365639819705393e-06</v>
+        <v>0.0002729654952418059</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.607839749340201e-06</v>
+        <v>2.249694080092013e-05</v>
       </c>
       <c r="AS15" t="n">
-        <v>5.547107093661907e-07</v>
+        <v>0.0001743322645779699</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.152381537394831e-05</v>
+        <v>0.0001265766331925988</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.430725569662172e-05</v>
+        <v>0.004841728135943413</v>
       </c>
       <c r="AV15" t="n">
-        <v>4.293675829103449e-06</v>
+        <v>0.0006004832684993744</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.387644624628592e-05</v>
+        <v>0.001275443821214139</v>
       </c>
       <c r="AX15" t="n">
-        <v>2.751862666627858e-05</v>
+        <v>0.0007486403919756413</v>
       </c>
       <c r="AY15" t="n">
-        <v>5.67547685932368e-05</v>
+        <v>0.004250217229127884</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.618828900973313e-05</v>
+        <v>0.001435567275620997</v>
       </c>
       <c r="BA15" t="n">
-        <v>2.583443711046129e-05</v>
+        <v>0.001758241560310125</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.582939512445591e-05</v>
+        <v>0.0008693658746778965</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.334660919383168e-05</v>
+        <v>0.001090232632122934</v>
       </c>
       <c r="BD15" t="n">
-        <v>2.802926246658899e-06</v>
+        <v>0.002982863690704107</v>
       </c>
       <c r="BE15" t="n">
-        <v>6.525455773953581e-06</v>
+        <v>0.0008120452403090894</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.77446872839937e-05</v>
+        <v>0.000536473176907748</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.704434336919803e-05</v>
+        <v>0.003128063166514039</v>
       </c>
       <c r="BH15" t="n">
-        <v>2.490230508556124e-05</v>
+        <v>9.114231215789914e-05</v>
       </c>
       <c r="BI15" t="n">
-        <v>6.980332727835048e-06</v>
+        <v>0.0003019269497599453</v>
       </c>
       <c r="BJ15" t="n">
-        <v>4.238526344124693e-06</v>
+        <v>0.0005538219702430069</v>
       </c>
       <c r="BK15" t="n">
-        <v>9.066521670320071e-06</v>
+        <v>0.0003468439099378884</v>
       </c>
       <c r="BL15" t="n">
-        <v>4.513879048317904e-07</v>
+        <v>0.0002108050684910268</v>
       </c>
       <c r="BM15" t="n">
-        <v>2.609563125588465e-05</v>
+        <v>0.000270390446530655</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.161312775366241e-05</v>
+        <v>0.002203085459768772</v>
       </c>
       <c r="BO15" t="n">
-        <v>5.00428541272413e-06</v>
+        <v>0.0006013450911268592</v>
       </c>
       <c r="BP15" t="n">
-        <v>6.422966635000193e-06</v>
+        <v>0.001329540624283254</v>
       </c>
       <c r="BQ15" t="n">
-        <v>6.545722499140538e-06</v>
+        <v>0.0006747323204763234</v>
       </c>
       <c r="BR15" t="n">
-        <v>1.392980811942834e-05</v>
+        <v>0.0003595396992750466</v>
       </c>
       <c r="BS15" t="n">
-        <v>1.382131631544326e-05</v>
+        <v>0.0007264447631314397</v>
       </c>
       <c r="BT15" t="n">
-        <v>1.581044307386037e-05</v>
+        <v>0.001386708812788129</v>
       </c>
       <c r="BU15" t="n">
-        <v>1.582496679475298e-06</v>
+        <v>0.0002569862990640104</v>
       </c>
       <c r="BV15" t="n">
-        <v>1.172101747215493e-05</v>
+        <v>0.00277043366804719</v>
       </c>
       <c r="BW15" t="n">
-        <v>3.809035206359113e-06</v>
+        <v>4.615526995621622e-05</v>
       </c>
       <c r="BX15" t="n">
-        <v>5.768277333118021e-06</v>
+        <v>0.0009607351385056973</v>
       </c>
       <c r="BY15" t="n">
-        <v>1.21105667858501e-05</v>
+        <v>0.0001640740520088002</v>
       </c>
       <c r="BZ15" t="n">
-        <v>2.534071063564625e-05</v>
+        <v>0.002503161784261465</v>
       </c>
       <c r="CA15" t="n">
-        <v>1.860421434685122e-06</v>
+        <v>0.0007426514057442546</v>
       </c>
       <c r="CB15" t="n">
-        <v>1.386451822327217e-05</v>
+        <v>0.0003987023083027452</v>
       </c>
       <c r="CC15" t="n">
-        <v>1.861457803897792e-06</v>
+        <v>0.0003399303532205522</v>
       </c>
       <c r="CD15" t="n">
-        <v>4.376749700440996e-07</v>
+        <v>0.0001750926167005673</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.736464810164762e-06</v>
+        <v>0.0007503445958718657</v>
       </c>
       <c r="CF15" t="n">
-        <v>1.162735088655609e-06</v>
+        <v>0.001045159297063947</v>
       </c>
       <c r="CG15" t="n">
-        <v>1.147494003816973e-06</v>
+        <v>7.370807725237682e-05</v>
       </c>
       <c r="CH15" t="n">
-        <v>8.940837687987369e-06</v>
+        <v>0.0003812357608694583</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.74837277882034e-05</v>
+        <v>0.001239218981936574</v>
       </c>
       <c r="CJ15" t="n">
-        <v>7.756063496344723e-06</v>
+        <v>0.0002070373011520132</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.103848990169354e-05</v>
+        <v>9.755103383213282e-05</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.956448159035062e-07</v>
+        <v>0.0003724817943293601</v>
       </c>
       <c r="CM15" t="n">
-        <v>8.338169550370367e-07</v>
+        <v>0.0002496834495104849</v>
       </c>
       <c r="CN15" t="n">
-        <v>5.081728431832744e-06</v>
+        <v>0.0004748578066937625</v>
       </c>
       <c r="CO15" t="n">
-        <v>9.449604476685636e-07</v>
+        <v>0.0004341364547144622</v>
       </c>
       <c r="CP15" t="n">
-        <v>2.160963049391285e-05</v>
+        <v>0.0002853974583558738</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.472608659649268e-05</v>
+        <v>0.002039775950834155</v>
       </c>
       <c r="CR15" t="n">
-        <v>6.382208994182292e-06</v>
+        <v>0.0008118471596390009</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.972851234517293e-06</v>
+        <v>0.0003503282787278295</v>
       </c>
       <c r="CT15" t="n">
-        <v>7.332503628276754e-06</v>
+        <v>0.001041005365550518</v>
       </c>
       <c r="CU15" t="n">
-        <v>8.320598681166302e-06</v>
+        <v>0.0005802036612294614</v>
       </c>
       <c r="CV15" t="n">
-        <v>1.39201290494384e-06</v>
+        <v>9.839523409027606e-05</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.231786654898315e-06</v>
+        <v>0.0004020377236884087</v>
       </c>
       <c r="CX15" t="n">
-        <v>8.392851214011898e-07</v>
+        <v>0.001052376930601895</v>
       </c>
       <c r="CY15" t="n">
-        <v>6.3612185385864e-07</v>
+        <v>4.939673090120777e-05</v>
       </c>
       <c r="CZ15" t="n">
-        <v>6.9046418502694e-06</v>
+        <v>0.0008846427081152797</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.972066093003377e-05</v>
+        <v>0.001515484414994717</v>
       </c>
       <c r="DB15" t="n">
-        <v>6.675934400846018e-06</v>
+        <v>7.347960490733385e-05</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.390568377246382e-05</v>
+        <v>0.0003762734122574329</v>
       </c>
       <c r="DD15" t="n">
-        <v>4.011762030131649e-06</v>
+        <v>0.0003565390361472964</v>
       </c>
       <c r="DE15" t="n">
-        <v>3.86346710001817e-06</v>
+        <v>0.001433212426491082</v>
       </c>
       <c r="DF15" t="n">
-        <v>2.012731783906929e-05</v>
+        <v>0.001178428065031767</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.618362486828119e-06</v>
+        <v>0.0004901631036773324</v>
       </c>
       <c r="DH15" t="n">
-        <v>1.791039176168852e-05</v>
+        <v>0.001006225938908756</v>
       </c>
       <c r="DI15" t="n">
-        <v>1.446875103283674e-06</v>
+        <v>0.0006531724939122796</v>
       </c>
       <c r="DJ15" t="n">
-        <v>5.502201929630246e-07</v>
+        <v>0.001231457339599729</v>
       </c>
       <c r="DK15" t="n">
-        <v>7.592675501655322e-06</v>
+        <v>0.001183269429020584</v>
       </c>
       <c r="DL15" t="n">
-        <v>1.937387423822656e-05</v>
+        <v>0.001635462744161487</v>
       </c>
       <c r="DM15" t="n">
-        <v>1.138016432378208e-05</v>
+        <v>0.001981016481295228</v>
       </c>
       <c r="DN15" t="n">
-        <v>6.432927875721361e-06</v>
+        <v>0.0001222803985001519</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.175584086216986e-07</v>
+        <v>0.001403862028382719</v>
       </c>
       <c r="DP15" t="n">
-        <v>2.87959551314998e-07</v>
+        <v>0.0005498832324519753</v>
       </c>
       <c r="DQ15" t="n">
-        <v>1.064297066477593e-05</v>
+        <v>1.536311174277216e-05</v>
       </c>
       <c r="DR15" t="n">
-        <v>1.686647374299355e-05</v>
+        <v>0.0007500607753172517</v>
       </c>
       <c r="DS15" t="n">
-        <v>2.073742507491261e-05</v>
+        <v>0.0005702014314010739</v>
       </c>
       <c r="DT15" t="n">
-        <v>1.484271524532232e-05</v>
+        <v>0.000229058408876881</v>
       </c>
       <c r="DU15" t="n">
-        <v>7.214505785668734e-06</v>
+        <v>0.0002697466406971216</v>
       </c>
       <c r="DV15" t="n">
-        <v>3.379280315130018e-06</v>
+        <v>0.001270633074454963</v>
       </c>
       <c r="DW15" t="n">
-        <v>2.135527893187827e-06</v>
+        <v>7.338396244449541e-05</v>
       </c>
       <c r="DX15" t="n">
-        <v>4.887738668912789e-06</v>
+        <v>0.001788840629160404</v>
       </c>
       <c r="DY15" t="n">
-        <v>7.299477147171274e-07</v>
+        <v>0.001665729214437306</v>
       </c>
       <c r="DZ15" t="n">
-        <v>1.308937135036103e-05</v>
+        <v>0.000883214408531785</v>
       </c>
       <c r="EA15" t="n">
-        <v>2.979564897032105e-06</v>
+        <v>0.001537976204417646</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.019044157146709e-05</v>
+        <v>0.0001018568582367152</v>
       </c>
       <c r="EC15" t="n">
-        <v>7.988543075043708e-06</v>
+        <v>7.800169987604022e-05</v>
       </c>
       <c r="ED15" t="n">
-        <v>3.432350922594196e-06</v>
+        <v>0.001315104309469461</v>
       </c>
       <c r="EE15" t="n">
-        <v>1.714949212328065e-05</v>
+        <v>0.0007037855684757233</v>
       </c>
       <c r="EF15" t="n">
-        <v>3.088315452259849e-06</v>
+        <v>0.0005973448278382421</v>
       </c>
       <c r="EG15" t="n">
-        <v>9.058093382918742e-06</v>
+        <v>4.470688872970641e-05</v>
       </c>
       <c r="EH15" t="n">
-        <v>7.497086699004285e-06</v>
+        <v>0.0005582688027061522</v>
       </c>
       <c r="EI15" t="n">
-        <v>1.395925573888235e-05</v>
+        <v>0.0002076074597425759</v>
       </c>
       <c r="EJ15" t="n">
-        <v>4.828635155718075e-06</v>
+        <v>0.0009077025461010635</v>
       </c>
       <c r="EK15" t="n">
-        <v>7.328871106437873e-06</v>
+        <v>0.000340718834195286</v>
       </c>
       <c r="EL15" t="n">
-        <v>6.559407211170765e-06</v>
+        <v>1.938379864441231e-05</v>
       </c>
       <c r="EM15" t="n">
-        <v>1.01737750810571e-05</v>
+        <v>0.0002136744151357561</v>
       </c>
       <c r="EN15" t="n">
-        <v>5.403806426329538e-06</v>
+        <v>0.0003717436920851469</v>
       </c>
       <c r="EO15" t="n">
-        <v>2.228117864433443e-06</v>
+        <v>0.0001818822493078187</v>
       </c>
       <c r="EP15" t="n">
-        <v>8.25400093162898e-06</v>
+        <v>0.0008649635128676891</v>
       </c>
       <c r="EQ15" t="n">
-        <v>7.230170922412071e-06</v>
+        <v>3.80657147616148e-05</v>
       </c>
       <c r="ER15" t="n">
-        <v>1.266184153791983e-05</v>
+        <v>0.0002355416800128296</v>
       </c>
       <c r="ES15" t="n">
-        <v>5.302104909787886e-06</v>
+        <v>0.0001721542066661641</v>
       </c>
       <c r="ET15" t="n">
-        <v>6.97286986905965e-06</v>
+        <v>0.001492862356826663</v>
       </c>
       <c r="EU15" t="n">
-        <v>9.989112186303828e-07</v>
+        <v>0.0001523578685009852</v>
       </c>
       <c r="EV15" t="n">
-        <v>2.783749914669897e-05</v>
+        <v>0.0005819621146656573</v>
       </c>
       <c r="EW15" t="n">
-        <v>1.932708255480975e-05</v>
+        <v>0.0003963396302424371</v>
       </c>
       <c r="EX15" t="n">
-        <v>1.700878442534304e-06</v>
+        <v>0.000119730771984905</v>
       </c>
       <c r="EY15" t="n">
-        <v>2.024228933805716e-06</v>
+        <v>0.000790008925832808</v>
       </c>
       <c r="EZ15" t="n">
-        <v>1.019489332065859e-06</v>
+        <v>0.0007732252706773579</v>
       </c>
       <c r="FA15" t="n">
-        <v>9.684795259090606e-07</v>
+        <v>0.0001160407700808719</v>
       </c>
       <c r="FB15" t="n">
-        <v>8.194044312404003e-06</v>
+        <v>0.0004805945209227502</v>
       </c>
       <c r="FC15" t="n">
-        <v>1.768353286024649e-05</v>
+        <v>0.001387955388054252</v>
       </c>
       <c r="FD15" t="n">
-        <v>9.144535397354048e-06</v>
+        <v>0.0002296790771652013</v>
       </c>
       <c r="FE15" t="n">
-        <v>1.340336166322231e-05</v>
+        <v>4.327643546275795e-05</v>
       </c>
       <c r="FF15" t="n">
-        <v>3.323086275486276e-06</v>
+        <v>0.0001479025231674314</v>
       </c>
       <c r="FG15" t="n">
-        <v>5.574707302002935e-06</v>
+        <v>0.0005027813604101539</v>
       </c>
       <c r="FH15" t="n">
-        <v>7.37645950721344e-06</v>
+        <v>0.0003793029754888266</v>
       </c>
       <c r="FI15" t="n">
-        <v>7.989605364855379e-06</v>
+        <v>0.000791694619692862</v>
       </c>
       <c r="FJ15" t="n">
-        <v>1.550434535602108e-05</v>
+        <v>0.001210794551298022</v>
       </c>
       <c r="FK15" t="n">
-        <v>7.602463028888451e-06</v>
+        <v>0.0004166975850239396</v>
       </c>
       <c r="FL15" t="n">
-        <v>1.578780211275443e-05</v>
+        <v>0.00195931363850832</v>
       </c>
       <c r="FM15" t="n">
-        <v>5.547090040636249e-06</v>
+        <v>0.0002651913091540337</v>
       </c>
       <c r="FN15" t="n">
-        <v>1.502699888078496e-06</v>
+        <v>0.0002639318117871881</v>
       </c>
       <c r="FO15" t="n">
-        <v>1.566126798024925e-06</v>
+        <v>0.001517573371529579</v>
       </c>
       <c r="FP15" t="n">
-        <v>2.023197794187581e-06</v>
+        <v>0.0007089662249200046</v>
       </c>
       <c r="FQ15" t="n">
-        <v>1.292723391088657e-05</v>
+        <v>0.000825682538561523</v>
       </c>
       <c r="FR15" t="n">
-        <v>1.871930635388708e-06</v>
+        <v>0.001907067722640932</v>
       </c>
       <c r="FS15" t="n">
-        <v>1.292261003982276e-06</v>
+        <v>0.001593316323123872</v>
       </c>
       <c r="FT15" t="n">
-        <v>2.970270725199953e-05</v>
+        <v>0.002219371031969786</v>
       </c>
       <c r="FU15" t="n">
-        <v>2.053229945886414e-05</v>
+        <v>0.001080773072317243</v>
       </c>
       <c r="FV15" t="n">
-        <v>3.537444626999786e-06</v>
+        <v>0.001360381371341646</v>
       </c>
       <c r="FW15" t="n">
-        <v>6.724016202497296e-06</v>
+        <v>0.002326868008822203</v>
       </c>
       <c r="FX15" t="n">
-        <v>1.144425004895311e-05</v>
+        <v>0.001799254911020398</v>
       </c>
       <c r="FY15" t="n">
-        <v>7.653505235794e-06</v>
+        <v>0.0002240449975943193</v>
       </c>
       <c r="FZ15" t="n">
-        <v>3.330958179503796e-06</v>
+        <v>0.0006541137699969113</v>
       </c>
       <c r="GA15" t="n">
-        <v>7.924590136099141e-06</v>
+        <v>0.001217689947225153</v>
       </c>
       <c r="GB15" t="n">
-        <v>6.648491762462072e-06</v>
+        <v>0.0009754875209182501</v>
       </c>
       <c r="GC15" t="n">
-        <v>2.359005156904459e-05</v>
+        <v>0.0005278683383949101</v>
       </c>
       <c r="GD15" t="n">
-        <v>3.530037702148547e-06</v>
+        <v>5.859821249032393e-05</v>
       </c>
       <c r="GE15" t="n">
-        <v>6.094596301409183e-06</v>
+        <v>0.000263521826127544</v>
       </c>
       <c r="GF15" t="n">
-        <v>8.010078090592287e-06</v>
+        <v>0.0001408884127158672</v>
       </c>
       <c r="GG15" t="n">
-        <v>5.458432497107424e-06</v>
+        <v>6.910758384037763e-05</v>
       </c>
     </row>
   </sheetData>
